--- a/transport/input_data/global/international_marine_and_aviation_data.xlsx
+++ b/transport/input_data/global/international_marine_and_aviation_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="52">
   <si>
     <t>Country</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Libya</t>
   </si>
   <si>
+    <t>Mauritania</t>
+  </si>
+  <si>
     <t>Mexico</t>
   </si>
   <si>
@@ -100,7 +103,7 @@
     <t>Peru</t>
   </si>
   <si>
-    <t>Republic of the Congo</t>
+    <t>Republic of Congo</t>
   </si>
   <si>
     <t>Russia</t>
@@ -524,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D443"/>
+  <dimension ref="A1:D456"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -546,7 +549,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>5.561388888888889</v>
@@ -560,7 +563,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3">
         <v>6.198611111111111</v>
@@ -574,7 +577,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>6.406666666666666</v>
@@ -588,7 +591,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5">
         <v>5.083611111111111</v>
@@ -602,7 +605,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6">
         <v>5.561388888888889</v>
@@ -616,7 +619,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7">
         <v>4.618333333333333</v>
@@ -630,7 +633,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8">
         <v>4.348611111111111</v>
@@ -644,7 +647,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9">
         <v>5.316388888888889</v>
@@ -658,7 +661,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10">
         <v>4.336388888888889</v>
@@ -672,7 +675,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11">
         <v>2.658333333333333</v>
@@ -686,7 +689,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12">
         <v>2.731666666666666</v>
@@ -700,7 +703,7 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13">
         <v>4.266944444444444</v>
@@ -714,7 +717,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14">
         <v>6.777222222222222</v>
@@ -728,7 +731,7 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>8.501388888888888</v>
@@ -742,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>8.489166666666666</v>
@@ -756,7 +759,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>10.89027777777778</v>
@@ -770,7 +773,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>10.79222222222222</v>
@@ -784,7 +787,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>10.97611111111111</v>
@@ -798,7 +801,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>11.33111111111111</v>
@@ -812,7 +815,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>12.02944444444444</v>
@@ -826,7 +829,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>10.93916666666667</v>
@@ -840,7 +843,7 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>10.80444444444444</v>
@@ -854,7 +857,7 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>4.613333333333333</v>
@@ -868,7 +871,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>4.65</v>
@@ -882,7 +885,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>9.015277777777778</v>
@@ -896,7 +899,7 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>11.62527777777778</v>
@@ -910,7 +913,7 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28">
         <v>38.28111111111111</v>
@@ -924,7 +927,7 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C29">
         <v>39.72666666666667</v>
@@ -938,7 +941,7 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30">
         <v>41.82138888888889</v>
@@ -952,7 +955,7 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31">
         <v>45.11666666666667</v>
@@ -966,7 +969,7 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C32">
         <v>44.835</v>
@@ -980,7 +983,7 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C33">
         <v>47.8975</v>
@@ -994,7 +997,7 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34">
         <v>51.63</v>
@@ -1008,7 +1011,7 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C35">
         <v>54.68305555555555</v>
@@ -1022,7 +1025,7 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C36">
         <v>58.1825</v>
@@ -1036,7 +1039,7 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C37">
         <v>44.60027777777778</v>
@@ -1050,7 +1053,7 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C38">
         <v>14.56805555555556</v>
@@ -1064,7 +1067,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39">
         <v>20.40527777777778</v>
@@ -1078,7 +1081,7 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40">
         <v>36.60055555555556</v>
@@ -1092,7 +1095,7 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C41">
         <v>25.16138888888889</v>
@@ -1106,7 +1109,7 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C42">
         <v>26.15361111111111</v>
@@ -1120,7 +1123,7 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C43">
         <v>27.29305555555555</v>
@@ -1134,7 +1137,7 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C44">
         <v>29.16722222222222</v>
@@ -1148,7 +1151,7 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C45">
         <v>28.48111111111111</v>
@@ -1162,7 +1165,7 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C46">
         <v>26.43555555555556</v>
@@ -1176,7 +1179,7 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C47">
         <v>25.8475</v>
@@ -1190,7 +1193,7 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C48">
         <v>29.30194444444444</v>
@@ -1204,7 +1207,7 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C49">
         <v>28.38333333333333</v>
@@ -1218,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C50">
         <v>11.95611111111111</v>
@@ -1232,7 +1235,7 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C51">
         <v>12.82416666666667</v>
@@ -1246,7 +1249,7 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C52">
         <v>20.87722222222222</v>
@@ -1260,7 +1263,7 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C53">
         <v>24.48527777777778</v>
@@ -1274,7 +1277,7 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C54">
         <v>35.95388888888889</v>
@@ -1288,7 +1291,7 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C55">
         <v>40.59666666666666</v>
@@ -1302,7 +1305,7 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C56">
         <v>42.37277777777778</v>
@@ -1316,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C57">
         <v>42.0175</v>
@@ -1330,7 +1333,7 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C58">
         <v>43.49972222222222</v>
@@ -1344,7 +1347,7 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C59">
         <v>45.76611111111111</v>
@@ -1358,7 +1361,7 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C60">
         <v>50.08888888888889</v>
@@ -1372,7 +1375,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C61">
         <v>57.17388888888889</v>
@@ -1386,7 +1389,7 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C62">
         <v>57.77027777777778</v>
@@ -1400,7 +1403,7 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C63">
         <v>25.07194444444444</v>
@@ -1414,7 +1417,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C64">
         <v>25.18222222222222</v>
@@ -1428,7 +1431,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C65">
         <v>43.41583333333333</v>
@@ -1442,7 +1445,7 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C66">
         <v>51.6675</v>
@@ -1456,7 +1459,7 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C67">
         <v>5.083611111111111</v>
@@ -1470,7 +1473,7 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C68">
         <v>8.183055555555555</v>
@@ -1484,7 +1487,7 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C69">
         <v>7.239722222222222</v>
@@ -1498,7 +1501,7 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C70">
         <v>7.533611111111111</v>
@@ -1512,7 +1515,7 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C71">
         <v>6.516944444444444</v>
@@ -1526,7 +1529,7 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C72">
         <v>6.713055555555556</v>
@@ -1540,7 +1543,7 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C73">
         <v>7.091944444444445</v>
@@ -1554,7 +1557,7 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C74">
         <v>7.791388888888889</v>
@@ -1568,7 +1571,7 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C75">
         <v>8.836666666666666</v>
@@ -1582,7 +1585,7 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C76">
         <v>4.733333333333333</v>
@@ -1596,7 +1599,7 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C77">
         <v>5.256111111111111</v>
@@ -1610,7 +1613,7 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C78">
         <v>7.254166666666666</v>
@@ -1624,7 +1627,7 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C79">
         <v>8.060833333333333</v>
@@ -1638,7 +1641,7 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C80">
         <v>69.01666666666667</v>
@@ -1652,7 +1655,7 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C81">
         <v>72.67277777777778</v>
@@ -1666,7 +1669,7 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C82">
         <v>77.78277777777778</v>
@@ -1680,7 +1683,7 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C83">
         <v>85.28333333333333</v>
@@ -1694,7 +1697,7 @@
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C84">
         <v>92.75944444444444</v>
@@ -1708,7 +1711,7 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C85">
         <v>102.4466666666667</v>
@@ -1722,7 +1725,7 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C86">
         <v>113.7425</v>
@@ -1736,7 +1739,7 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C87">
         <v>123.6858333333333</v>
@@ -1750,7 +1753,7 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C88">
         <v>127.5972222222222</v>
@@ -1764,7 +1767,7 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C89">
         <v>58.44472222222223</v>
@@ -1778,7 +1781,7 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C90">
         <v>53.64277777777778</v>
@@ -1792,7 +1795,7 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C91">
         <v>47.18444444444444</v>
@@ -1806,7 +1809,7 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C92">
         <v>73.82083333333334</v>
@@ -1820,7 +1823,7 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C93">
         <v>5.524722222222223</v>
@@ -1834,7 +1837,7 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C94">
         <v>6.051388888888889</v>
@@ -1848,7 +1851,7 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C95">
         <v>6.37</v>
@@ -1862,7 +1865,7 @@
         <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C96">
         <v>8.183055555555555</v>
@@ -1876,7 +1879,7 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C97">
         <v>8.832222222222223</v>
@@ -1890,7 +1893,7 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C98">
         <v>8.86888888888889</v>
@@ -1904,7 +1907,7 @@
         <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C99">
         <v>9.088333333333333</v>
@@ -1918,7 +1921,7 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C100">
         <v>10.39055555555556</v>
@@ -1932,7 +1935,7 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C101">
         <v>10.5775</v>
@@ -1946,7 +1949,7 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C102">
         <v>4.895833333333333</v>
@@ -1960,7 +1963,7 @@
         <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C103">
         <v>5.739166666666667</v>
@@ -1974,7 +1977,7 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C104">
         <v>11.20555555555556</v>
@@ -1988,7 +1991,7 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C105">
         <v>10.44277777777778</v>
@@ -2002,7 +2005,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C106">
         <v>9.444722222222222</v>
@@ -2016,7 +2019,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C107">
         <v>9.983611111111111</v>
@@ -2030,7 +2033,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C108">
         <v>6.908888888888889</v>
@@ -2044,7 +2047,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C109">
         <v>8.146111111111111</v>
@@ -2058,7 +2061,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C110">
         <v>6.198611111111111</v>
@@ -2072,7 +2075,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C111">
         <v>5.206111111111111</v>
@@ -2086,7 +2089,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C112">
         <v>7.643888888888889</v>
@@ -2100,7 +2103,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C113">
         <v>8.795555555555556</v>
@@ -2114,7 +2117,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C114">
         <v>7.852222222222222</v>
@@ -2128,7 +2131,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C115">
         <v>3.7425</v>
@@ -2142,7 +2145,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C116">
         <v>3.273611111111111</v>
@@ -2156,7 +2159,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C117">
         <v>3.124444444444444</v>
@@ -2170,7 +2173,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C118">
         <v>12.59305555555556</v>
@@ -2184,7 +2187,7 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C119">
         <v>3.601388888888889</v>
@@ -2198,7 +2201,7 @@
         <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C120">
         <v>4.311944444444444</v>
@@ -2212,7 +2215,7 @@
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C121">
         <v>4.667222222222223</v>
@@ -2226,7 +2229,7 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C122">
         <v>5.255277777777778</v>
@@ -2240,7 +2243,7 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C123">
         <v>5.573611111111111</v>
@@ -2254,7 +2257,7 @@
         <v>13</v>
       </c>
       <c r="B124" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C124">
         <v>7.203055555555555</v>
@@ -2268,7 +2271,7 @@
         <v>13</v>
       </c>
       <c r="B125" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C125">
         <v>8.359166666666667</v>
@@ -2282,7 +2285,7 @@
         <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C126">
         <v>8.955555555555556</v>
@@ -2296,7 +2299,7 @@
         <v>13</v>
       </c>
       <c r="B127" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C127">
         <v>10.045</v>
@@ -2310,7 +2313,7 @@
         <v>13</v>
       </c>
       <c r="B128" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C128">
         <v>4.641666666666667</v>
@@ -2324,7 +2327,7 @@
         <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C129">
         <v>10.10444444444444</v>
@@ -2338,7 +2341,7 @@
         <v>13</v>
       </c>
       <c r="B130" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C130">
         <v>11.57111111111111</v>
@@ -2352,7 +2355,7 @@
         <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C131">
         <v>13.60027777777778</v>
@@ -2366,7 +2369,7 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C132">
         <v>65.75805555555556</v>
@@ -2380,7 +2383,7 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C133">
         <v>64.36138888888888</v>
@@ -2394,7 +2397,7 @@
         <v>14</v>
       </c>
       <c r="B134" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C134">
         <v>63.79805555555556</v>
@@ -2408,7 +2411,7 @@
         <v>14</v>
       </c>
       <c r="B135" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C135">
         <v>64.41055555555556</v>
@@ -2422,7 +2425,7 @@
         <v>14</v>
       </c>
       <c r="B136" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C136">
         <v>68.19583333333334</v>
@@ -2436,7 +2439,7 @@
         <v>14</v>
       </c>
       <c r="B137" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C137">
         <v>67.06861111111111</v>
@@ -2450,7 +2453,7 @@
         <v>14</v>
       </c>
       <c r="B138" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C138">
         <v>68.12666666666667</v>
@@ -2464,7 +2467,7 @@
         <v>14</v>
       </c>
       <c r="B139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C139">
         <v>70.50722222222223</v>
@@ -2478,7 +2481,7 @@
         <v>14</v>
       </c>
       <c r="B140" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C140">
         <v>74.05527777777777</v>
@@ -2492,7 +2495,7 @@
         <v>14</v>
       </c>
       <c r="B141" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C141">
         <v>31.44361111111111</v>
@@ -2506,7 +2509,7 @@
         <v>14</v>
       </c>
       <c r="B142" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C142">
         <v>34.19</v>
@@ -2520,7 +2523,7 @@
         <v>14</v>
       </c>
       <c r="B143" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C143">
         <v>58.5775</v>
@@ -2534,7 +2537,7 @@
         <v>14</v>
       </c>
       <c r="B144" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C144">
         <v>64.37638888888888</v>
@@ -2548,7 +2551,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C145">
         <v>91.74027777777778</v>
@@ -2562,7 +2565,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C146">
         <v>97.8775</v>
@@ -2576,7 +2579,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C147">
         <v>99.83750000000001</v>
@@ -2590,7 +2593,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C148">
         <v>95.86861111111111</v>
@@ -2604,7 +2607,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C149">
         <v>95.99111111111111</v>
@@ -2618,7 +2621,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C150">
         <v>103.2552777777778</v>
@@ -2632,7 +2635,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C151">
         <v>114.1577777777778</v>
@@ -2646,7 +2649,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C152">
         <v>117.7347222222222</v>
@@ -2660,7 +2663,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C153">
         <v>116.7669444444444</v>
@@ -2674,7 +2677,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C154">
         <v>53.99805555555555</v>
@@ -2688,7 +2691,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C155">
         <v>72.11583333333333</v>
@@ -2702,7 +2705,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C156">
         <v>107.1752777777778</v>
@@ -2716,7 +2719,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C157">
         <v>111.7566666666667</v>
@@ -2730,7 +2733,7 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C158">
         <v>1.646666666666667</v>
@@ -2744,7 +2747,7 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C159">
         <v>1.690833333333333</v>
@@ -2758,7 +2761,7 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C160">
         <v>1.596666666666667</v>
@@ -2772,7 +2775,7 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C161">
         <v>1.391944444444444</v>
@@ -2786,7 +2789,7 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C162">
         <v>1.223333333333333</v>
@@ -2800,7 +2803,7 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C163">
         <v>1.598055555555556</v>
@@ -2814,7 +2817,7 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C164">
         <v>1.749722222222222</v>
@@ -2828,7 +2831,7 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C165">
         <v>2.136388888888889</v>
@@ -2842,7 +2845,7 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C166">
         <v>2.599444444444444</v>
@@ -2856,7 +2859,7 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C167">
         <v>1.476111111111111</v>
@@ -2870,7 +2873,7 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C168">
         <v>2.341388888888889</v>
@@ -2884,7 +2887,7 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C169">
         <v>2.345</v>
@@ -2898,7 +2901,7 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C170">
         <v>2.386111111111111</v>
@@ -2912,7 +2915,7 @@
         <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C171">
         <v>57.80777777777778</v>
@@ -2926,7 +2929,7 @@
         <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C172">
         <v>57.80777777777778</v>
@@ -2940,7 +2943,7 @@
         <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C173">
         <v>47.19916666666666</v>
@@ -2954,7 +2957,7 @@
         <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C174">
         <v>46.52555555555556</v>
@@ -2968,7 +2971,7 @@
         <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C175">
         <v>53.69166666666667</v>
@@ -2982,7 +2985,7 @@
         <v>17</v>
       </c>
       <c r="B176" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C176">
         <v>60.01277777777778</v>
@@ -2996,7 +2999,7 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C177">
         <v>46.45194444444444</v>
@@ -3010,7 +3013,7 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C178">
         <v>50.58027777777778</v>
@@ -3024,7 +3027,7 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C179">
         <v>48.74277777777777</v>
@@ -3038,7 +3041,7 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C180">
         <v>15.64333333333333</v>
@@ -3052,7 +3055,7 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C181">
         <v>21.44972222222222</v>
@@ -3066,7 +3069,7 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C182">
         <v>37.84027777777778</v>
@@ -3080,7 +3083,7 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C183">
         <v>47.39111111111111</v>
@@ -3094,7 +3097,7 @@
         <v>18</v>
       </c>
       <c r="B184" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C184">
         <v>8.33</v>
@@ -3108,7 +3111,7 @@
         <v>18</v>
       </c>
       <c r="B185" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C185">
         <v>8.844444444444445</v>
@@ -3122,7 +3125,7 @@
         <v>18</v>
       </c>
       <c r="B186" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C186">
         <v>10.94416666666667</v>
@@ -3136,7 +3139,7 @@
         <v>18</v>
       </c>
       <c r="B187" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C187">
         <v>15.89555555555556</v>
@@ -3150,7 +3153,7 @@
         <v>18</v>
       </c>
       <c r="B188" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C188">
         <v>10.23083333333333</v>
@@ -3164,7 +3167,7 @@
         <v>18</v>
       </c>
       <c r="B189" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C189">
         <v>9.493611111111111</v>
@@ -3178,7 +3181,7 @@
         <v>18</v>
       </c>
       <c r="B190" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C190">
         <v>11.80666666666667</v>
@@ -3192,7 +3195,7 @@
         <v>18</v>
       </c>
       <c r="B191" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C191">
         <v>12.65805555555556</v>
@@ -3206,7 +3209,7 @@
         <v>18</v>
       </c>
       <c r="B192" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C192">
         <v>11.22222222222222</v>
@@ -3220,7 +3223,7 @@
         <v>18</v>
       </c>
       <c r="B193" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C193">
         <v>5.414444444444444</v>
@@ -3234,7 +3237,7 @@
         <v>18</v>
       </c>
       <c r="B194" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C194">
         <v>2.246666666666667</v>
@@ -3248,7 +3251,7 @@
         <v>18</v>
       </c>
       <c r="B195" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C195">
         <v>2.540277777777778</v>
@@ -3262,7 +3265,7 @@
         <v>18</v>
       </c>
       <c r="B196" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C196">
         <v>7.815</v>
@@ -3276,7 +3279,7 @@
         <v>19</v>
       </c>
       <c r="B197" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C197">
         <v>38.75888888888889</v>
@@ -3290,7 +3293,7 @@
         <v>19</v>
       </c>
       <c r="B198" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C198">
         <v>36.98277777777778</v>
@@ -3304,7 +3307,7 @@
         <v>19</v>
       </c>
       <c r="B199" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C199">
         <v>35.79444444444444</v>
@@ -3318,7 +3321,7 @@
         <v>19</v>
       </c>
       <c r="B200" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C200">
         <v>36.68861111111111</v>
@@ -3332,7 +3335,7 @@
         <v>19</v>
       </c>
       <c r="B201" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C201">
         <v>37.76666666666667</v>
@@ -3346,7 +3349,7 @@
         <v>19</v>
       </c>
       <c r="B202" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C202">
         <v>39.31027777777778</v>
@@ -3360,7 +3363,7 @@
         <v>19</v>
       </c>
       <c r="B203" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C203">
         <v>40.78222222222222</v>
@@ -3374,7 +3377,7 @@
         <v>19</v>
       </c>
       <c r="B204" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C204">
         <v>45.74027777777778</v>
@@ -3388,7 +3391,7 @@
         <v>19</v>
       </c>
       <c r="B205" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C205">
         <v>47.33444444444444</v>
@@ -3402,7 +3405,7 @@
         <v>19</v>
       </c>
       <c r="B206" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C206">
         <v>17.83083333333333</v>
@@ -3416,7 +3419,7 @@
         <v>19</v>
       </c>
       <c r="B207" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C207">
         <v>19.46805555555556</v>
@@ -3430,7 +3433,7 @@
         <v>19</v>
       </c>
       <c r="B208" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C208">
         <v>33.92527777777778</v>
@@ -3444,7 +3447,7 @@
         <v>19</v>
       </c>
       <c r="B209" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C209">
         <v>42.93805555555556</v>
@@ -3458,7 +3461,7 @@
         <v>20</v>
       </c>
       <c r="B210" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C210">
         <v>71.07444444444444</v>
@@ -3472,7 +3475,7 @@
         <v>20</v>
       </c>
       <c r="B211" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C211">
         <v>74.55361111111111</v>
@@ -3486,7 +3489,7 @@
         <v>20</v>
       </c>
       <c r="B212" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C212">
         <v>75.53361111111111</v>
@@ -3500,7 +3503,7 @@
         <v>20</v>
       </c>
       <c r="B213" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C213">
         <v>73.81861111111111</v>
@@ -3514,7 +3517,7 @@
         <v>20</v>
       </c>
       <c r="B214" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C214">
         <v>74.43111111111111</v>
@@ -3528,7 +3531,7 @@
         <v>20</v>
       </c>
       <c r="B215" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C215">
         <v>77.82416666666667</v>
@@ -3542,7 +3545,7 @@
         <v>20</v>
       </c>
       <c r="B216" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C216">
         <v>81.48583333333333</v>
@@ -3556,7 +3559,7 @@
         <v>20</v>
       </c>
       <c r="B217" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C217">
         <v>83.79527777777778</v>
@@ -3570,7 +3573,7 @@
         <v>20</v>
       </c>
       <c r="B218" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C218">
         <v>84.10472222222222</v>
@@ -3584,7 +3587,7 @@
         <v>20</v>
       </c>
       <c r="B219" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C219">
         <v>33.12833333333333</v>
@@ -3598,7 +3601,7 @@
         <v>20</v>
       </c>
       <c r="B220" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C220">
         <v>46.12833333333333</v>
@@ -3612,7 +3615,7 @@
         <v>20</v>
       </c>
       <c r="B221" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C221">
         <v>56.31222222222222</v>
@@ -3626,7 +3629,7 @@
         <v>20</v>
       </c>
       <c r="B222" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C222">
         <v>84.56361111111111</v>
@@ -3640,7 +3643,7 @@
         <v>21</v>
       </c>
       <c r="B223" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C223">
         <v>8.219722222222222</v>
@@ -3654,7 +3657,7 @@
         <v>21</v>
       </c>
       <c r="B224" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C224">
         <v>8.219722222222222</v>
@@ -3668,7 +3671,7 @@
         <v>21</v>
       </c>
       <c r="B225" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C225">
         <v>6.753333333333333</v>
@@ -3682,7 +3685,7 @@
         <v>21</v>
       </c>
       <c r="B226" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C226">
         <v>2.571388888888889</v>
@@ -3696,7 +3699,7 @@
         <v>21</v>
       </c>
       <c r="B227" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C227">
         <v>3.683611111111111</v>
@@ -3710,7 +3713,7 @@
         <v>21</v>
       </c>
       <c r="B228" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C228">
         <v>8.631388888888889</v>
@@ -3724,7 +3727,7 @@
         <v>21</v>
       </c>
       <c r="B229" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C229">
         <v>9.331111111111111</v>
@@ -3738,7 +3741,7 @@
         <v>21</v>
       </c>
       <c r="B230" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C230">
         <v>8.256388888888889</v>
@@ -3752,7 +3755,7 @@
         <v>21</v>
       </c>
       <c r="B231" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C231">
         <v>8.641111111111112</v>
@@ -3766,7 +3769,7 @@
         <v>21</v>
       </c>
       <c r="B232" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C232">
         <v>4.804166666666666</v>
@@ -3780,7 +3783,7 @@
         <v>21</v>
       </c>
       <c r="B233" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C233">
         <v>5.882777777777778</v>
@@ -3794,7 +3797,7 @@
         <v>21</v>
       </c>
       <c r="B234" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C234">
         <v>6.680555555555555</v>
@@ -3808,7 +3811,7 @@
         <v>21</v>
       </c>
       <c r="B235" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C235">
         <v>7.816111111111111</v>
@@ -3822,7 +3825,7 @@
         <v>22</v>
       </c>
       <c r="B236" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C236">
         <v>0.5022222222222222</v>
@@ -3836,7 +3839,7 @@
         <v>22</v>
       </c>
       <c r="B237" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C237">
         <v>2.0825</v>
@@ -3850,7 +3853,7 @@
         <v>22</v>
       </c>
       <c r="B238" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C238">
         <v>1.555833333333333</v>
@@ -3864,7 +3867,7 @@
         <v>22</v>
       </c>
       <c r="B239" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C239">
         <v>1.188333333333333</v>
@@ -3878,7 +3881,7 @@
         <v>22</v>
       </c>
       <c r="B240" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C240">
         <v>0.6247222222222222</v>
@@ -3892,7 +3895,7 @@
         <v>22</v>
       </c>
       <c r="B241" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C241">
         <v>0.6491666666666667</v>
@@ -3906,7 +3909,7 @@
         <v>22</v>
       </c>
       <c r="B242" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C242">
         <v>0.6875</v>
@@ -3920,7 +3923,7 @@
         <v>22</v>
       </c>
       <c r="B243" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C243">
         <v>0.5686111111111111</v>
@@ -3934,7 +3937,7 @@
         <v>22</v>
       </c>
       <c r="B244" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C244">
         <v>0.6036111111111111</v>
@@ -3948,7 +3951,7 @@
         <v>22</v>
       </c>
       <c r="B245" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C245">
         <v>0.2116666666666667</v>
@@ -3962,7 +3965,7 @@
         <v>22</v>
       </c>
       <c r="B246" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C246">
         <v>0.5252777777777777</v>
@@ -3976,7 +3979,7 @@
         <v>22</v>
       </c>
       <c r="B247" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C247">
         <v>0.7352777777777778</v>
@@ -3990,7 +3993,7 @@
         <v>22</v>
       </c>
       <c r="B248" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C248">
         <v>1.201944444444444</v>
@@ -4004,13 +4007,13 @@
         <v>23</v>
       </c>
       <c r="B249" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C249">
-        <v>17.65277777777778</v>
+        <v>0.2058333333333333</v>
       </c>
       <c r="D249">
-        <v>10.85694444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4018,13 +4021,13 @@
         <v>23</v>
       </c>
       <c r="B250" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C250">
-        <v>18.68194444444444</v>
+        <v>0.2791666666666667</v>
       </c>
       <c r="D250">
-        <v>10.91361111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4032,13 +4035,13 @@
         <v>23</v>
       </c>
       <c r="B251" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C251">
-        <v>19.55166666666667</v>
+        <v>0.25</v>
       </c>
       <c r="D251">
-        <v>9.529722222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4046,13 +4049,13 @@
         <v>23</v>
       </c>
       <c r="B252" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C252">
-        <v>21.23</v>
+        <v>0.2522222222222222</v>
       </c>
       <c r="D252">
-        <v>9.654722222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4060,13 +4063,13 @@
         <v>23</v>
       </c>
       <c r="B253" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C253">
-        <v>22.94472222222222</v>
+        <v>0.245</v>
       </c>
       <c r="D253">
-        <v>9.976944444444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4074,13 +4077,13 @@
         <v>23</v>
       </c>
       <c r="B254" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C254">
-        <v>24.23111111111111</v>
+        <v>0.2475</v>
       </c>
       <c r="D254">
-        <v>10.50805555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4088,13 +4091,13 @@
         <v>23</v>
       </c>
       <c r="B255" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C255">
-        <v>26.40277777777778</v>
+        <v>0.25</v>
       </c>
       <c r="D255">
-        <v>9.323611111111111</v>
+        <v>0.1738888888888889</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4102,13 +4105,13 @@
         <v>23</v>
       </c>
       <c r="B256" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C256">
-        <v>27.37805555555556</v>
+        <v>0.2744444444444444</v>
       </c>
       <c r="D256">
-        <v>8.24</v>
+        <v>0.1794444444444444</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4116,13 +4119,13 @@
         <v>23</v>
       </c>
       <c r="B257" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C257">
-        <v>27.88138888888889</v>
+        <v>0.2486111111111111</v>
       </c>
       <c r="D257">
-        <v>9.262499999999999</v>
+        <v>0.2019444444444445</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4130,13 +4133,13 @@
         <v>23</v>
       </c>
       <c r="B258" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C258">
-        <v>11.13083333333333</v>
+        <v>0.1469444444444444</v>
       </c>
       <c r="D258">
-        <v>1.836944444444444</v>
+        <v>0.2019444444444445</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4144,13 +4147,13 @@
         <v>23</v>
       </c>
       <c r="B259" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C259">
-        <v>17.93277777777778</v>
+        <v>0.2044444444444445</v>
       </c>
       <c r="D259">
-        <v>4.953611111111111</v>
+        <v>0.2019444444444445</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4158,13 +4161,13 @@
         <v>23</v>
       </c>
       <c r="B260" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C260">
-        <v>26.82333333333333</v>
+        <v>0.2191666666666667</v>
       </c>
       <c r="D260">
-        <v>6.8</v>
+        <v>0.2233333333333333</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4172,13 +4175,13 @@
         <v>23</v>
       </c>
       <c r="B261" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C261">
-        <v>28.36694444444445</v>
+        <v>0.1605555555555556</v>
       </c>
       <c r="D261">
-        <v>6.111388888888889</v>
+        <v>0.2355555555555555</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4186,13 +4189,13 @@
         <v>24</v>
       </c>
       <c r="B262" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C262">
-        <v>6.602777777777778</v>
+        <v>17.65277777777778</v>
       </c>
       <c r="D262">
-        <v>1.554166666666667</v>
+        <v>10.85694444444444</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4200,13 +4203,13 @@
         <v>24</v>
       </c>
       <c r="B263" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C263">
-        <v>5.928888888888889</v>
+        <v>18.68194444444444</v>
       </c>
       <c r="D263">
-        <v>1.554166666666667</v>
+        <v>10.91361111111111</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4214,13 +4217,13 @@
         <v>24</v>
       </c>
       <c r="B264" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C264">
-        <v>6.749722222222222</v>
+        <v>19.55166666666667</v>
       </c>
       <c r="D264">
-        <v>1.554166666666667</v>
+        <v>9.529722222222222</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4228,13 +4231,13 @@
         <v>24</v>
       </c>
       <c r="B265" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C265">
-        <v>7.423611111111111</v>
+        <v>21.23</v>
       </c>
       <c r="D265">
-        <v>1.554166666666667</v>
+        <v>9.654722222222222</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4242,13 +4245,13 @@
         <v>24</v>
       </c>
       <c r="B266" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C266">
-        <v>7.7175</v>
+        <v>22.94472222222222</v>
       </c>
       <c r="D266">
-        <v>1.554166666666667</v>
+        <v>9.976944444444445</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4256,13 +4259,13 @@
         <v>24</v>
       </c>
       <c r="B267" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C267">
-        <v>7.864444444444445</v>
+        <v>24.23111111111111</v>
       </c>
       <c r="D267">
-        <v>1.554166666666667</v>
+        <v>10.50805555555556</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4270,13 +4273,13 @@
         <v>24</v>
       </c>
       <c r="B268" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C268">
-        <v>8.305555555555555</v>
+        <v>26.40277777777778</v>
       </c>
       <c r="D268">
-        <v>1.557222222222222</v>
+        <v>9.323611111111111</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4284,13 +4287,13 @@
         <v>24</v>
       </c>
       <c r="B269" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C269">
-        <v>8.989722222222222</v>
+        <v>27.37805555555556</v>
       </c>
       <c r="D269">
-        <v>1.557222222222222</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4298,13 +4301,13 @@
         <v>24</v>
       </c>
       <c r="B270" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C270">
-        <v>9.484722222222222</v>
+        <v>27.88138888888889</v>
       </c>
       <c r="D270">
-        <v>1.563055555555556</v>
+        <v>9.262499999999999</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4312,13 +4315,13 @@
         <v>24</v>
       </c>
       <c r="B271" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C271">
-        <v>3.410833333333333</v>
+        <v>11.13083333333333</v>
       </c>
       <c r="D271">
-        <v>1.563055555555556</v>
+        <v>1.836944444444444</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4326,13 +4329,13 @@
         <v>24</v>
       </c>
       <c r="B272" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C272">
-        <v>4.5975</v>
+        <v>17.93277777777778</v>
       </c>
       <c r="D272">
-        <v>1.563055555555556</v>
+        <v>4.953611111111111</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4340,13 +4343,13 @@
         <v>24</v>
       </c>
       <c r="B273" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C273">
-        <v>7.714444444444444</v>
+        <v>26.82333333333333</v>
       </c>
       <c r="D273">
-        <v>1.563055555555556</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4354,13 +4357,13 @@
         <v>24</v>
       </c>
       <c r="B274" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C274">
-        <v>9.737222222222222</v>
+        <v>28.36694444444445</v>
       </c>
       <c r="D274">
-        <v>1.563055555555556</v>
+        <v>6.111388888888889</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4368,13 +4371,13 @@
         <v>25</v>
       </c>
       <c r="B275" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C275">
-        <v>0.1225</v>
+        <v>6.602777777777778</v>
       </c>
       <c r="D275">
-        <v>0.05388888888888889</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4382,13 +4385,13 @@
         <v>25</v>
       </c>
       <c r="B276" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C276">
-        <v>0.5197222222222222</v>
+        <v>5.928888888888889</v>
       </c>
       <c r="D276">
-        <v>0.09888888888888889</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4396,13 +4399,13 @@
         <v>25</v>
       </c>
       <c r="B277" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C277">
-        <v>0.2697222222222222</v>
+        <v>6.749722222222222</v>
       </c>
       <c r="D277">
-        <v>0.1908333333333333</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4410,13 +4413,13 @@
         <v>25</v>
       </c>
       <c r="B278" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C278">
-        <v>0.2697222222222222</v>
+        <v>7.423611111111111</v>
       </c>
       <c r="D278">
-        <v>0.2233333333333333</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4424,13 +4427,13 @@
         <v>25</v>
       </c>
       <c r="B279" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C279">
-        <v>0.9066666666666666</v>
+        <v>7.7175</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4438,13 +4441,13 @@
         <v>25</v>
       </c>
       <c r="B280" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C280">
-        <v>0.7719444444444444</v>
+        <v>7.864444444444445</v>
       </c>
       <c r="D280">
-        <v>0</v>
+        <v>1.554166666666667</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4452,13 +4455,13 @@
         <v>25</v>
       </c>
       <c r="B281" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C281">
-        <v>0.3597222222222222</v>
+        <v>8.305555555555555</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>1.557222222222222</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4466,13 +4469,13 @@
         <v>25</v>
       </c>
       <c r="B282" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C282">
-        <v>0.985</v>
+        <v>8.989722222222222</v>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>1.557222222222222</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4480,13 +4483,13 @@
         <v>25</v>
       </c>
       <c r="B283" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C283">
-        <v>1.001944444444445</v>
+        <v>9.484722222222222</v>
       </c>
       <c r="D283">
-        <v>0</v>
+        <v>1.563055555555556</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4494,13 +4497,13 @@
         <v>25</v>
       </c>
       <c r="B284" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C284">
-        <v>1.029166666666667</v>
+        <v>3.410833333333333</v>
       </c>
       <c r="D284">
-        <v>0</v>
+        <v>1.563055555555556</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4508,13 +4511,13 @@
         <v>25</v>
       </c>
       <c r="B285" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C285">
-        <v>1.153055555555556</v>
+        <v>4.5975</v>
       </c>
       <c r="D285">
-        <v>0</v>
+        <v>1.563055555555556</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4522,13 +4525,13 @@
         <v>25</v>
       </c>
       <c r="B286" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C286">
-        <v>1.204166666666667</v>
+        <v>7.714444444444444</v>
       </c>
       <c r="D286">
-        <v>0</v>
+        <v>1.563055555555556</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4536,13 +4539,13 @@
         <v>25</v>
       </c>
       <c r="B287" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C287">
-        <v>1.254166666666667</v>
+        <v>9.737222222222222</v>
       </c>
       <c r="D287">
-        <v>0</v>
+        <v>1.563055555555556</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4550,13 +4553,13 @@
         <v>26</v>
       </c>
       <c r="B288" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C288">
-        <v>4.703888888888889</v>
+        <v>0.1225</v>
       </c>
       <c r="D288">
-        <v>4.578333333333333</v>
+        <v>0.05388888888888889</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4564,13 +4567,13 @@
         <v>26</v>
       </c>
       <c r="B289" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C289">
-        <v>4.998055555555555</v>
+        <v>0.5197222222222222</v>
       </c>
       <c r="D289">
-        <v>4.624166666666667</v>
+        <v>0.09888888888888889</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4578,13 +4581,13 @@
         <v>26</v>
       </c>
       <c r="B290" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C290">
-        <v>4.152777777777778</v>
+        <v>0.2697222222222222</v>
       </c>
       <c r="D290">
-        <v>4.246388888888889</v>
+        <v>0.1908333333333333</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4592,13 +4595,13 @@
         <v>26</v>
       </c>
       <c r="B291" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C291">
-        <v>3.699444444444445</v>
+        <v>0.2697222222222222</v>
       </c>
       <c r="D291">
-        <v>4.315277777777778</v>
+        <v>0.2233333333333333</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4606,13 +4609,13 @@
         <v>26</v>
       </c>
       <c r="B292" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C292">
-        <v>4.152777777777778</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="D292">
-        <v>4.292222222222223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4620,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="B293" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C293">
-        <v>5.193888888888889</v>
+        <v>0.7719444444444444</v>
       </c>
       <c r="D293">
-        <v>3.5825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4634,13 +4637,13 @@
         <v>26</v>
       </c>
       <c r="B294" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C294">
-        <v>6.183611111111111</v>
+        <v>0.3597222222222222</v>
       </c>
       <c r="D294">
-        <v>3.608888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4648,13 +4651,13 @@
         <v>26</v>
       </c>
       <c r="B295" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C295">
-        <v>7.9675</v>
+        <v>0.985</v>
       </c>
       <c r="D295">
-        <v>3.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4662,13 +4665,13 @@
         <v>26</v>
       </c>
       <c r="B296" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C296">
-        <v>7.991944444444444</v>
+        <v>1.001944444444445</v>
       </c>
       <c r="D296">
-        <v>3.926388888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4676,13 +4679,13 @@
         <v>26</v>
       </c>
       <c r="B297" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C297">
-        <v>3.724722222222222</v>
+        <v>1.029166666666667</v>
       </c>
       <c r="D297">
-        <v>2.944166666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4690,13 +4693,13 @@
         <v>26</v>
       </c>
       <c r="B298" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C298">
-        <v>5.591666666666667</v>
+        <v>1.153055555555556</v>
       </c>
       <c r="D298">
-        <v>2.443888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4704,13 +4707,13 @@
         <v>26</v>
       </c>
       <c r="B299" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C299">
-        <v>7.243055555555555</v>
+        <v>1.204166666666667</v>
       </c>
       <c r="D299">
-        <v>2.177222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -4718,13 +4721,13 @@
         <v>26</v>
       </c>
       <c r="B300" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C300">
-        <v>7.11</v>
+        <v>1.254166666666667</v>
       </c>
       <c r="D300">
-        <v>2.445277777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4732,13 +4735,13 @@
         <v>27</v>
       </c>
       <c r="B301" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C301">
-        <v>9.224166666666667</v>
+        <v>4.703888888888889</v>
       </c>
       <c r="D301">
-        <v>1.930277777777778</v>
+        <v>4.578333333333333</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4746,13 +4749,13 @@
         <v>27</v>
       </c>
       <c r="B302" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C302">
-        <v>8.097222222222221</v>
+        <v>4.998055555555555</v>
       </c>
       <c r="D302">
-        <v>2.423888888888889</v>
+        <v>4.624166666666667</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4760,13 +4763,13 @@
         <v>27</v>
       </c>
       <c r="B303" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C303">
-        <v>8.834722222222222</v>
+        <v>4.152777777777778</v>
       </c>
       <c r="D303">
-        <v>0</v>
+        <v>4.246388888888889</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4774,13 +4777,13 @@
         <v>27</v>
       </c>
       <c r="B304" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C304">
-        <v>9.811111111111112</v>
+        <v>3.699444444444445</v>
       </c>
       <c r="D304">
-        <v>0</v>
+        <v>4.315277777777778</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4788,13 +4791,13 @@
         <v>27</v>
       </c>
       <c r="B305" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C305">
-        <v>10.28638888888889</v>
+        <v>4.152777777777778</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>4.292222222222223</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -4802,13 +4805,13 @@
         <v>27</v>
       </c>
       <c r="B306" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C306">
-        <v>11.6375</v>
+        <v>5.193888888888889</v>
       </c>
       <c r="D306">
-        <v>0</v>
+        <v>3.5825</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -4816,13 +4819,13 @@
         <v>27</v>
       </c>
       <c r="B307" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C307">
-        <v>8.300555555555556</v>
+        <v>6.183611111111111</v>
       </c>
       <c r="D307">
-        <v>0</v>
+        <v>3.608888888888889</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -4830,13 +4833,13 @@
         <v>27</v>
       </c>
       <c r="B308" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C308">
-        <v>8.294166666666667</v>
+        <v>7.9675</v>
       </c>
       <c r="D308">
-        <v>5.326111111111111</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4844,13 +4847,13 @@
         <v>27</v>
       </c>
       <c r="B309" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C309">
-        <v>8.652222222222223</v>
+        <v>7.991944444444444</v>
       </c>
       <c r="D309">
-        <v>4.897222222222222</v>
+        <v>3.926388888888889</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4858,13 +4861,13 @@
         <v>27</v>
       </c>
       <c r="B310" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C310">
-        <v>3.089444444444445</v>
+        <v>3.724722222222222</v>
       </c>
       <c r="D310">
-        <v>2.796111111111111</v>
+        <v>2.944166666666667</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4872,13 +4875,13 @@
         <v>27</v>
       </c>
       <c r="B311" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C311">
-        <v>3.726666666666667</v>
+        <v>5.591666666666667</v>
       </c>
       <c r="D311">
-        <v>3.046388888888889</v>
+        <v>2.443888888888889</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -4886,13 +4889,13 @@
         <v>27</v>
       </c>
       <c r="B312" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C312">
-        <v>5.495277777777778</v>
+        <v>7.243055555555555</v>
       </c>
       <c r="D312">
-        <v>2.928611111111111</v>
+        <v>2.177222222222222</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -4900,13 +4903,13 @@
         <v>27</v>
       </c>
       <c r="B313" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C313">
-        <v>6.546111111111111</v>
+        <v>7.11</v>
       </c>
       <c r="D313">
-        <v>1.485555555555556</v>
+        <v>2.445277777777778</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -4914,13 +4917,13 @@
         <v>28</v>
       </c>
       <c r="B314" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C314">
-        <v>0.6002777777777778</v>
+        <v>9.224166666666667</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>1.930277777777778</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4928,13 +4931,13 @@
         <v>28</v>
       </c>
       <c r="B315" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C315">
-        <v>0.5758333333333333</v>
+        <v>8.097222222222221</v>
       </c>
       <c r="D315">
-        <v>0</v>
+        <v>2.423888888888889</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4942,10 +4945,10 @@
         <v>28</v>
       </c>
       <c r="B316" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C316">
-        <v>0.5266666666666666</v>
+        <v>8.834722222222222</v>
       </c>
       <c r="D316">
         <v>0</v>
@@ -4956,10 +4959,10 @@
         <v>28</v>
       </c>
       <c r="B317" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C317">
-        <v>0.49</v>
+        <v>9.811111111111112</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -4970,10 +4973,10 @@
         <v>28</v>
       </c>
       <c r="B318" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C318">
-        <v>0.6125</v>
+        <v>10.28638888888889</v>
       </c>
       <c r="D318">
         <v>0</v>
@@ -4984,10 +4987,10 @@
         <v>28</v>
       </c>
       <c r="B319" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C319">
-        <v>0.5022222222222222</v>
+        <v>11.6375</v>
       </c>
       <c r="D319">
         <v>0</v>
@@ -4998,10 +5001,10 @@
         <v>28</v>
       </c>
       <c r="B320" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C320">
-        <v>0.3841666666666667</v>
+        <v>8.300555555555556</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -5012,13 +5015,13 @@
         <v>28</v>
       </c>
       <c r="B321" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C321">
-        <v>0.3858333333333333</v>
+        <v>8.294166666666667</v>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>5.326111111111111</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5026,13 +5029,13 @@
         <v>28</v>
       </c>
       <c r="B322" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C322">
-        <v>0.2163888888888889</v>
+        <v>8.652222222222223</v>
       </c>
       <c r="D322">
-        <v>0</v>
+        <v>4.897222222222222</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5040,13 +5043,13 @@
         <v>28</v>
       </c>
       <c r="B323" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C323">
-        <v>0.2619444444444444</v>
+        <v>3.089444444444445</v>
       </c>
       <c r="D323">
-        <v>0</v>
+        <v>2.796111111111111</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5054,13 +5057,13 @@
         <v>28</v>
       </c>
       <c r="B324" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C324">
-        <v>0.2669444444444444</v>
+        <v>3.726666666666667</v>
       </c>
       <c r="D324">
-        <v>0</v>
+        <v>3.046388888888889</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5068,13 +5071,13 @@
         <v>28</v>
       </c>
       <c r="B325" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C325">
-        <v>0.3594444444444445</v>
+        <v>5.495277777777778</v>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>2.928611111111111</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5082,13 +5085,13 @@
         <v>28</v>
       </c>
       <c r="B326" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C326">
-        <v>0.3875</v>
+        <v>6.546111111111111</v>
       </c>
       <c r="D326">
-        <v>0</v>
+        <v>1.485555555555556</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5096,13 +5099,13 @@
         <v>29</v>
       </c>
       <c r="B327" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C327">
-        <v>76.64833333333333</v>
+        <v>0.6002777777777778</v>
       </c>
       <c r="D327">
-        <v>35.11305555555555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5110,13 +5113,13 @@
         <v>29</v>
       </c>
       <c r="B328" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C328">
-        <v>80.90861111111111</v>
+        <v>0.5758333333333333</v>
       </c>
       <c r="D328">
-        <v>43.24305555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5124,13 +5127,13 @@
         <v>29</v>
       </c>
       <c r="B329" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C329">
-        <v>74.14472222222223</v>
+        <v>0.5266666666666666</v>
       </c>
       <c r="D329">
-        <v>59.66194444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5138,13 +5141,13 @@
         <v>29</v>
       </c>
       <c r="B330" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C330">
-        <v>68.93722222222222</v>
+        <v>0.49</v>
       </c>
       <c r="D330">
-        <v>179.4602777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5152,13 +5155,13 @@
         <v>29</v>
       </c>
       <c r="B331" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C331">
-        <v>61.8075</v>
+        <v>0.6125</v>
       </c>
       <c r="D331">
-        <v>201.7544444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5166,13 +5169,13 @@
         <v>29</v>
       </c>
       <c r="B332" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C332">
-        <v>59.50416666666667</v>
+        <v>0.5022222222222222</v>
       </c>
       <c r="D332">
-        <v>192.0925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5180,13 +5183,13 @@
         <v>29</v>
       </c>
       <c r="B333" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C333">
-        <v>66.14611111111111</v>
+        <v>0.3841666666666667</v>
       </c>
       <c r="D333">
-        <v>202.5288888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5194,13 +5197,13 @@
         <v>29</v>
       </c>
       <c r="B334" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C334">
-        <v>68.33222222222223</v>
+        <v>0.3858333333333333</v>
       </c>
       <c r="D334">
-        <v>138.0383333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5208,13 +5211,13 @@
         <v>29</v>
       </c>
       <c r="B335" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C335">
-        <v>39.34722222222222</v>
+        <v>0.2163888888888889</v>
       </c>
       <c r="D335">
-        <v>126.8880555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5222,13 +5225,13 @@
         <v>29</v>
       </c>
       <c r="B336" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C336">
-        <v>16.48944444444444</v>
+        <v>0.2619444444444444</v>
       </c>
       <c r="D336">
-        <v>79.93972222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5236,13 +5239,13 @@
         <v>29</v>
       </c>
       <c r="B337" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C337">
-        <v>20.13666666666667</v>
+        <v>0.2669444444444444</v>
       </c>
       <c r="D337">
-        <v>70.97750000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5250,13 +5253,13 @@
         <v>29</v>
       </c>
       <c r="B338" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C338">
-        <v>18.49861111111111</v>
+        <v>0.3594444444444445</v>
       </c>
       <c r="D338">
-        <v>77.7475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5264,13 +5267,13 @@
         <v>29</v>
       </c>
       <c r="B339" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C339">
-        <v>22.11</v>
+        <v>0.3875</v>
       </c>
       <c r="D339">
-        <v>81.71250000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5278,13 +5281,13 @@
         <v>30</v>
       </c>
       <c r="B340" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C340">
-        <v>24.61027777777778</v>
+        <v>76.64833333333333</v>
       </c>
       <c r="D340">
-        <v>35.88861111111111</v>
+        <v>35.11305555555555</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5292,13 +5295,13 @@
         <v>30</v>
       </c>
       <c r="B341" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C341">
-        <v>25.49222222222222</v>
+        <v>80.90861111111111</v>
       </c>
       <c r="D341">
-        <v>37.95361111111111</v>
+        <v>43.24305555555556</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5306,13 +5309,13 @@
         <v>30</v>
       </c>
       <c r="B342" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C342">
-        <v>22.89527777777778</v>
+        <v>74.14472222222223</v>
       </c>
       <c r="D342">
-        <v>38.425</v>
+        <v>59.66194444444444</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5320,13 +5323,13 @@
         <v>30</v>
       </c>
       <c r="B343" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C343">
-        <v>28.10138888888889</v>
+        <v>68.93722222222222</v>
       </c>
       <c r="D343">
-        <v>36.18055555555556</v>
+        <v>179.4602777777778</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5334,13 +5337,13 @@
         <v>30</v>
       </c>
       <c r="B344" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C344">
-        <v>32.31555555555556</v>
+        <v>61.8075</v>
       </c>
       <c r="D344">
-        <v>35.67555555555555</v>
+        <v>201.7544444444444</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5348,13 +5351,13 @@
         <v>30</v>
       </c>
       <c r="B345" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C345">
-        <v>34.33666666666667</v>
+        <v>59.50416666666667</v>
       </c>
       <c r="D345">
-        <v>38.75027777777778</v>
+        <v>192.0925</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5362,13 +5365,13 @@
         <v>30</v>
       </c>
       <c r="B346" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C346">
-        <v>38.72222222222222</v>
+        <v>66.14611111111111</v>
       </c>
       <c r="D346">
-        <v>37.31388888888889</v>
+        <v>202.5288888888889</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5376,13 +5379,13 @@
         <v>30</v>
       </c>
       <c r="B347" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C347">
-        <v>41.90722222222222</v>
+        <v>68.33222222222223</v>
       </c>
       <c r="D347">
-        <v>39.47972222222222</v>
+        <v>138.0383333333333</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5390,13 +5393,13 @@
         <v>30</v>
       </c>
       <c r="B348" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C348">
-        <v>41.30694444444445</v>
+        <v>39.34722222222222</v>
       </c>
       <c r="D348">
-        <v>37.68944444444445</v>
+        <v>126.8880555555556</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5404,13 +5407,13 @@
         <v>30</v>
       </c>
       <c r="B349" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C349">
-        <v>13.3525</v>
+        <v>16.48944444444444</v>
       </c>
       <c r="D349">
-        <v>30.76</v>
+        <v>79.93972222222222</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5418,13 +5421,13 @@
         <v>30</v>
       </c>
       <c r="B350" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C350">
-        <v>13.00944444444444</v>
+        <v>20.13666666666667</v>
       </c>
       <c r="D350">
-        <v>33.3525</v>
+        <v>70.97750000000001</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5432,13 +5435,13 @@
         <v>30</v>
       </c>
       <c r="B351" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C351">
-        <v>32.64777777777778</v>
+        <v>18.49861111111111</v>
       </c>
       <c r="D351">
-        <v>39.43222222222222</v>
+        <v>77.7475</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5446,13 +5449,13 @@
         <v>30</v>
       </c>
       <c r="B352" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C352">
-        <v>43.29</v>
+        <v>22.11</v>
       </c>
       <c r="D352">
-        <v>39.13472222222222</v>
+        <v>81.71250000000001</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5460,13 +5463,13 @@
         <v>31</v>
       </c>
       <c r="B353" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C353">
-        <v>18.31416666666667</v>
+        <v>24.61027777777778</v>
       </c>
       <c r="D353">
-        <v>36.465</v>
+        <v>35.88861111111111</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5474,13 +5477,13 @@
         <v>31</v>
       </c>
       <c r="B354" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C354">
-        <v>17.65277777777778</v>
+        <v>25.49222222222222</v>
       </c>
       <c r="D354">
-        <v>37.33111111111111</v>
+        <v>37.95361111111111</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5488,13 +5491,13 @@
         <v>31</v>
       </c>
       <c r="B355" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C355">
-        <v>17.00361111111111</v>
+        <v>22.89527777777778</v>
       </c>
       <c r="D355">
-        <v>38.26694444444445</v>
+        <v>38.425</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5502,13 +5505,13 @@
         <v>31</v>
       </c>
       <c r="B356" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C356">
-        <v>16.57472222222222</v>
+        <v>28.10138888888889</v>
       </c>
       <c r="D356">
-        <v>38.80944444444444</v>
+        <v>36.18055555555556</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5516,13 +5519,13 @@
         <v>31</v>
       </c>
       <c r="B357" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C357">
-        <v>17.56694444444445</v>
+        <v>32.31555555555556</v>
       </c>
       <c r="D357">
-        <v>39.31777777777778</v>
+        <v>35.67555555555555</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5530,13 +5533,13 @@
         <v>31</v>
       </c>
       <c r="B358" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C358">
-        <v>19.88861111111111</v>
+        <v>34.33666666666667</v>
       </c>
       <c r="D358">
-        <v>18.66916666666667</v>
+        <v>38.75027777777778</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5544,13 +5547,13 @@
         <v>31</v>
       </c>
       <c r="B359" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C359">
-        <v>23.93416666666667</v>
+        <v>38.72222222222222</v>
       </c>
       <c r="D359">
-        <v>8.970277777777778</v>
+        <v>37.31388888888889</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5558,13 +5561,13 @@
         <v>31</v>
       </c>
       <c r="B360" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C360">
-        <v>19.43472222222222</v>
+        <v>41.90722222222222</v>
       </c>
       <c r="D360">
-        <v>34.5775</v>
+        <v>39.47972222222222</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5572,13 +5575,13 @@
         <v>31</v>
       </c>
       <c r="B361" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C361">
-        <v>17.78583333333333</v>
+        <v>41.30694444444445</v>
       </c>
       <c r="D361">
-        <v>34.6675</v>
+        <v>37.68944444444445</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5586,13 +5589,13 @@
         <v>31</v>
       </c>
       <c r="B362" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C362">
-        <v>7.890833333333333</v>
+        <v>13.3525</v>
       </c>
       <c r="D362">
-        <v>32.53166666666667</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5600,13 +5603,13 @@
         <v>31</v>
       </c>
       <c r="B363" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C363">
-        <v>6.443611111111111</v>
+        <v>13.00944444444444</v>
       </c>
       <c r="D363">
-        <v>28.02888888888889</v>
+        <v>33.3525</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -5614,13 +5617,13 @@
         <v>31</v>
       </c>
       <c r="B364" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C364">
-        <v>9.902222222222223</v>
+        <v>32.64777777777778</v>
       </c>
       <c r="D364">
-        <v>27.18833333333333</v>
+        <v>39.43222222222222</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5628,13 +5631,13 @@
         <v>31</v>
       </c>
       <c r="B365" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C365">
-        <v>12.71777777777778</v>
+        <v>43.29</v>
       </c>
       <c r="D365">
-        <v>27.185</v>
+        <v>39.13472222222222</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5642,13 +5645,13 @@
         <v>32</v>
       </c>
       <c r="B366" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C366">
-        <v>46.64805555555556</v>
+        <v>18.31416666666667</v>
       </c>
       <c r="D366">
-        <v>97.20166666666667</v>
+        <v>36.465</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5656,13 +5659,13 @@
         <v>32</v>
       </c>
       <c r="B367" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C367">
-        <v>46.6725</v>
+        <v>17.65277777777778</v>
       </c>
       <c r="D367">
-        <v>94.59722222222223</v>
+        <v>37.33111111111111</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5670,13 +5673,13 @@
         <v>32</v>
       </c>
       <c r="B368" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C368">
-        <v>49.28166666666667</v>
+        <v>17.00361111111111</v>
       </c>
       <c r="D368">
-        <v>92.50444444444445</v>
+        <v>38.26694444444445</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -5684,13 +5687,13 @@
         <v>32</v>
       </c>
       <c r="B369" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C369">
-        <v>49.40416666666667</v>
+        <v>16.57472222222222</v>
       </c>
       <c r="D369">
-        <v>94.10916666666667</v>
+        <v>38.80944444444444</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -5698,13 +5701,13 @@
         <v>32</v>
       </c>
       <c r="B370" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C370">
-        <v>50.78861111111111</v>
+        <v>17.56694444444445</v>
       </c>
       <c r="D370">
-        <v>104.9333333333333</v>
+        <v>39.31777777777778</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5712,13 +5715,13 @@
         <v>32</v>
       </c>
       <c r="B371" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C371">
-        <v>56.74194444444444</v>
+        <v>19.88861111111111</v>
       </c>
       <c r="D371">
-        <v>117.3113888888889</v>
+        <v>18.66916666666667</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -5726,13 +5729,13 @@
         <v>32</v>
       </c>
       <c r="B372" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C372">
-        <v>58.08944444444445</v>
+        <v>23.93416666666667</v>
       </c>
       <c r="D372">
-        <v>113.5002777777778</v>
+        <v>8.970277777777778</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -5740,13 +5743,13 @@
         <v>32</v>
       </c>
       <c r="B373" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C373">
-        <v>61.20111111111111</v>
+        <v>19.43472222222222</v>
       </c>
       <c r="D373">
-        <v>106.0505555555556</v>
+        <v>34.5775</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -5754,13 +5757,13 @@
         <v>32</v>
       </c>
       <c r="B374" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C374">
-        <v>64.92472222222223</v>
+        <v>17.78583333333333</v>
       </c>
       <c r="D374">
-        <v>92.80416666666666</v>
+        <v>34.6675</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -5768,13 +5771,13 @@
         <v>32</v>
       </c>
       <c r="B375" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C375">
-        <v>34.68694444444444</v>
+        <v>7.890833333333333</v>
       </c>
       <c r="D375">
-        <v>111.2963888888889</v>
+        <v>32.53166666666667</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -5782,13 +5785,13 @@
         <v>32</v>
       </c>
       <c r="B376" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C376">
-        <v>30.58861111111111</v>
+        <v>6.443611111111111</v>
       </c>
       <c r="D376">
-        <v>117.7855555555556</v>
+        <v>28.02888888888889</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5796,13 +5799,13 @@
         <v>32</v>
       </c>
       <c r="B377" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C377">
-        <v>38.38694444444445</v>
+        <v>9.902222222222223</v>
       </c>
       <c r="D377">
-        <v>129.37</v>
+        <v>27.18833333333333</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5810,13 +5813,13 @@
         <v>32</v>
       </c>
       <c r="B378" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C378">
-        <v>62.20138888888889</v>
+        <v>12.71777777777778</v>
       </c>
       <c r="D378">
-        <v>120.4041666666667</v>
+        <v>27.185</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5824,13 +5827,13 @@
         <v>33</v>
       </c>
       <c r="B379" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C379">
-        <v>1.176111111111111</v>
+        <v>46.64805555555556</v>
       </c>
       <c r="D379">
-        <v>0.1908333333333333</v>
+        <v>97.20166666666667</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5838,13 +5841,13 @@
         <v>33</v>
       </c>
       <c r="B380" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C380">
-        <v>1.212777777777778</v>
+        <v>46.6725</v>
       </c>
       <c r="D380">
-        <v>0.2805555555555556</v>
+        <v>94.59722222222223</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5852,13 +5855,13 @@
         <v>33</v>
       </c>
       <c r="B381" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C381">
-        <v>1.176111111111111</v>
+        <v>49.28166666666667</v>
       </c>
       <c r="D381">
-        <v>0.2133333333333333</v>
+        <v>92.50444444444445</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5866,13 +5869,13 @@
         <v>33</v>
       </c>
       <c r="B382" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C382">
-        <v>1.273888888888889</v>
+        <v>49.40416666666667</v>
       </c>
       <c r="D382">
-        <v>0.2580555555555555</v>
+        <v>94.10916666666667</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5880,13 +5883,13 @@
         <v>33</v>
       </c>
       <c r="B383" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C383">
-        <v>1.273888888888889</v>
+        <v>50.78861111111111</v>
       </c>
       <c r="D383">
-        <v>0.2244444444444444</v>
+        <v>104.9333333333333</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -5894,13 +5897,13 @@
         <v>33</v>
       </c>
       <c r="B384" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C384">
-        <v>1.335277777777778</v>
+        <v>56.74194444444444</v>
       </c>
       <c r="D384">
-        <v>0.2244444444444444</v>
+        <v>117.3113888888889</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5908,13 +5911,13 @@
         <v>33</v>
       </c>
       <c r="B385" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C385">
-        <v>1.596388888888889</v>
+        <v>58.08944444444445</v>
       </c>
       <c r="D385">
-        <v>0.2244444444444444</v>
+        <v>113.5002777777778</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5922,13 +5925,13 @@
         <v>33</v>
       </c>
       <c r="B386" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C386">
-        <v>1.721111111111111</v>
+        <v>61.20111111111111</v>
       </c>
       <c r="D386">
-        <v>0.2355555555555555</v>
+        <v>106.0505555555556</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5936,13 +5939,13 @@
         <v>33</v>
       </c>
       <c r="B387" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C387">
-        <v>1.937777777777778</v>
+        <v>64.92472222222223</v>
       </c>
       <c r="D387">
-        <v>0.2469444444444444</v>
+        <v>92.80416666666666</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5950,13 +5953,13 @@
         <v>33</v>
       </c>
       <c r="B388" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C388">
-        <v>0.9813888888888889</v>
+        <v>34.68694444444444</v>
       </c>
       <c r="D388">
-        <v>0.2469444444444444</v>
+        <v>111.2963888888889</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5964,13 +5967,13 @@
         <v>33</v>
       </c>
       <c r="B389" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C389">
-        <v>1.290277777777778</v>
+        <v>30.58861111111111</v>
       </c>
       <c r="D389">
-        <v>0.2694444444444444</v>
+        <v>117.7855555555556</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5978,13 +5981,13 @@
         <v>33</v>
       </c>
       <c r="B390" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C390">
-        <v>1.577222222222222</v>
+        <v>38.38694444444445</v>
       </c>
       <c r="D390">
-        <v>0.3255555555555555</v>
+        <v>129.37</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5992,13 +5995,13 @@
         <v>33</v>
       </c>
       <c r="B391" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C391">
-        <v>1.848333333333333</v>
+        <v>62.20138888888889</v>
       </c>
       <c r="D391">
-        <v>0.3816666666666667</v>
+        <v>120.4041666666667</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6006,13 +6009,13 @@
         <v>34</v>
       </c>
       <c r="B392" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C392">
-        <v>2.866388888888889</v>
+        <v>1.176111111111111</v>
       </c>
       <c r="D392">
-        <v>0.1455555555555555</v>
+        <v>0.1908333333333333</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6020,13 +6023,13 @@
         <v>34</v>
       </c>
       <c r="B393" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C393">
-        <v>3.454444444444444</v>
+        <v>1.212777777777778</v>
       </c>
       <c r="D393">
-        <v>0.1425</v>
+        <v>0.2805555555555556</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6034,13 +6037,13 @@
         <v>34</v>
       </c>
       <c r="B394" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C394">
-        <v>3.466666666666667</v>
+        <v>1.176111111111111</v>
       </c>
       <c r="D394">
-        <v>0.1358333333333333</v>
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6048,13 +6051,13 @@
         <v>34</v>
       </c>
       <c r="B395" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C395">
-        <v>3.233888888888889</v>
+        <v>1.273888888888889</v>
       </c>
       <c r="D395">
-        <v>0.1791666666666667</v>
+        <v>0.2580555555555555</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6062,13 +6065,13 @@
         <v>34</v>
       </c>
       <c r="B396" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C396">
-        <v>2.474444444444444</v>
+        <v>1.273888888888889</v>
       </c>
       <c r="D396">
-        <v>0.03583333333333334</v>
+        <v>0.2244444444444444</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6076,13 +6079,13 @@
         <v>34</v>
       </c>
       <c r="B397" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C397">
-        <v>2.633611111111111</v>
+        <v>1.335277777777778</v>
       </c>
       <c r="D397">
-        <v>0.02388888888888889</v>
+        <v>0.2244444444444444</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6090,13 +6093,13 @@
         <v>34</v>
       </c>
       <c r="B398" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C398">
-        <v>3.074722222222222</v>
+        <v>1.596388888888889</v>
       </c>
       <c r="D398">
-        <v>0.08361111111111111</v>
+        <v>0.2244444444444444</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -6104,13 +6107,13 @@
         <v>34</v>
       </c>
       <c r="B399" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C399">
-        <v>3.478888888888889</v>
+        <v>1.721111111111111</v>
       </c>
       <c r="D399">
-        <v>0.12</v>
+        <v>0.2355555555555555</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6118,13 +6121,13 @@
         <v>34</v>
       </c>
       <c r="B400" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C400">
-        <v>3.674722222222222</v>
+        <v>1.937777777777778</v>
       </c>
       <c r="D400">
-        <v>0.1158333333333333</v>
+        <v>0.2469444444444444</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6132,13 +6135,13 @@
         <v>34</v>
       </c>
       <c r="B401" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C401">
-        <v>1.237222222222222</v>
+        <v>0.9813888888888889</v>
       </c>
       <c r="D401">
-        <v>0.07972222222222222</v>
+        <v>0.2469444444444444</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6146,13 +6149,13 @@
         <v>34</v>
       </c>
       <c r="B402" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C402">
-        <v>1.564444444444445</v>
+        <v>1.290277777777778</v>
       </c>
       <c r="D402">
-        <v>0.1266666666666667</v>
+        <v>0.2694444444444444</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6160,13 +6163,13 @@
         <v>34</v>
       </c>
       <c r="B403" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C403">
-        <v>2.598333333333333</v>
+        <v>1.577222222222222</v>
       </c>
       <c r="D403">
-        <v>0.0925</v>
+        <v>0.3255555555555555</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6174,13 +6177,13 @@
         <v>34</v>
       </c>
       <c r="B404" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C404">
-        <v>3.003055555555556</v>
+        <v>1.848333333333333</v>
       </c>
       <c r="D404">
-        <v>0.07027777777777777</v>
+        <v>0.3816666666666667</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6188,13 +6191,13 @@
         <v>35</v>
       </c>
       <c r="B405" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C405">
-        <v>133.2677777777778</v>
+        <v>2.866388888888889</v>
       </c>
       <c r="D405">
-        <v>35.82944444444445</v>
+        <v>0.1455555555555555</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6202,13 +6205,13 @@
         <v>35</v>
       </c>
       <c r="B406" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C406">
-        <v>129.2008333333333</v>
+        <v>3.454444444444444</v>
       </c>
       <c r="D406">
-        <v>30.69583333333333</v>
+        <v>0.1425</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6216,13 +6219,13 @@
         <v>35</v>
       </c>
       <c r="B407" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C407">
-        <v>128.0736111111111</v>
+        <v>3.466666666666667</v>
       </c>
       <c r="D407">
-        <v>31.49083333333333</v>
+        <v>0.1358333333333333</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6230,13 +6233,13 @@
         <v>35</v>
       </c>
       <c r="B408" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C408">
-        <v>128.0255555555555</v>
+        <v>3.233888888888889</v>
       </c>
       <c r="D408">
-        <v>31.92555555555555</v>
+        <v>0.1791666666666667</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6244,13 +6247,13 @@
         <v>35</v>
       </c>
       <c r="B409" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C409">
-        <v>129.2380555555555</v>
+        <v>2.474444444444444</v>
       </c>
       <c r="D409">
-        <v>29.35444444444444</v>
+        <v>0.03583333333333334</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6258,13 +6261,13 @@
         <v>35</v>
       </c>
       <c r="B410" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C410">
-        <v>129.3238888888889</v>
+        <v>2.633611111111111</v>
       </c>
       <c r="D410">
-        <v>31.11833333333333</v>
+        <v>0.02388888888888889</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6272,13 +6275,13 @@
         <v>35</v>
       </c>
       <c r="B411" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C411">
-        <v>138.9427777777778</v>
+        <v>3.074722222222222</v>
       </c>
       <c r="D411">
-        <v>26.30277777777778</v>
+        <v>0.08361111111111111</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6286,13 +6289,13 @@
         <v>35</v>
       </c>
       <c r="B412" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C412">
-        <v>139.9469444444445</v>
+        <v>3.478888888888889</v>
       </c>
       <c r="D412">
-        <v>28.64416666666667</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6300,13 +6303,13 @@
         <v>35</v>
       </c>
       <c r="B413" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C413">
-        <v>140.3980555555555</v>
+        <v>3.674722222222222</v>
       </c>
       <c r="D413">
-        <v>26.69833333333333</v>
+        <v>0.1158333333333333</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6314,13 +6317,13 @@
         <v>35</v>
       </c>
       <c r="B414" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C414">
-        <v>58.20027777777778</v>
+        <v>1.237222222222222</v>
       </c>
       <c r="D414">
-        <v>21.9775</v>
+        <v>0.07972222222222222</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6328,13 +6331,13 @@
         <v>35</v>
       </c>
       <c r="B415" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C415">
-        <v>55.26777777777778</v>
+        <v>1.564444444444445</v>
       </c>
       <c r="D415">
-        <v>22.60972222222222</v>
+        <v>0.1266666666666667</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6342,13 +6345,13 @@
         <v>35</v>
       </c>
       <c r="B416" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C416">
-        <v>109.3866666666667</v>
+        <v>2.598333333333333</v>
       </c>
       <c r="D416">
-        <v>22.87027777777778</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6356,13 +6359,13 @@
         <v>35</v>
       </c>
       <c r="B417" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C417">
-        <v>127.6063888888889</v>
+        <v>3.003055555555556</v>
       </c>
       <c r="D417">
-        <v>22.78194444444444</v>
+        <v>0.07027777777777777</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6370,13 +6373,13 @@
         <v>36</v>
       </c>
       <c r="B418" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C418">
-        <v>251.2230555555556</v>
+        <v>133.2677777777778</v>
       </c>
       <c r="D418">
-        <v>292.6522222222222</v>
+        <v>35.82944444444445</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6384,13 +6387,13 @@
         <v>36</v>
       </c>
       <c r="B419" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C419">
-        <v>237.2580555555556</v>
+        <v>129.2008333333333</v>
       </c>
       <c r="D419">
-        <v>208.875</v>
+        <v>30.69583333333333</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6398,13 +6401,13 @@
         <v>36</v>
       </c>
       <c r="B420" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C420">
-        <v>242.3786111111111</v>
+        <v>128.0736111111111</v>
       </c>
       <c r="D420">
-        <v>200.8572222222222</v>
+        <v>31.49083333333333</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6412,13 +6415,13 @@
         <v>36</v>
       </c>
       <c r="B421" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C421">
-        <v>248.5769444444445</v>
+        <v>128.0255555555555</v>
       </c>
       <c r="D421">
-        <v>199.7672222222222</v>
+        <v>31.92555555555555</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6426,13 +6429,13 @@
         <v>36</v>
       </c>
       <c r="B422" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C422">
-        <v>272.5625</v>
+        <v>129.2380555555555</v>
       </c>
       <c r="D422">
-        <v>199.0302777777778</v>
+        <v>29.35444444444444</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6440,13 +6443,13 @@
         <v>36</v>
       </c>
       <c r="B423" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C423">
-        <v>283.1463888888889</v>
+        <v>129.3238888888889</v>
       </c>
       <c r="D423">
-        <v>233.0841666666667</v>
+        <v>31.11833333333333</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6454,13 +6457,13 @@
         <v>36</v>
       </c>
       <c r="B424" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C424">
-        <v>285.1633333333334</v>
+        <v>138.9427777777778</v>
       </c>
       <c r="D424">
-        <v>274.0144444444445</v>
+        <v>26.30277777777778</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6468,13 +6471,13 @@
         <v>36</v>
       </c>
       <c r="B425" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C425">
-        <v>289.5675</v>
+        <v>139.9469444444445</v>
       </c>
       <c r="D425">
-        <v>237.2283333333333</v>
+        <v>28.64416666666667</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6482,13 +6485,13 @@
         <v>36</v>
       </c>
       <c r="B426" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C426">
-        <v>294.49</v>
+        <v>140.3980555555555</v>
       </c>
       <c r="D426">
-        <v>268.1486111111111</v>
+        <v>26.69833333333333</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6496,13 +6499,13 @@
         <v>36</v>
       </c>
       <c r="B427" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C427">
-        <v>182.2222222222222</v>
+        <v>58.20027777777778</v>
       </c>
       <c r="D427">
-        <v>182.9433333333333</v>
+        <v>21.9775</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6510,13 +6513,13 @@
         <v>36</v>
       </c>
       <c r="B428" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C428">
-        <v>231.5616666666667</v>
+        <v>55.26777777777778</v>
       </c>
       <c r="D428">
-        <v>203.9113888888889</v>
+        <v>22.60972222222222</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6524,13 +6527,13 @@
         <v>36</v>
       </c>
       <c r="B429" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C429">
-        <v>263.5433333333334</v>
+        <v>109.3866666666667</v>
       </c>
       <c r="D429">
-        <v>190.6069444444445</v>
+        <v>22.87027777777778</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6538,13 +6541,13 @@
         <v>36</v>
       </c>
       <c r="B430" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C430">
-        <v>281.2844444444444</v>
+        <v>127.6063888888889</v>
       </c>
       <c r="D430">
-        <v>190.5597222222222</v>
+        <v>22.78194444444444</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6552,13 +6555,13 @@
         <v>37</v>
       </c>
       <c r="B431" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C431">
-        <v>1.580277777777778</v>
+        <v>251.2230555555556</v>
       </c>
       <c r="D431">
-        <v>3.891944444444444</v>
+        <v>292.6522222222222</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6566,13 +6569,13 @@
         <v>37</v>
       </c>
       <c r="B432" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C432">
-        <v>0.9186111111111112</v>
+        <v>237.2580555555556</v>
       </c>
       <c r="D432">
-        <v>3.616944444444445</v>
+        <v>208.875</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6580,13 +6583,13 @@
         <v>37</v>
       </c>
       <c r="B433" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C433">
-        <v>1.482222222222222</v>
+        <v>242.3786111111111</v>
       </c>
       <c r="D433">
-        <v>3.159444444444444</v>
+        <v>200.8572222222222</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6594,13 +6597,13 @@
         <v>37</v>
       </c>
       <c r="B434" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C434">
-        <v>2.339722222222222</v>
+        <v>248.5769444444445</v>
       </c>
       <c r="D434">
-        <v>2.93</v>
+        <v>199.7672222222222</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -6608,13 +6611,13 @@
         <v>37</v>
       </c>
       <c r="B435" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C435">
-        <v>5.353333333333333</v>
+        <v>272.5625</v>
       </c>
       <c r="D435">
-        <v>2.746666666666667</v>
+        <v>199.0302777777778</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6622,13 +6625,13 @@
         <v>37</v>
       </c>
       <c r="B436" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C436">
-        <v>3.895555555555556</v>
+        <v>283.1463888888889</v>
       </c>
       <c r="D436">
-        <v>2.277222222222222</v>
+        <v>233.0841666666667</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6636,13 +6639,13 @@
         <v>37</v>
       </c>
       <c r="B437" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C437">
-        <v>3.930277777777778</v>
+        <v>285.1633333333334</v>
       </c>
       <c r="D437">
-        <v>1.920277777777778</v>
+        <v>274.0144444444445</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6650,13 +6653,13 @@
         <v>37</v>
       </c>
       <c r="B438" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C438">
-        <v>3.729166666666667</v>
+        <v>289.5675</v>
       </c>
       <c r="D438">
-        <v>1.543055555555556</v>
+        <v>237.2283333333333</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6664,13 +6667,13 @@
         <v>37</v>
       </c>
       <c r="B439" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C439">
-        <v>2.942777777777778</v>
+        <v>294.49</v>
       </c>
       <c r="D439">
-        <v>1.116111111111111</v>
+        <v>268.1486111111111</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6678,13 +6681,13 @@
         <v>37</v>
       </c>
       <c r="B440" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C440">
-        <v>1.018611111111111</v>
+        <v>182.2222222222222</v>
       </c>
       <c r="D440">
-        <v>0.7813888888888889</v>
+        <v>182.9433333333333</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6692,13 +6695,13 @@
         <v>37</v>
       </c>
       <c r="B441" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C441">
-        <v>1.962777777777778</v>
+        <v>231.5616666666667</v>
       </c>
       <c r="D441">
-        <v>0.7891666666666667</v>
+        <v>203.9113888888889</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6706,13 +6709,13 @@
         <v>37</v>
       </c>
       <c r="B442" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C442">
-        <v>3.623611111111111</v>
+        <v>263.5433333333334</v>
       </c>
       <c r="D442">
-        <v>0.8522222222222222</v>
+        <v>190.6069444444445</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6720,12 +6723,194 @@
         <v>37</v>
       </c>
       <c r="B443" t="s">
+        <v>51</v>
+      </c>
+      <c r="C443">
+        <v>281.2844444444444</v>
+      </c>
+      <c r="D443">
+        <v>190.5597222222222</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4">
+      <c r="A444" t="s">
+        <v>38</v>
+      </c>
+      <c r="B444" t="s">
+        <v>39</v>
+      </c>
+      <c r="C444">
+        <v>1.580277777777778</v>
+      </c>
+      <c r="D444">
+        <v>3.891944444444444</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4">
+      <c r="A445" t="s">
+        <v>38</v>
+      </c>
+      <c r="B445" t="s">
+        <v>40</v>
+      </c>
+      <c r="C445">
+        <v>0.9186111111111112</v>
+      </c>
+      <c r="D445">
+        <v>3.616944444444445</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4">
+      <c r="A446" t="s">
+        <v>38</v>
+      </c>
+      <c r="B446" t="s">
+        <v>41</v>
+      </c>
+      <c r="C446">
+        <v>1.482222222222222</v>
+      </c>
+      <c r="D446">
+        <v>3.159444444444444</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4">
+      <c r="A447" t="s">
+        <v>38</v>
+      </c>
+      <c r="B447" t="s">
+        <v>42</v>
+      </c>
+      <c r="C447">
+        <v>2.339722222222222</v>
+      </c>
+      <c r="D447">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4">
+      <c r="A448" t="s">
+        <v>38</v>
+      </c>
+      <c r="B448" t="s">
+        <v>43</v>
+      </c>
+      <c r="C448">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="D448">
+        <v>2.746666666666667</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4">
+      <c r="A449" t="s">
+        <v>38</v>
+      </c>
+      <c r="B449" t="s">
+        <v>44</v>
+      </c>
+      <c r="C449">
+        <v>3.895555555555556</v>
+      </c>
+      <c r="D449">
+        <v>2.277222222222222</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4">
+      <c r="A450" t="s">
+        <v>38</v>
+      </c>
+      <c r="B450" t="s">
+        <v>45</v>
+      </c>
+      <c r="C450">
+        <v>3.930277777777778</v>
+      </c>
+      <c r="D450">
+        <v>1.920277777777778</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4">
+      <c r="A451" t="s">
+        <v>38</v>
+      </c>
+      <c r="B451" t="s">
+        <v>46</v>
+      </c>
+      <c r="C451">
+        <v>3.729166666666667</v>
+      </c>
+      <c r="D451">
+        <v>1.543055555555556</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4">
+      <c r="A452" t="s">
+        <v>38</v>
+      </c>
+      <c r="B452" t="s">
+        <v>47</v>
+      </c>
+      <c r="C452">
+        <v>2.942777777777778</v>
+      </c>
+      <c r="D452">
+        <v>1.116111111111111</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4">
+      <c r="A453" t="s">
+        <v>38</v>
+      </c>
+      <c r="B453" t="s">
+        <v>48</v>
+      </c>
+      <c r="C453">
+        <v>1.018611111111111</v>
+      </c>
+      <c r="D453">
+        <v>0.7813888888888889</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4">
+      <c r="A454" t="s">
+        <v>38</v>
+      </c>
+      <c r="B454" t="s">
+        <v>49</v>
+      </c>
+      <c r="C454">
+        <v>1.962777777777778</v>
+      </c>
+      <c r="D454">
+        <v>0.7891666666666667</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4">
+      <c r="A455" t="s">
+        <v>38</v>
+      </c>
+      <c r="B455" t="s">
         <v>50</v>
       </c>
-      <c r="C443">
+      <c r="C455">
+        <v>3.623611111111111</v>
+      </c>
+      <c r="D455">
+        <v>0.8522222222222222</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4">
+      <c r="A456" t="s">
+        <v>38</v>
+      </c>
+      <c r="B456" t="s">
+        <v>51</v>
+      </c>
+      <c r="C456">
         <v>5.216666666666667</v>
       </c>
-      <c r="D443">
+      <c r="D456">
         <v>0.8863888888888889</v>
       </c>
     </row>

--- a/transport/input_data/global/international_marine_and_aviation_data.xlsx
+++ b/transport/input_data/global/international_marine_and_aviation_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="53">
   <si>
     <t>Country</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>United States of America</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
   </si>
   <si>
     <t>Venezuela</t>
@@ -527,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D456"/>
+  <dimension ref="A1:D469"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -549,7 +552,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>5.561388888888889</v>
@@ -563,7 +566,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3">
         <v>6.198611111111111</v>
@@ -577,7 +580,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4">
         <v>6.406666666666666</v>
@@ -591,7 +594,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>5.083611111111111</v>
@@ -605,7 +608,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6">
         <v>5.561388888888889</v>
@@ -619,7 +622,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7">
         <v>4.618333333333333</v>
@@ -633,7 +636,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8">
         <v>4.348611111111111</v>
@@ -647,7 +650,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9">
         <v>5.316388888888889</v>
@@ -661,7 +664,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10">
         <v>4.336388888888889</v>
@@ -675,7 +678,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11">
         <v>2.658333333333333</v>
@@ -689,7 +692,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12">
         <v>2.731666666666666</v>
@@ -703,7 +706,7 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13">
         <v>4.266944444444444</v>
@@ -717,7 +720,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14">
         <v>6.777222222222222</v>
@@ -731,7 +734,7 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>8.501388888888888</v>
@@ -745,7 +748,7 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>8.489166666666666</v>
@@ -759,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>10.89027777777778</v>
@@ -773,7 +776,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>10.79222222222222</v>
@@ -787,7 +790,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>10.97611111111111</v>
@@ -801,7 +804,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>11.33111111111111</v>
@@ -815,7 +818,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>12.02944444444444</v>
@@ -829,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>10.93916666666667</v>
@@ -843,7 +846,7 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>10.80444444444444</v>
@@ -857,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>4.613333333333333</v>
@@ -871,7 +874,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>4.65</v>
@@ -885,7 +888,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>9.015277777777778</v>
@@ -899,7 +902,7 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>11.62527777777778</v>
@@ -913,7 +916,7 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28">
         <v>38.28111111111111</v>
@@ -927,7 +930,7 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29">
         <v>39.72666666666667</v>
@@ -941,7 +944,7 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30">
         <v>41.82138888888889</v>
@@ -955,7 +958,7 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31">
         <v>45.11666666666667</v>
@@ -969,7 +972,7 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32">
         <v>44.835</v>
@@ -983,7 +986,7 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33">
         <v>47.8975</v>
@@ -997,7 +1000,7 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C34">
         <v>51.63</v>
@@ -1011,7 +1014,7 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C35">
         <v>54.68305555555555</v>
@@ -1025,7 +1028,7 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C36">
         <v>58.1825</v>
@@ -1039,7 +1042,7 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C37">
         <v>44.60027777777778</v>
@@ -1053,7 +1056,7 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C38">
         <v>14.56805555555556</v>
@@ -1067,7 +1070,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C39">
         <v>20.40527777777778</v>
@@ -1081,7 +1084,7 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C40">
         <v>36.60055555555556</v>
@@ -1095,7 +1098,7 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C41">
         <v>25.16138888888889</v>
@@ -1109,7 +1112,7 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C42">
         <v>26.15361111111111</v>
@@ -1123,7 +1126,7 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C43">
         <v>27.29305555555555</v>
@@ -1137,7 +1140,7 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C44">
         <v>29.16722222222222</v>
@@ -1151,7 +1154,7 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C45">
         <v>28.48111111111111</v>
@@ -1165,7 +1168,7 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C46">
         <v>26.43555555555556</v>
@@ -1179,7 +1182,7 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C47">
         <v>25.8475</v>
@@ -1193,7 +1196,7 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C48">
         <v>29.30194444444444</v>
@@ -1207,7 +1210,7 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C49">
         <v>28.38333333333333</v>
@@ -1221,7 +1224,7 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C50">
         <v>11.95611111111111</v>
@@ -1235,7 +1238,7 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C51">
         <v>12.82416666666667</v>
@@ -1249,7 +1252,7 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C52">
         <v>20.87722222222222</v>
@@ -1263,7 +1266,7 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C53">
         <v>24.48527777777778</v>
@@ -1277,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C54">
         <v>35.95388888888889</v>
@@ -1291,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C55">
         <v>40.59666666666666</v>
@@ -1305,7 +1308,7 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C56">
         <v>42.37277777777778</v>
@@ -1319,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C57">
         <v>42.0175</v>
@@ -1333,7 +1336,7 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C58">
         <v>43.49972222222222</v>
@@ -1347,7 +1350,7 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C59">
         <v>45.76611111111111</v>
@@ -1361,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C60">
         <v>50.08888888888889</v>
@@ -1375,7 +1378,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C61">
         <v>57.17388888888889</v>
@@ -1389,7 +1392,7 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C62">
         <v>57.77027777777778</v>
@@ -1403,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C63">
         <v>25.07194444444444</v>
@@ -1417,7 +1420,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C64">
         <v>25.18222222222222</v>
@@ -1431,7 +1434,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C65">
         <v>43.41583333333333</v>
@@ -1445,7 +1448,7 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C66">
         <v>51.6675</v>
@@ -1459,7 +1462,7 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C67">
         <v>5.083611111111111</v>
@@ -1473,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C68">
         <v>8.183055555555555</v>
@@ -1487,7 +1490,7 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C69">
         <v>7.239722222222222</v>
@@ -1501,7 +1504,7 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C70">
         <v>7.533611111111111</v>
@@ -1515,7 +1518,7 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C71">
         <v>6.516944444444444</v>
@@ -1529,7 +1532,7 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C72">
         <v>6.713055555555556</v>
@@ -1543,7 +1546,7 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C73">
         <v>7.091944444444445</v>
@@ -1557,7 +1560,7 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C74">
         <v>7.791388888888889</v>
@@ -1571,7 +1574,7 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C75">
         <v>8.836666666666666</v>
@@ -1585,7 +1588,7 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C76">
         <v>4.733333333333333</v>
@@ -1599,7 +1602,7 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C77">
         <v>5.256111111111111</v>
@@ -1613,7 +1616,7 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C78">
         <v>7.254166666666666</v>
@@ -1627,7 +1630,7 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C79">
         <v>8.060833333333333</v>
@@ -1641,7 +1644,7 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C80">
         <v>69.01666666666667</v>
@@ -1655,7 +1658,7 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C81">
         <v>72.67277777777778</v>
@@ -1669,7 +1672,7 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C82">
         <v>77.78277777777778</v>
@@ -1683,7 +1686,7 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C83">
         <v>85.28333333333333</v>
@@ -1697,7 +1700,7 @@
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C84">
         <v>92.75944444444444</v>
@@ -1711,7 +1714,7 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C85">
         <v>102.4466666666667</v>
@@ -1725,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C86">
         <v>113.7425</v>
@@ -1739,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C87">
         <v>123.6858333333333</v>
@@ -1753,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C88">
         <v>127.5972222222222</v>
@@ -1767,7 +1770,7 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C89">
         <v>58.44472222222223</v>
@@ -1781,7 +1784,7 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C90">
         <v>53.64277777777778</v>
@@ -1795,7 +1798,7 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C91">
         <v>47.18444444444444</v>
@@ -1809,7 +1812,7 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C92">
         <v>73.82083333333334</v>
@@ -1823,7 +1826,7 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C93">
         <v>5.524722222222223</v>
@@ -1837,7 +1840,7 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C94">
         <v>6.051388888888889</v>
@@ -1851,7 +1854,7 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C95">
         <v>6.37</v>
@@ -1865,7 +1868,7 @@
         <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C96">
         <v>8.183055555555555</v>
@@ -1879,7 +1882,7 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C97">
         <v>8.832222222222223</v>
@@ -1893,7 +1896,7 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C98">
         <v>8.86888888888889</v>
@@ -1907,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C99">
         <v>9.088333333333333</v>
@@ -1921,7 +1924,7 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C100">
         <v>10.39055555555556</v>
@@ -1935,7 +1938,7 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C101">
         <v>10.5775</v>
@@ -1949,7 +1952,7 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C102">
         <v>4.895833333333333</v>
@@ -1963,7 +1966,7 @@
         <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C103">
         <v>5.739166666666667</v>
@@ -1977,7 +1980,7 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C104">
         <v>11.20555555555556</v>
@@ -1991,7 +1994,7 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C105">
         <v>10.44277777777778</v>
@@ -2005,7 +2008,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C106">
         <v>9.444722222222222</v>
@@ -2019,7 +2022,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C107">
         <v>9.983611111111111</v>
@@ -2033,7 +2036,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C108">
         <v>6.908888888888889</v>
@@ -2047,7 +2050,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C109">
         <v>8.146111111111111</v>
@@ -2061,7 +2064,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C110">
         <v>6.198611111111111</v>
@@ -2075,7 +2078,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C111">
         <v>5.206111111111111</v>
@@ -2089,7 +2092,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C112">
         <v>7.643888888888889</v>
@@ -2103,7 +2106,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C113">
         <v>8.795555555555556</v>
@@ -2117,7 +2120,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C114">
         <v>7.852222222222222</v>
@@ -2131,7 +2134,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C115">
         <v>3.7425</v>
@@ -2145,7 +2148,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C116">
         <v>3.273611111111111</v>
@@ -2159,7 +2162,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C117">
         <v>3.124444444444444</v>
@@ -2173,7 +2176,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C118">
         <v>12.59305555555556</v>
@@ -2187,7 +2190,7 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C119">
         <v>3.601388888888889</v>
@@ -2201,7 +2204,7 @@
         <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C120">
         <v>4.311944444444444</v>
@@ -2215,7 +2218,7 @@
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C121">
         <v>4.667222222222223</v>
@@ -2229,7 +2232,7 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C122">
         <v>5.255277777777778</v>
@@ -2243,7 +2246,7 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C123">
         <v>5.573611111111111</v>
@@ -2257,7 +2260,7 @@
         <v>13</v>
       </c>
       <c r="B124" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C124">
         <v>7.203055555555555</v>
@@ -2271,7 +2274,7 @@
         <v>13</v>
       </c>
       <c r="B125" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C125">
         <v>8.359166666666667</v>
@@ -2285,7 +2288,7 @@
         <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C126">
         <v>8.955555555555556</v>
@@ -2299,7 +2302,7 @@
         <v>13</v>
       </c>
       <c r="B127" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C127">
         <v>10.045</v>
@@ -2313,7 +2316,7 @@
         <v>13</v>
       </c>
       <c r="B128" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C128">
         <v>4.641666666666667</v>
@@ -2327,7 +2330,7 @@
         <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C129">
         <v>10.10444444444444</v>
@@ -2341,7 +2344,7 @@
         <v>13</v>
       </c>
       <c r="B130" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C130">
         <v>11.57111111111111</v>
@@ -2355,7 +2358,7 @@
         <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C131">
         <v>13.60027777777778</v>
@@ -2369,7 +2372,7 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C132">
         <v>65.75805555555556</v>
@@ -2383,7 +2386,7 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C133">
         <v>64.36138888888888</v>
@@ -2397,7 +2400,7 @@
         <v>14</v>
       </c>
       <c r="B134" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C134">
         <v>63.79805555555556</v>
@@ -2411,7 +2414,7 @@
         <v>14</v>
       </c>
       <c r="B135" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C135">
         <v>64.41055555555556</v>
@@ -2425,7 +2428,7 @@
         <v>14</v>
       </c>
       <c r="B136" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C136">
         <v>68.19583333333334</v>
@@ -2439,7 +2442,7 @@
         <v>14</v>
       </c>
       <c r="B137" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C137">
         <v>67.06861111111111</v>
@@ -2453,7 +2456,7 @@
         <v>14</v>
       </c>
       <c r="B138" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C138">
         <v>68.12666666666667</v>
@@ -2467,7 +2470,7 @@
         <v>14</v>
       </c>
       <c r="B139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C139">
         <v>70.50722222222223</v>
@@ -2481,7 +2484,7 @@
         <v>14</v>
       </c>
       <c r="B140" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C140">
         <v>74.05527777777777</v>
@@ -2495,7 +2498,7 @@
         <v>14</v>
       </c>
       <c r="B141" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C141">
         <v>31.44361111111111</v>
@@ -2509,7 +2512,7 @@
         <v>14</v>
       </c>
       <c r="B142" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C142">
         <v>34.19</v>
@@ -2523,7 +2526,7 @@
         <v>14</v>
       </c>
       <c r="B143" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C143">
         <v>58.5775</v>
@@ -2537,7 +2540,7 @@
         <v>14</v>
       </c>
       <c r="B144" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C144">
         <v>64.37638888888888</v>
@@ -2551,7 +2554,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C145">
         <v>91.74027777777778</v>
@@ -2565,7 +2568,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C146">
         <v>97.8775</v>
@@ -2579,7 +2582,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C147">
         <v>99.83750000000001</v>
@@ -2593,7 +2596,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C148">
         <v>95.86861111111111</v>
@@ -2607,7 +2610,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C149">
         <v>95.99111111111111</v>
@@ -2621,7 +2624,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C150">
         <v>103.2552777777778</v>
@@ -2635,7 +2638,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C151">
         <v>114.1577777777778</v>
@@ -2649,7 +2652,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C152">
         <v>117.7347222222222</v>
@@ -2663,7 +2666,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C153">
         <v>116.7669444444444</v>
@@ -2677,7 +2680,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C154">
         <v>53.99805555555555</v>
@@ -2691,7 +2694,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C155">
         <v>72.11583333333333</v>
@@ -2705,7 +2708,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C156">
         <v>107.1752777777778</v>
@@ -2719,7 +2722,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C157">
         <v>111.7566666666667</v>
@@ -2733,7 +2736,7 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C158">
         <v>1.646666666666667</v>
@@ -2747,7 +2750,7 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C159">
         <v>1.690833333333333</v>
@@ -2761,7 +2764,7 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C160">
         <v>1.596666666666667</v>
@@ -2775,7 +2778,7 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C161">
         <v>1.391944444444444</v>
@@ -2789,7 +2792,7 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C162">
         <v>1.223333333333333</v>
@@ -2803,7 +2806,7 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C163">
         <v>1.598055555555556</v>
@@ -2817,7 +2820,7 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C164">
         <v>1.749722222222222</v>
@@ -2831,7 +2834,7 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C165">
         <v>2.136388888888889</v>
@@ -2845,7 +2848,7 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C166">
         <v>2.599444444444444</v>
@@ -2859,7 +2862,7 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C167">
         <v>1.476111111111111</v>
@@ -2873,7 +2876,7 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C168">
         <v>2.341388888888889</v>
@@ -2887,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C169">
         <v>2.345</v>
@@ -2901,7 +2904,7 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C170">
         <v>2.386111111111111</v>
@@ -2915,7 +2918,7 @@
         <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C171">
         <v>57.80777777777778</v>
@@ -2929,7 +2932,7 @@
         <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C172">
         <v>57.80777777777778</v>
@@ -2943,7 +2946,7 @@
         <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C173">
         <v>47.19916666666666</v>
@@ -2957,7 +2960,7 @@
         <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C174">
         <v>46.52555555555556</v>
@@ -2971,7 +2974,7 @@
         <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C175">
         <v>53.69166666666667</v>
@@ -2985,7 +2988,7 @@
         <v>17</v>
       </c>
       <c r="B176" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C176">
         <v>60.01277777777778</v>
@@ -2999,7 +3002,7 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C177">
         <v>46.45194444444444</v>
@@ -3013,7 +3016,7 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C178">
         <v>50.58027777777778</v>
@@ -3027,7 +3030,7 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C179">
         <v>48.74277777777777</v>
@@ -3041,7 +3044,7 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C180">
         <v>15.64333333333333</v>
@@ -3055,7 +3058,7 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C181">
         <v>21.44972222222222</v>
@@ -3069,7 +3072,7 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C182">
         <v>37.84027777777778</v>
@@ -3083,7 +3086,7 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C183">
         <v>47.39111111111111</v>
@@ -3097,7 +3100,7 @@
         <v>18</v>
       </c>
       <c r="B184" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C184">
         <v>8.33</v>
@@ -3111,7 +3114,7 @@
         <v>18</v>
       </c>
       <c r="B185" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C185">
         <v>8.844444444444445</v>
@@ -3125,7 +3128,7 @@
         <v>18</v>
       </c>
       <c r="B186" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C186">
         <v>10.94416666666667</v>
@@ -3139,7 +3142,7 @@
         <v>18</v>
       </c>
       <c r="B187" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C187">
         <v>15.89555555555556</v>
@@ -3153,7 +3156,7 @@
         <v>18</v>
       </c>
       <c r="B188" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C188">
         <v>10.23083333333333</v>
@@ -3167,7 +3170,7 @@
         <v>18</v>
       </c>
       <c r="B189" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C189">
         <v>9.493611111111111</v>
@@ -3181,7 +3184,7 @@
         <v>18</v>
       </c>
       <c r="B190" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C190">
         <v>11.80666666666667</v>
@@ -3195,7 +3198,7 @@
         <v>18</v>
       </c>
       <c r="B191" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C191">
         <v>12.65805555555556</v>
@@ -3209,7 +3212,7 @@
         <v>18</v>
       </c>
       <c r="B192" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C192">
         <v>11.22222222222222</v>
@@ -3223,7 +3226,7 @@
         <v>18</v>
       </c>
       <c r="B193" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C193">
         <v>5.414444444444444</v>
@@ -3237,7 +3240,7 @@
         <v>18</v>
       </c>
       <c r="B194" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C194">
         <v>2.246666666666667</v>
@@ -3251,7 +3254,7 @@
         <v>18</v>
       </c>
       <c r="B195" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C195">
         <v>2.540277777777778</v>
@@ -3265,7 +3268,7 @@
         <v>18</v>
       </c>
       <c r="B196" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C196">
         <v>7.815</v>
@@ -3279,7 +3282,7 @@
         <v>19</v>
       </c>
       <c r="B197" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C197">
         <v>38.75888888888889</v>
@@ -3293,7 +3296,7 @@
         <v>19</v>
       </c>
       <c r="B198" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C198">
         <v>36.98277777777778</v>
@@ -3307,7 +3310,7 @@
         <v>19</v>
       </c>
       <c r="B199" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C199">
         <v>35.79444444444444</v>
@@ -3321,7 +3324,7 @@
         <v>19</v>
       </c>
       <c r="B200" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C200">
         <v>36.68861111111111</v>
@@ -3335,7 +3338,7 @@
         <v>19</v>
       </c>
       <c r="B201" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C201">
         <v>37.76666666666667</v>
@@ -3349,7 +3352,7 @@
         <v>19</v>
       </c>
       <c r="B202" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C202">
         <v>39.31027777777778</v>
@@ -3363,7 +3366,7 @@
         <v>19</v>
       </c>
       <c r="B203" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C203">
         <v>40.78222222222222</v>
@@ -3377,7 +3380,7 @@
         <v>19</v>
       </c>
       <c r="B204" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C204">
         <v>45.74027777777778</v>
@@ -3391,7 +3394,7 @@
         <v>19</v>
       </c>
       <c r="B205" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C205">
         <v>47.33444444444444</v>
@@ -3405,7 +3408,7 @@
         <v>19</v>
       </c>
       <c r="B206" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C206">
         <v>17.83083333333333</v>
@@ -3419,7 +3422,7 @@
         <v>19</v>
       </c>
       <c r="B207" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C207">
         <v>19.46805555555556</v>
@@ -3433,7 +3436,7 @@
         <v>19</v>
       </c>
       <c r="B208" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C208">
         <v>33.92527777777778</v>
@@ -3447,7 +3450,7 @@
         <v>19</v>
       </c>
       <c r="B209" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C209">
         <v>42.93805555555556</v>
@@ -3461,7 +3464,7 @@
         <v>20</v>
       </c>
       <c r="B210" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C210">
         <v>71.07444444444444</v>
@@ -3475,7 +3478,7 @@
         <v>20</v>
       </c>
       <c r="B211" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C211">
         <v>74.55361111111111</v>
@@ -3489,7 +3492,7 @@
         <v>20</v>
       </c>
       <c r="B212" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C212">
         <v>75.53361111111111</v>
@@ -3503,7 +3506,7 @@
         <v>20</v>
       </c>
       <c r="B213" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C213">
         <v>73.81861111111111</v>
@@ -3517,7 +3520,7 @@
         <v>20</v>
       </c>
       <c r="B214" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C214">
         <v>74.43111111111111</v>
@@ -3531,7 +3534,7 @@
         <v>20</v>
       </c>
       <c r="B215" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C215">
         <v>77.82416666666667</v>
@@ -3545,7 +3548,7 @@
         <v>20</v>
       </c>
       <c r="B216" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C216">
         <v>81.48583333333333</v>
@@ -3559,7 +3562,7 @@
         <v>20</v>
       </c>
       <c r="B217" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C217">
         <v>83.79527777777778</v>
@@ -3573,7 +3576,7 @@
         <v>20</v>
       </c>
       <c r="B218" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C218">
         <v>84.10472222222222</v>
@@ -3587,7 +3590,7 @@
         <v>20</v>
       </c>
       <c r="B219" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C219">
         <v>33.12833333333333</v>
@@ -3601,7 +3604,7 @@
         <v>20</v>
       </c>
       <c r="B220" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C220">
         <v>46.12833333333333</v>
@@ -3615,7 +3618,7 @@
         <v>20</v>
       </c>
       <c r="B221" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C221">
         <v>56.31222222222222</v>
@@ -3629,7 +3632,7 @@
         <v>20</v>
       </c>
       <c r="B222" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C222">
         <v>84.56361111111111</v>
@@ -3643,7 +3646,7 @@
         <v>21</v>
       </c>
       <c r="B223" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C223">
         <v>8.219722222222222</v>
@@ -3657,7 +3660,7 @@
         <v>21</v>
       </c>
       <c r="B224" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C224">
         <v>8.219722222222222</v>
@@ -3671,7 +3674,7 @@
         <v>21</v>
       </c>
       <c r="B225" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C225">
         <v>6.753333333333333</v>
@@ -3685,7 +3688,7 @@
         <v>21</v>
       </c>
       <c r="B226" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C226">
         <v>2.571388888888889</v>
@@ -3699,7 +3702,7 @@
         <v>21</v>
       </c>
       <c r="B227" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C227">
         <v>3.683611111111111</v>
@@ -3713,7 +3716,7 @@
         <v>21</v>
       </c>
       <c r="B228" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C228">
         <v>8.631388888888889</v>
@@ -3727,7 +3730,7 @@
         <v>21</v>
       </c>
       <c r="B229" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C229">
         <v>9.331111111111111</v>
@@ -3741,7 +3744,7 @@
         <v>21</v>
       </c>
       <c r="B230" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C230">
         <v>8.256388888888889</v>
@@ -3755,7 +3758,7 @@
         <v>21</v>
       </c>
       <c r="B231" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C231">
         <v>8.641111111111112</v>
@@ -3769,7 +3772,7 @@
         <v>21</v>
       </c>
       <c r="B232" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C232">
         <v>4.804166666666666</v>
@@ -3783,7 +3786,7 @@
         <v>21</v>
       </c>
       <c r="B233" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C233">
         <v>5.882777777777778</v>
@@ -3797,7 +3800,7 @@
         <v>21</v>
       </c>
       <c r="B234" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C234">
         <v>6.680555555555555</v>
@@ -3811,7 +3814,7 @@
         <v>21</v>
       </c>
       <c r="B235" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C235">
         <v>7.816111111111111</v>
@@ -3825,7 +3828,7 @@
         <v>22</v>
       </c>
       <c r="B236" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C236">
         <v>0.5022222222222222</v>
@@ -3839,7 +3842,7 @@
         <v>22</v>
       </c>
       <c r="B237" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C237">
         <v>2.0825</v>
@@ -3853,7 +3856,7 @@
         <v>22</v>
       </c>
       <c r="B238" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C238">
         <v>1.555833333333333</v>
@@ -3867,7 +3870,7 @@
         <v>22</v>
       </c>
       <c r="B239" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C239">
         <v>1.188333333333333</v>
@@ -3881,7 +3884,7 @@
         <v>22</v>
       </c>
       <c r="B240" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C240">
         <v>0.6247222222222222</v>
@@ -3895,7 +3898,7 @@
         <v>22</v>
       </c>
       <c r="B241" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C241">
         <v>0.6491666666666667</v>
@@ -3909,7 +3912,7 @@
         <v>22</v>
       </c>
       <c r="B242" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C242">
         <v>0.6875</v>
@@ -3923,7 +3926,7 @@
         <v>22</v>
       </c>
       <c r="B243" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C243">
         <v>0.5686111111111111</v>
@@ -3937,7 +3940,7 @@
         <v>22</v>
       </c>
       <c r="B244" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C244">
         <v>0.6036111111111111</v>
@@ -3951,7 +3954,7 @@
         <v>22</v>
       </c>
       <c r="B245" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C245">
         <v>0.2116666666666667</v>
@@ -3965,7 +3968,7 @@
         <v>22</v>
       </c>
       <c r="B246" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C246">
         <v>0.5252777777777777</v>
@@ -3979,7 +3982,7 @@
         <v>22</v>
       </c>
       <c r="B247" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C247">
         <v>0.7352777777777778</v>
@@ -3993,7 +3996,7 @@
         <v>22</v>
       </c>
       <c r="B248" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C248">
         <v>1.201944444444444</v>
@@ -4007,7 +4010,7 @@
         <v>23</v>
       </c>
       <c r="B249" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C249">
         <v>0.2058333333333333</v>
@@ -4021,7 +4024,7 @@
         <v>23</v>
       </c>
       <c r="B250" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C250">
         <v>0.2791666666666667</v>
@@ -4035,7 +4038,7 @@
         <v>23</v>
       </c>
       <c r="B251" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C251">
         <v>0.25</v>
@@ -4049,7 +4052,7 @@
         <v>23</v>
       </c>
       <c r="B252" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C252">
         <v>0.2522222222222222</v>
@@ -4063,7 +4066,7 @@
         <v>23</v>
       </c>
       <c r="B253" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C253">
         <v>0.245</v>
@@ -4077,7 +4080,7 @@
         <v>23</v>
       </c>
       <c r="B254" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C254">
         <v>0.2475</v>
@@ -4091,7 +4094,7 @@
         <v>23</v>
       </c>
       <c r="B255" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C255">
         <v>0.25</v>
@@ -4105,7 +4108,7 @@
         <v>23</v>
       </c>
       <c r="B256" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C256">
         <v>0.2744444444444444</v>
@@ -4119,7 +4122,7 @@
         <v>23</v>
       </c>
       <c r="B257" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C257">
         <v>0.2486111111111111</v>
@@ -4133,7 +4136,7 @@
         <v>23</v>
       </c>
       <c r="B258" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C258">
         <v>0.1469444444444444</v>
@@ -4147,7 +4150,7 @@
         <v>23</v>
       </c>
       <c r="B259" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C259">
         <v>0.2044444444444445</v>
@@ -4161,7 +4164,7 @@
         <v>23</v>
       </c>
       <c r="B260" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C260">
         <v>0.2191666666666667</v>
@@ -4175,7 +4178,7 @@
         <v>23</v>
       </c>
       <c r="B261" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C261">
         <v>0.1605555555555556</v>
@@ -4189,7 +4192,7 @@
         <v>24</v>
       </c>
       <c r="B262" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C262">
         <v>17.65277777777778</v>
@@ -4203,7 +4206,7 @@
         <v>24</v>
       </c>
       <c r="B263" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C263">
         <v>18.68194444444444</v>
@@ -4217,7 +4220,7 @@
         <v>24</v>
       </c>
       <c r="B264" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C264">
         <v>19.55166666666667</v>
@@ -4231,7 +4234,7 @@
         <v>24</v>
       </c>
       <c r="B265" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C265">
         <v>21.23</v>
@@ -4245,7 +4248,7 @@
         <v>24</v>
       </c>
       <c r="B266" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C266">
         <v>22.94472222222222</v>
@@ -4259,7 +4262,7 @@
         <v>24</v>
       </c>
       <c r="B267" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C267">
         <v>24.23111111111111</v>
@@ -4273,7 +4276,7 @@
         <v>24</v>
       </c>
       <c r="B268" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C268">
         <v>26.40277777777778</v>
@@ -4287,7 +4290,7 @@
         <v>24</v>
       </c>
       <c r="B269" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C269">
         <v>27.37805555555556</v>
@@ -4301,7 +4304,7 @@
         <v>24</v>
       </c>
       <c r="B270" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C270">
         <v>27.88138888888889</v>
@@ -4315,7 +4318,7 @@
         <v>24</v>
       </c>
       <c r="B271" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C271">
         <v>11.13083333333333</v>
@@ -4329,7 +4332,7 @@
         <v>24</v>
       </c>
       <c r="B272" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C272">
         <v>17.93277777777778</v>
@@ -4343,7 +4346,7 @@
         <v>24</v>
       </c>
       <c r="B273" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C273">
         <v>26.82333333333333</v>
@@ -4357,7 +4360,7 @@
         <v>24</v>
       </c>
       <c r="B274" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C274">
         <v>28.36694444444445</v>
@@ -4371,7 +4374,7 @@
         <v>25</v>
       </c>
       <c r="B275" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C275">
         <v>6.602777777777778</v>
@@ -4385,7 +4388,7 @@
         <v>25</v>
       </c>
       <c r="B276" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C276">
         <v>5.928888888888889</v>
@@ -4399,7 +4402,7 @@
         <v>25</v>
       </c>
       <c r="B277" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C277">
         <v>6.749722222222222</v>
@@ -4413,7 +4416,7 @@
         <v>25</v>
       </c>
       <c r="B278" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C278">
         <v>7.423611111111111</v>
@@ -4427,7 +4430,7 @@
         <v>25</v>
       </c>
       <c r="B279" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C279">
         <v>7.7175</v>
@@ -4441,7 +4444,7 @@
         <v>25</v>
       </c>
       <c r="B280" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C280">
         <v>7.864444444444445</v>
@@ -4455,7 +4458,7 @@
         <v>25</v>
       </c>
       <c r="B281" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C281">
         <v>8.305555555555555</v>
@@ -4469,7 +4472,7 @@
         <v>25</v>
       </c>
       <c r="B282" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C282">
         <v>8.989722222222222</v>
@@ -4483,7 +4486,7 @@
         <v>25</v>
       </c>
       <c r="B283" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C283">
         <v>9.484722222222222</v>
@@ -4497,7 +4500,7 @@
         <v>25</v>
       </c>
       <c r="B284" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C284">
         <v>3.410833333333333</v>
@@ -4511,7 +4514,7 @@
         <v>25</v>
       </c>
       <c r="B285" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C285">
         <v>4.5975</v>
@@ -4525,7 +4528,7 @@
         <v>25</v>
       </c>
       <c r="B286" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C286">
         <v>7.714444444444444</v>
@@ -4539,7 +4542,7 @@
         <v>25</v>
       </c>
       <c r="B287" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C287">
         <v>9.737222222222222</v>
@@ -4553,7 +4556,7 @@
         <v>26</v>
       </c>
       <c r="B288" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C288">
         <v>0.1225</v>
@@ -4567,7 +4570,7 @@
         <v>26</v>
       </c>
       <c r="B289" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C289">
         <v>0.5197222222222222</v>
@@ -4581,7 +4584,7 @@
         <v>26</v>
       </c>
       <c r="B290" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C290">
         <v>0.2697222222222222</v>
@@ -4595,7 +4598,7 @@
         <v>26</v>
       </c>
       <c r="B291" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C291">
         <v>0.2697222222222222</v>
@@ -4609,7 +4612,7 @@
         <v>26</v>
       </c>
       <c r="B292" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C292">
         <v>0.9066666666666666</v>
@@ -4623,7 +4626,7 @@
         <v>26</v>
       </c>
       <c r="B293" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C293">
         <v>0.7719444444444444</v>
@@ -4637,7 +4640,7 @@
         <v>26</v>
       </c>
       <c r="B294" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C294">
         <v>0.3597222222222222</v>
@@ -4651,7 +4654,7 @@
         <v>26</v>
       </c>
       <c r="B295" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C295">
         <v>0.985</v>
@@ -4665,7 +4668,7 @@
         <v>26</v>
       </c>
       <c r="B296" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C296">
         <v>1.001944444444445</v>
@@ -4679,7 +4682,7 @@
         <v>26</v>
       </c>
       <c r="B297" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C297">
         <v>1.029166666666667</v>
@@ -4693,7 +4696,7 @@
         <v>26</v>
       </c>
       <c r="B298" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C298">
         <v>1.153055555555556</v>
@@ -4707,7 +4710,7 @@
         <v>26</v>
       </c>
       <c r="B299" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C299">
         <v>1.204166666666667</v>
@@ -4721,7 +4724,7 @@
         <v>26</v>
       </c>
       <c r="B300" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C300">
         <v>1.254166666666667</v>
@@ -4735,7 +4738,7 @@
         <v>27</v>
       </c>
       <c r="B301" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C301">
         <v>4.703888888888889</v>
@@ -4749,7 +4752,7 @@
         <v>27</v>
       </c>
       <c r="B302" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C302">
         <v>4.998055555555555</v>
@@ -4763,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="B303" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C303">
         <v>4.152777777777778</v>
@@ -4777,7 +4780,7 @@
         <v>27</v>
       </c>
       <c r="B304" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C304">
         <v>3.699444444444445</v>
@@ -4791,7 +4794,7 @@
         <v>27</v>
       </c>
       <c r="B305" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C305">
         <v>4.152777777777778</v>
@@ -4805,7 +4808,7 @@
         <v>27</v>
       </c>
       <c r="B306" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C306">
         <v>5.193888888888889</v>
@@ -4819,7 +4822,7 @@
         <v>27</v>
       </c>
       <c r="B307" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C307">
         <v>6.183611111111111</v>
@@ -4833,7 +4836,7 @@
         <v>27</v>
       </c>
       <c r="B308" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C308">
         <v>7.9675</v>
@@ -4847,7 +4850,7 @@
         <v>27</v>
       </c>
       <c r="B309" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C309">
         <v>7.991944444444444</v>
@@ -4861,7 +4864,7 @@
         <v>27</v>
       </c>
       <c r="B310" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C310">
         <v>3.724722222222222</v>
@@ -4875,7 +4878,7 @@
         <v>27</v>
       </c>
       <c r="B311" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C311">
         <v>5.591666666666667</v>
@@ -4889,7 +4892,7 @@
         <v>27</v>
       </c>
       <c r="B312" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C312">
         <v>7.243055555555555</v>
@@ -4903,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="B313" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C313">
         <v>7.11</v>
@@ -4917,7 +4920,7 @@
         <v>28</v>
       </c>
       <c r="B314" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C314">
         <v>9.224166666666667</v>
@@ -4931,7 +4934,7 @@
         <v>28</v>
       </c>
       <c r="B315" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C315">
         <v>8.097222222222221</v>
@@ -4945,7 +4948,7 @@
         <v>28</v>
       </c>
       <c r="B316" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C316">
         <v>8.834722222222222</v>
@@ -4959,7 +4962,7 @@
         <v>28</v>
       </c>
       <c r="B317" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C317">
         <v>9.811111111111112</v>
@@ -4973,7 +4976,7 @@
         <v>28</v>
       </c>
       <c r="B318" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C318">
         <v>10.28638888888889</v>
@@ -4987,7 +4990,7 @@
         <v>28</v>
       </c>
       <c r="B319" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C319">
         <v>11.6375</v>
@@ -5001,7 +5004,7 @@
         <v>28</v>
       </c>
       <c r="B320" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C320">
         <v>8.300555555555556</v>
@@ -5015,7 +5018,7 @@
         <v>28</v>
       </c>
       <c r="B321" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C321">
         <v>8.294166666666667</v>
@@ -5029,7 +5032,7 @@
         <v>28</v>
       </c>
       <c r="B322" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C322">
         <v>8.652222222222223</v>
@@ -5043,7 +5046,7 @@
         <v>28</v>
       </c>
       <c r="B323" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C323">
         <v>3.089444444444445</v>
@@ -5057,7 +5060,7 @@
         <v>28</v>
       </c>
       <c r="B324" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C324">
         <v>3.726666666666667</v>
@@ -5071,7 +5074,7 @@
         <v>28</v>
       </c>
       <c r="B325" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C325">
         <v>5.495277777777778</v>
@@ -5085,7 +5088,7 @@
         <v>28</v>
       </c>
       <c r="B326" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C326">
         <v>6.546111111111111</v>
@@ -5099,7 +5102,7 @@
         <v>29</v>
       </c>
       <c r="B327" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C327">
         <v>0.6002777777777778</v>
@@ -5113,7 +5116,7 @@
         <v>29</v>
       </c>
       <c r="B328" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C328">
         <v>0.5758333333333333</v>
@@ -5127,7 +5130,7 @@
         <v>29</v>
       </c>
       <c r="B329" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C329">
         <v>0.5266666666666666</v>
@@ -5141,7 +5144,7 @@
         <v>29</v>
       </c>
       <c r="B330" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C330">
         <v>0.49</v>
@@ -5155,7 +5158,7 @@
         <v>29</v>
       </c>
       <c r="B331" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C331">
         <v>0.6125</v>
@@ -5169,7 +5172,7 @@
         <v>29</v>
       </c>
       <c r="B332" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C332">
         <v>0.5022222222222222</v>
@@ -5183,7 +5186,7 @@
         <v>29</v>
       </c>
       <c r="B333" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C333">
         <v>0.3841666666666667</v>
@@ -5197,7 +5200,7 @@
         <v>29</v>
       </c>
       <c r="B334" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C334">
         <v>0.3858333333333333</v>
@@ -5211,7 +5214,7 @@
         <v>29</v>
       </c>
       <c r="B335" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C335">
         <v>0.2163888888888889</v>
@@ -5225,7 +5228,7 @@
         <v>29</v>
       </c>
       <c r="B336" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C336">
         <v>0.2619444444444444</v>
@@ -5239,7 +5242,7 @@
         <v>29</v>
       </c>
       <c r="B337" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C337">
         <v>0.2669444444444444</v>
@@ -5253,7 +5256,7 @@
         <v>29</v>
       </c>
       <c r="B338" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C338">
         <v>0.3594444444444445</v>
@@ -5267,7 +5270,7 @@
         <v>29</v>
       </c>
       <c r="B339" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C339">
         <v>0.3875</v>
@@ -5281,7 +5284,7 @@
         <v>30</v>
       </c>
       <c r="B340" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C340">
         <v>76.64833333333333</v>
@@ -5295,7 +5298,7 @@
         <v>30</v>
       </c>
       <c r="B341" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C341">
         <v>80.90861111111111</v>
@@ -5309,7 +5312,7 @@
         <v>30</v>
       </c>
       <c r="B342" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C342">
         <v>74.14472222222223</v>
@@ -5323,7 +5326,7 @@
         <v>30</v>
       </c>
       <c r="B343" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C343">
         <v>68.93722222222222</v>
@@ -5337,7 +5340,7 @@
         <v>30</v>
       </c>
       <c r="B344" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C344">
         <v>61.8075</v>
@@ -5351,7 +5354,7 @@
         <v>30</v>
       </c>
       <c r="B345" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C345">
         <v>59.50416666666667</v>
@@ -5365,7 +5368,7 @@
         <v>30</v>
       </c>
       <c r="B346" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C346">
         <v>66.14611111111111</v>
@@ -5379,7 +5382,7 @@
         <v>30</v>
       </c>
       <c r="B347" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C347">
         <v>68.33222222222223</v>
@@ -5393,7 +5396,7 @@
         <v>30</v>
       </c>
       <c r="B348" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C348">
         <v>39.34722222222222</v>
@@ -5407,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="B349" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C349">
         <v>16.48944444444444</v>
@@ -5421,7 +5424,7 @@
         <v>30</v>
       </c>
       <c r="B350" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C350">
         <v>20.13666666666667</v>
@@ -5435,7 +5438,7 @@
         <v>30</v>
       </c>
       <c r="B351" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C351">
         <v>18.49861111111111</v>
@@ -5449,7 +5452,7 @@
         <v>30</v>
       </c>
       <c r="B352" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C352">
         <v>22.11</v>
@@ -5463,7 +5466,7 @@
         <v>31</v>
       </c>
       <c r="B353" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C353">
         <v>24.61027777777778</v>
@@ -5477,7 +5480,7 @@
         <v>31</v>
       </c>
       <c r="B354" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C354">
         <v>25.49222222222222</v>
@@ -5491,7 +5494,7 @@
         <v>31</v>
       </c>
       <c r="B355" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C355">
         <v>22.89527777777778</v>
@@ -5505,7 +5508,7 @@
         <v>31</v>
       </c>
       <c r="B356" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C356">
         <v>28.10138888888889</v>
@@ -5519,7 +5522,7 @@
         <v>31</v>
       </c>
       <c r="B357" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C357">
         <v>32.31555555555556</v>
@@ -5533,7 +5536,7 @@
         <v>31</v>
       </c>
       <c r="B358" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C358">
         <v>34.33666666666667</v>
@@ -5547,7 +5550,7 @@
         <v>31</v>
       </c>
       <c r="B359" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C359">
         <v>38.72222222222222</v>
@@ -5561,7 +5564,7 @@
         <v>31</v>
       </c>
       <c r="B360" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C360">
         <v>41.90722222222222</v>
@@ -5575,7 +5578,7 @@
         <v>31</v>
       </c>
       <c r="B361" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C361">
         <v>41.30694444444445</v>
@@ -5589,7 +5592,7 @@
         <v>31</v>
       </c>
       <c r="B362" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C362">
         <v>13.3525</v>
@@ -5603,7 +5606,7 @@
         <v>31</v>
       </c>
       <c r="B363" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C363">
         <v>13.00944444444444</v>
@@ -5617,7 +5620,7 @@
         <v>31</v>
       </c>
       <c r="B364" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C364">
         <v>32.64777777777778</v>
@@ -5631,7 +5634,7 @@
         <v>31</v>
       </c>
       <c r="B365" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C365">
         <v>43.29</v>
@@ -5645,7 +5648,7 @@
         <v>32</v>
       </c>
       <c r="B366" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C366">
         <v>18.31416666666667</v>
@@ -5659,7 +5662,7 @@
         <v>32</v>
       </c>
       <c r="B367" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C367">
         <v>17.65277777777778</v>
@@ -5673,7 +5676,7 @@
         <v>32</v>
       </c>
       <c r="B368" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C368">
         <v>17.00361111111111</v>
@@ -5687,7 +5690,7 @@
         <v>32</v>
       </c>
       <c r="B369" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C369">
         <v>16.57472222222222</v>
@@ -5701,7 +5704,7 @@
         <v>32</v>
       </c>
       <c r="B370" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C370">
         <v>17.56694444444445</v>
@@ -5715,7 +5718,7 @@
         <v>32</v>
       </c>
       <c r="B371" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C371">
         <v>19.88861111111111</v>
@@ -5729,7 +5732,7 @@
         <v>32</v>
       </c>
       <c r="B372" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C372">
         <v>23.93416666666667</v>
@@ -5743,7 +5746,7 @@
         <v>32</v>
       </c>
       <c r="B373" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C373">
         <v>19.43472222222222</v>
@@ -5757,7 +5760,7 @@
         <v>32</v>
       </c>
       <c r="B374" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C374">
         <v>17.78583333333333</v>
@@ -5771,7 +5774,7 @@
         <v>32</v>
       </c>
       <c r="B375" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C375">
         <v>7.890833333333333</v>
@@ -5785,7 +5788,7 @@
         <v>32</v>
       </c>
       <c r="B376" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C376">
         <v>6.443611111111111</v>
@@ -5799,7 +5802,7 @@
         <v>32</v>
       </c>
       <c r="B377" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C377">
         <v>9.902222222222223</v>
@@ -5813,7 +5816,7 @@
         <v>32</v>
       </c>
       <c r="B378" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C378">
         <v>12.71777777777778</v>
@@ -5827,7 +5830,7 @@
         <v>33</v>
       </c>
       <c r="B379" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C379">
         <v>46.64805555555556</v>
@@ -5841,7 +5844,7 @@
         <v>33</v>
       </c>
       <c r="B380" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C380">
         <v>46.6725</v>
@@ -5855,7 +5858,7 @@
         <v>33</v>
       </c>
       <c r="B381" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C381">
         <v>49.28166666666667</v>
@@ -5869,7 +5872,7 @@
         <v>33</v>
       </c>
       <c r="B382" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C382">
         <v>49.40416666666667</v>
@@ -5883,7 +5886,7 @@
         <v>33</v>
       </c>
       <c r="B383" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C383">
         <v>50.78861111111111</v>
@@ -5897,7 +5900,7 @@
         <v>33</v>
       </c>
       <c r="B384" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C384">
         <v>56.74194444444444</v>
@@ -5911,7 +5914,7 @@
         <v>33</v>
       </c>
       <c r="B385" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C385">
         <v>58.08944444444445</v>
@@ -5925,7 +5928,7 @@
         <v>33</v>
       </c>
       <c r="B386" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C386">
         <v>61.20111111111111</v>
@@ -5939,7 +5942,7 @@
         <v>33</v>
       </c>
       <c r="B387" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C387">
         <v>64.92472222222223</v>
@@ -5953,7 +5956,7 @@
         <v>33</v>
       </c>
       <c r="B388" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C388">
         <v>34.68694444444444</v>
@@ -5967,7 +5970,7 @@
         <v>33</v>
       </c>
       <c r="B389" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C389">
         <v>30.58861111111111</v>
@@ -5981,7 +5984,7 @@
         <v>33</v>
       </c>
       <c r="B390" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C390">
         <v>38.38694444444445</v>
@@ -5995,7 +5998,7 @@
         <v>33</v>
       </c>
       <c r="B391" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C391">
         <v>62.20138888888889</v>
@@ -6009,7 +6012,7 @@
         <v>34</v>
       </c>
       <c r="B392" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C392">
         <v>1.176111111111111</v>
@@ -6023,7 +6026,7 @@
         <v>34</v>
       </c>
       <c r="B393" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C393">
         <v>1.212777777777778</v>
@@ -6037,7 +6040,7 @@
         <v>34</v>
       </c>
       <c r="B394" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C394">
         <v>1.176111111111111</v>
@@ -6051,7 +6054,7 @@
         <v>34</v>
       </c>
       <c r="B395" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C395">
         <v>1.273888888888889</v>
@@ -6065,7 +6068,7 @@
         <v>34</v>
       </c>
       <c r="B396" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C396">
         <v>1.273888888888889</v>
@@ -6079,7 +6082,7 @@
         <v>34</v>
       </c>
       <c r="B397" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C397">
         <v>1.335277777777778</v>
@@ -6093,7 +6096,7 @@
         <v>34</v>
       </c>
       <c r="B398" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C398">
         <v>1.596388888888889</v>
@@ -6107,7 +6110,7 @@
         <v>34</v>
       </c>
       <c r="B399" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C399">
         <v>1.721111111111111</v>
@@ -6121,7 +6124,7 @@
         <v>34</v>
       </c>
       <c r="B400" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C400">
         <v>1.937777777777778</v>
@@ -6135,7 +6138,7 @@
         <v>34</v>
       </c>
       <c r="B401" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C401">
         <v>0.9813888888888889</v>
@@ -6149,7 +6152,7 @@
         <v>34</v>
       </c>
       <c r="B402" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C402">
         <v>1.290277777777778</v>
@@ -6163,7 +6166,7 @@
         <v>34</v>
       </c>
       <c r="B403" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C403">
         <v>1.577222222222222</v>
@@ -6177,7 +6180,7 @@
         <v>34</v>
       </c>
       <c r="B404" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C404">
         <v>1.848333333333333</v>
@@ -6191,7 +6194,7 @@
         <v>35</v>
       </c>
       <c r="B405" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C405">
         <v>2.866388888888889</v>
@@ -6205,7 +6208,7 @@
         <v>35</v>
       </c>
       <c r="B406" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C406">
         <v>3.454444444444444</v>
@@ -6219,7 +6222,7 @@
         <v>35</v>
       </c>
       <c r="B407" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C407">
         <v>3.466666666666667</v>
@@ -6233,7 +6236,7 @@
         <v>35</v>
       </c>
       <c r="B408" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C408">
         <v>3.233888888888889</v>
@@ -6247,7 +6250,7 @@
         <v>35</v>
       </c>
       <c r="B409" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C409">
         <v>2.474444444444444</v>
@@ -6261,7 +6264,7 @@
         <v>35</v>
       </c>
       <c r="B410" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C410">
         <v>2.633611111111111</v>
@@ -6275,7 +6278,7 @@
         <v>35</v>
       </c>
       <c r="B411" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C411">
         <v>3.074722222222222</v>
@@ -6289,7 +6292,7 @@
         <v>35</v>
       </c>
       <c r="B412" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C412">
         <v>3.478888888888889</v>
@@ -6303,7 +6306,7 @@
         <v>35</v>
       </c>
       <c r="B413" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C413">
         <v>3.674722222222222</v>
@@ -6317,7 +6320,7 @@
         <v>35</v>
       </c>
       <c r="B414" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C414">
         <v>1.237222222222222</v>
@@ -6331,7 +6334,7 @@
         <v>35</v>
       </c>
       <c r="B415" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C415">
         <v>1.564444444444445</v>
@@ -6345,7 +6348,7 @@
         <v>35</v>
       </c>
       <c r="B416" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C416">
         <v>2.598333333333333</v>
@@ -6359,7 +6362,7 @@
         <v>35</v>
       </c>
       <c r="B417" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C417">
         <v>3.003055555555556</v>
@@ -6373,7 +6376,7 @@
         <v>36</v>
       </c>
       <c r="B418" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C418">
         <v>133.2677777777778</v>
@@ -6387,7 +6390,7 @@
         <v>36</v>
       </c>
       <c r="B419" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C419">
         <v>129.2008333333333</v>
@@ -6401,7 +6404,7 @@
         <v>36</v>
       </c>
       <c r="B420" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C420">
         <v>128.0736111111111</v>
@@ -6415,7 +6418,7 @@
         <v>36</v>
       </c>
       <c r="B421" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C421">
         <v>128.0255555555555</v>
@@ -6429,7 +6432,7 @@
         <v>36</v>
       </c>
       <c r="B422" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C422">
         <v>129.2380555555555</v>
@@ -6443,7 +6446,7 @@
         <v>36</v>
       </c>
       <c r="B423" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C423">
         <v>129.3238888888889</v>
@@ -6457,7 +6460,7 @@
         <v>36</v>
       </c>
       <c r="B424" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C424">
         <v>138.9427777777778</v>
@@ -6471,7 +6474,7 @@
         <v>36</v>
       </c>
       <c r="B425" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C425">
         <v>139.9469444444445</v>
@@ -6485,7 +6488,7 @@
         <v>36</v>
       </c>
       <c r="B426" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C426">
         <v>140.3980555555555</v>
@@ -6499,7 +6502,7 @@
         <v>36</v>
       </c>
       <c r="B427" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C427">
         <v>58.20027777777778</v>
@@ -6513,7 +6516,7 @@
         <v>36</v>
       </c>
       <c r="B428" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C428">
         <v>55.26777777777778</v>
@@ -6527,7 +6530,7 @@
         <v>36</v>
       </c>
       <c r="B429" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C429">
         <v>109.3866666666667</v>
@@ -6541,7 +6544,7 @@
         <v>36</v>
       </c>
       <c r="B430" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C430">
         <v>127.6063888888889</v>
@@ -6555,7 +6558,7 @@
         <v>37</v>
       </c>
       <c r="B431" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C431">
         <v>251.2230555555556</v>
@@ -6569,7 +6572,7 @@
         <v>37</v>
       </c>
       <c r="B432" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C432">
         <v>237.2580555555556</v>
@@ -6583,7 +6586,7 @@
         <v>37</v>
       </c>
       <c r="B433" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C433">
         <v>242.3786111111111</v>
@@ -6597,7 +6600,7 @@
         <v>37</v>
       </c>
       <c r="B434" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C434">
         <v>248.5769444444445</v>
@@ -6611,7 +6614,7 @@
         <v>37</v>
       </c>
       <c r="B435" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C435">
         <v>272.5625</v>
@@ -6625,7 +6628,7 @@
         <v>37</v>
       </c>
       <c r="B436" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C436">
         <v>283.1463888888889</v>
@@ -6639,7 +6642,7 @@
         <v>37</v>
       </c>
       <c r="B437" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C437">
         <v>285.1633333333334</v>
@@ -6653,7 +6656,7 @@
         <v>37</v>
       </c>
       <c r="B438" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C438">
         <v>289.5675</v>
@@ -6667,7 +6670,7 @@
         <v>37</v>
       </c>
       <c r="B439" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C439">
         <v>294.49</v>
@@ -6681,7 +6684,7 @@
         <v>37</v>
       </c>
       <c r="B440" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C440">
         <v>182.2222222222222</v>
@@ -6695,7 +6698,7 @@
         <v>37</v>
       </c>
       <c r="B441" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C441">
         <v>231.5616666666667</v>
@@ -6709,7 +6712,7 @@
         <v>37</v>
       </c>
       <c r="B442" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C442">
         <v>263.5433333333334</v>
@@ -6723,7 +6726,7 @@
         <v>37</v>
       </c>
       <c r="B443" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C443">
         <v>281.2844444444444</v>
@@ -6737,13 +6740,13 @@
         <v>38</v>
       </c>
       <c r="B444" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C444">
-        <v>1.580277777777778</v>
+        <v>1.129444444444444</v>
       </c>
       <c r="D444">
-        <v>3.891944444444444</v>
+        <v>4.313333333333333</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6751,13 +6754,13 @@
         <v>38</v>
       </c>
       <c r="B445" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C445">
-        <v>0.9186111111111112</v>
+        <v>1.120833333333333</v>
       </c>
       <c r="D445">
-        <v>3.616944444444445</v>
+        <v>3.272222222222222</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6765,13 +6768,13 @@
         <v>38</v>
       </c>
       <c r="B446" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C446">
-        <v>1.482222222222222</v>
+        <v>0.8611111111111112</v>
       </c>
       <c r="D446">
-        <v>3.159444444444444</v>
+        <v>2.668333333333333</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6779,13 +6782,13 @@
         <v>38</v>
       </c>
       <c r="B447" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C447">
-        <v>2.339722222222222</v>
+        <v>0.9627777777777777</v>
       </c>
       <c r="D447">
-        <v>2.93</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6793,13 +6796,13 @@
         <v>38</v>
       </c>
       <c r="B448" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C448">
-        <v>5.353333333333333</v>
+        <v>1.133055555555555</v>
       </c>
       <c r="D448">
-        <v>2.746666666666667</v>
+        <v>2.049166666666667</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -6807,13 +6810,13 @@
         <v>38</v>
       </c>
       <c r="B449" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C449">
-        <v>3.895555555555556</v>
+        <v>1.171111111111111</v>
       </c>
       <c r="D449">
-        <v>2.277222222222222</v>
+        <v>1.555277777777778</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6821,13 +6824,13 @@
         <v>38</v>
       </c>
       <c r="B450" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C450">
-        <v>3.930277777777778</v>
+        <v>1.194444444444444</v>
       </c>
       <c r="D450">
-        <v>1.920277777777778</v>
+        <v>1.213888888888889</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -6835,13 +6838,13 @@
         <v>38</v>
       </c>
       <c r="B451" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C451">
-        <v>3.729166666666667</v>
+        <v>1.28</v>
       </c>
       <c r="D451">
-        <v>1.543055555555556</v>
+        <v>1.668055555555556</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6849,13 +6852,13 @@
         <v>38</v>
       </c>
       <c r="B452" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C452">
-        <v>2.942777777777778</v>
+        <v>1.189444444444445</v>
       </c>
       <c r="D452">
-        <v>1.116111111111111</v>
+        <v>1.821111111111111</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6863,13 +6866,13 @@
         <v>38</v>
       </c>
       <c r="B453" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C453">
-        <v>1.018611111111111</v>
+        <v>0.5194444444444445</v>
       </c>
       <c r="D453">
-        <v>0.7813888888888889</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -6877,13 +6880,13 @@
         <v>38</v>
       </c>
       <c r="B454" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C454">
-        <v>1.962777777777778</v>
+        <v>0.5169444444444444</v>
       </c>
       <c r="D454">
-        <v>0.7891666666666667</v>
+        <v>1.058888888888889</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -6891,13 +6894,13 @@
         <v>38</v>
       </c>
       <c r="B455" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C455">
-        <v>3.623611111111111</v>
+        <v>0.9002777777777777</v>
       </c>
       <c r="D455">
-        <v>0.8522222222222222</v>
+        <v>1.123055555555555</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -6905,12 +6908,194 @@
         <v>38</v>
       </c>
       <c r="B456" t="s">
+        <v>52</v>
+      </c>
+      <c r="C456">
+        <v>1.116111111111111</v>
+      </c>
+      <c r="D456">
+        <v>1.143055555555555</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" t="s">
+        <v>39</v>
+      </c>
+      <c r="B457" t="s">
+        <v>40</v>
+      </c>
+      <c r="C457">
+        <v>1.580277777777778</v>
+      </c>
+      <c r="D457">
+        <v>3.891944444444444</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" t="s">
+        <v>39</v>
+      </c>
+      <c r="B458" t="s">
+        <v>41</v>
+      </c>
+      <c r="C458">
+        <v>0.9186111111111112</v>
+      </c>
+      <c r="D458">
+        <v>3.616944444444445</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" t="s">
+        <v>39</v>
+      </c>
+      <c r="B459" t="s">
+        <v>42</v>
+      </c>
+      <c r="C459">
+        <v>1.482222222222222</v>
+      </c>
+      <c r="D459">
+        <v>3.159444444444444</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" t="s">
+        <v>39</v>
+      </c>
+      <c r="B460" t="s">
+        <v>43</v>
+      </c>
+      <c r="C460">
+        <v>2.339722222222222</v>
+      </c>
+      <c r="D460">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" t="s">
+        <v>39</v>
+      </c>
+      <c r="B461" t="s">
+        <v>44</v>
+      </c>
+      <c r="C461">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="D461">
+        <v>2.746666666666667</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" t="s">
+        <v>39</v>
+      </c>
+      <c r="B462" t="s">
+        <v>45</v>
+      </c>
+      <c r="C462">
+        <v>3.895555555555556</v>
+      </c>
+      <c r="D462">
+        <v>2.277222222222222</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463" t="s">
+        <v>39</v>
+      </c>
+      <c r="B463" t="s">
+        <v>46</v>
+      </c>
+      <c r="C463">
+        <v>3.930277777777778</v>
+      </c>
+      <c r="D463">
+        <v>1.920277777777778</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" t="s">
+        <v>39</v>
+      </c>
+      <c r="B464" t="s">
+        <v>47</v>
+      </c>
+      <c r="C464">
+        <v>3.729166666666667</v>
+      </c>
+      <c r="D464">
+        <v>1.543055555555556</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" t="s">
+        <v>39</v>
+      </c>
+      <c r="B465" t="s">
+        <v>48</v>
+      </c>
+      <c r="C465">
+        <v>2.942777777777778</v>
+      </c>
+      <c r="D465">
+        <v>1.116111111111111</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" t="s">
+        <v>39</v>
+      </c>
+      <c r="B466" t="s">
+        <v>49</v>
+      </c>
+      <c r="C466">
+        <v>1.018611111111111</v>
+      </c>
+      <c r="D466">
+        <v>0.7813888888888889</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" t="s">
+        <v>39</v>
+      </c>
+      <c r="B467" t="s">
+        <v>50</v>
+      </c>
+      <c r="C467">
+        <v>1.962777777777778</v>
+      </c>
+      <c r="D467">
+        <v>0.7891666666666667</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" t="s">
+        <v>39</v>
+      </c>
+      <c r="B468" t="s">
         <v>51</v>
       </c>
-      <c r="C456">
+      <c r="C468">
+        <v>3.623611111111111</v>
+      </c>
+      <c r="D468">
+        <v>0.8522222222222222</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" t="s">
+        <v>39</v>
+      </c>
+      <c r="B469" t="s">
+        <v>52</v>
+      </c>
+      <c r="C469">
         <v>5.216666666666667</v>
       </c>
-      <c r="D456">
+      <c r="D469">
         <v>0.8863888888888889</v>
       </c>
     </row>

--- a/transport/input_data/global/international_marine_and_aviation_data.xlsx
+++ b/transport/input_data/global/international_marine_and_aviation_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="54">
   <si>
     <t>Country</t>
   </si>
@@ -106,6 +106,9 @@
     <t>Republic of Congo</t>
   </si>
   <si>
+    <t>Republic of the Congo</t>
+  </si>
+  <si>
     <t>Russia</t>
   </si>
   <si>
@@ -128,6 +131,9 @@
   </si>
   <si>
     <t>United States of America</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
   </si>
   <si>
     <t>Venezuela</t>
@@ -527,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D456"/>
+  <dimension ref="A1:D482"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -549,7 +555,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2">
         <v>5.561388888888889</v>
@@ -563,7 +569,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3">
         <v>6.198611111111111</v>
@@ -577,7 +583,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4">
         <v>6.406666666666666</v>
@@ -591,7 +597,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5">
         <v>5.083611111111111</v>
@@ -605,7 +611,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C6">
         <v>5.561388888888889</v>
@@ -619,7 +625,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7">
         <v>4.618333333333333</v>
@@ -633,7 +639,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8">
         <v>4.348611111111111</v>
@@ -647,7 +653,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C9">
         <v>5.316388888888889</v>
@@ -661,7 +667,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C10">
         <v>4.336388888888889</v>
@@ -675,7 +681,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C11">
         <v>2.658333333333333</v>
@@ -689,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12">
         <v>2.731666666666666</v>
@@ -703,7 +709,7 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C13">
         <v>4.266944444444444</v>
@@ -717,7 +723,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C14">
         <v>6.777222222222222</v>
@@ -731,7 +737,7 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>8.501388888888888</v>
@@ -745,7 +751,7 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>8.489166666666666</v>
@@ -759,7 +765,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>10.89027777777778</v>
@@ -773,7 +779,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>10.79222222222222</v>
@@ -787,7 +793,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <v>10.97611111111111</v>
@@ -801,7 +807,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C20">
         <v>11.33111111111111</v>
@@ -815,7 +821,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>12.02944444444444</v>
@@ -829,7 +835,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C22">
         <v>10.93916666666667</v>
@@ -843,7 +849,7 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C23">
         <v>10.80444444444444</v>
@@ -857,7 +863,7 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C24">
         <v>4.613333333333333</v>
@@ -871,7 +877,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C25">
         <v>4.65</v>
@@ -885,7 +891,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C26">
         <v>9.015277777777778</v>
@@ -899,7 +905,7 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C27">
         <v>11.62527777777778</v>
@@ -913,7 +919,7 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C28">
         <v>38.28111111111111</v>
@@ -927,7 +933,7 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C29">
         <v>39.72666666666667</v>
@@ -941,7 +947,7 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C30">
         <v>41.82138888888889</v>
@@ -955,7 +961,7 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C31">
         <v>45.11666666666667</v>
@@ -969,7 +975,7 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C32">
         <v>44.835</v>
@@ -983,7 +989,7 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C33">
         <v>47.8975</v>
@@ -997,7 +1003,7 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C34">
         <v>51.63</v>
@@ -1011,7 +1017,7 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C35">
         <v>54.68305555555555</v>
@@ -1025,7 +1031,7 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C36">
         <v>58.1825</v>
@@ -1039,7 +1045,7 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C37">
         <v>44.60027777777778</v>
@@ -1053,7 +1059,7 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C38">
         <v>14.56805555555556</v>
@@ -1067,7 +1073,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C39">
         <v>20.40527777777778</v>
@@ -1081,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C40">
         <v>36.60055555555556</v>
@@ -1095,7 +1101,7 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C41">
         <v>25.16138888888889</v>
@@ -1109,7 +1115,7 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C42">
         <v>26.15361111111111</v>
@@ -1123,7 +1129,7 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C43">
         <v>27.29305555555555</v>
@@ -1137,7 +1143,7 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C44">
         <v>29.16722222222222</v>
@@ -1151,7 +1157,7 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C45">
         <v>28.48111111111111</v>
@@ -1165,7 +1171,7 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C46">
         <v>26.43555555555556</v>
@@ -1179,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C47">
         <v>25.8475</v>
@@ -1193,7 +1199,7 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C48">
         <v>29.30194444444444</v>
@@ -1207,7 +1213,7 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C49">
         <v>28.38333333333333</v>
@@ -1221,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C50">
         <v>11.95611111111111</v>
@@ -1235,7 +1241,7 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C51">
         <v>12.82416666666667</v>
@@ -1249,7 +1255,7 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C52">
         <v>20.87722222222222</v>
@@ -1263,7 +1269,7 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C53">
         <v>24.48527777777778</v>
@@ -1277,7 +1283,7 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C54">
         <v>35.95388888888889</v>
@@ -1291,7 +1297,7 @@
         <v>8</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C55">
         <v>40.59666666666666</v>
@@ -1305,7 +1311,7 @@
         <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C56">
         <v>42.37277777777778</v>
@@ -1319,7 +1325,7 @@
         <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C57">
         <v>42.0175</v>
@@ -1333,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C58">
         <v>43.49972222222222</v>
@@ -1347,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C59">
         <v>45.76611111111111</v>
@@ -1361,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C60">
         <v>50.08888888888889</v>
@@ -1375,7 +1381,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C61">
         <v>57.17388888888889</v>
@@ -1389,7 +1395,7 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C62">
         <v>57.77027777777778</v>
@@ -1403,7 +1409,7 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C63">
         <v>25.07194444444444</v>
@@ -1417,7 +1423,7 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C64">
         <v>25.18222222222222</v>
@@ -1431,7 +1437,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C65">
         <v>43.41583333333333</v>
@@ -1445,7 +1451,7 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C66">
         <v>51.6675</v>
@@ -1459,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C67">
         <v>5.083611111111111</v>
@@ -1473,7 +1479,7 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C68">
         <v>8.183055555555555</v>
@@ -1487,7 +1493,7 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C69">
         <v>7.239722222222222</v>
@@ -1501,7 +1507,7 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C70">
         <v>7.533611111111111</v>
@@ -1515,7 +1521,7 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C71">
         <v>6.516944444444444</v>
@@ -1529,7 +1535,7 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C72">
         <v>6.713055555555556</v>
@@ -1543,7 +1549,7 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C73">
         <v>7.091944444444445</v>
@@ -1557,7 +1563,7 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C74">
         <v>7.791388888888889</v>
@@ -1571,7 +1577,7 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C75">
         <v>8.836666666666666</v>
@@ -1585,7 +1591,7 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C76">
         <v>4.733333333333333</v>
@@ -1599,7 +1605,7 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C77">
         <v>5.256111111111111</v>
@@ -1613,7 +1619,7 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C78">
         <v>7.254166666666666</v>
@@ -1627,7 +1633,7 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C79">
         <v>8.060833333333333</v>
@@ -1641,7 +1647,7 @@
         <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C80">
         <v>69.01666666666667</v>
@@ -1655,7 +1661,7 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C81">
         <v>72.67277777777778</v>
@@ -1669,7 +1675,7 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C82">
         <v>77.78277777777778</v>
@@ -1683,7 +1689,7 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C83">
         <v>85.28333333333333</v>
@@ -1697,7 +1703,7 @@
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C84">
         <v>92.75944444444444</v>
@@ -1711,7 +1717,7 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C85">
         <v>102.4466666666667</v>
@@ -1725,7 +1731,7 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C86">
         <v>113.7425</v>
@@ -1739,7 +1745,7 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C87">
         <v>123.6858333333333</v>
@@ -1753,7 +1759,7 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C88">
         <v>127.5972222222222</v>
@@ -1767,7 +1773,7 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C89">
         <v>58.44472222222223</v>
@@ -1781,7 +1787,7 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C90">
         <v>53.64277777777778</v>
@@ -1795,7 +1801,7 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C91">
         <v>47.18444444444444</v>
@@ -1809,7 +1815,7 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C92">
         <v>73.82083333333334</v>
@@ -1823,7 +1829,7 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C93">
         <v>5.524722222222223</v>
@@ -1837,7 +1843,7 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C94">
         <v>6.051388888888889</v>
@@ -1851,7 +1857,7 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C95">
         <v>6.37</v>
@@ -1865,7 +1871,7 @@
         <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C96">
         <v>8.183055555555555</v>
@@ -1879,7 +1885,7 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C97">
         <v>8.832222222222223</v>
@@ -1893,7 +1899,7 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C98">
         <v>8.86888888888889</v>
@@ -1907,7 +1913,7 @@
         <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C99">
         <v>9.088333333333333</v>
@@ -1921,7 +1927,7 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C100">
         <v>10.39055555555556</v>
@@ -1935,7 +1941,7 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C101">
         <v>10.5775</v>
@@ -1949,7 +1955,7 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C102">
         <v>4.895833333333333</v>
@@ -1963,7 +1969,7 @@
         <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C103">
         <v>5.739166666666667</v>
@@ -1977,7 +1983,7 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C104">
         <v>11.20555555555556</v>
@@ -1991,7 +1997,7 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C105">
         <v>10.44277777777778</v>
@@ -2005,7 +2011,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C106">
         <v>9.444722222222222</v>
@@ -2019,7 +2025,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C107">
         <v>9.983611111111111</v>
@@ -2033,7 +2039,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C108">
         <v>6.908888888888889</v>
@@ -2047,7 +2053,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C109">
         <v>8.146111111111111</v>
@@ -2061,7 +2067,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C110">
         <v>6.198611111111111</v>
@@ -2075,7 +2081,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C111">
         <v>5.206111111111111</v>
@@ -2089,7 +2095,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C112">
         <v>7.643888888888889</v>
@@ -2103,7 +2109,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C113">
         <v>8.795555555555556</v>
@@ -2117,7 +2123,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C114">
         <v>7.852222222222222</v>
@@ -2131,7 +2137,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C115">
         <v>3.7425</v>
@@ -2145,7 +2151,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C116">
         <v>3.273611111111111</v>
@@ -2159,7 +2165,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C117">
         <v>3.124444444444444</v>
@@ -2173,7 +2179,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C118">
         <v>12.59305555555556</v>
@@ -2187,7 +2193,7 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C119">
         <v>3.601388888888889</v>
@@ -2201,7 +2207,7 @@
         <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C120">
         <v>4.311944444444444</v>
@@ -2215,7 +2221,7 @@
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C121">
         <v>4.667222222222223</v>
@@ -2229,7 +2235,7 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C122">
         <v>5.255277777777778</v>
@@ -2243,7 +2249,7 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C123">
         <v>5.573611111111111</v>
@@ -2257,7 +2263,7 @@
         <v>13</v>
       </c>
       <c r="B124" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C124">
         <v>7.203055555555555</v>
@@ -2271,7 +2277,7 @@
         <v>13</v>
       </c>
       <c r="B125" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C125">
         <v>8.359166666666667</v>
@@ -2285,7 +2291,7 @@
         <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C126">
         <v>8.955555555555556</v>
@@ -2299,7 +2305,7 @@
         <v>13</v>
       </c>
       <c r="B127" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C127">
         <v>10.045</v>
@@ -2313,7 +2319,7 @@
         <v>13</v>
       </c>
       <c r="B128" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C128">
         <v>4.641666666666667</v>
@@ -2327,7 +2333,7 @@
         <v>13</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C129">
         <v>10.10444444444444</v>
@@ -2341,7 +2347,7 @@
         <v>13</v>
       </c>
       <c r="B130" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C130">
         <v>11.57111111111111</v>
@@ -2355,7 +2361,7 @@
         <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C131">
         <v>13.60027777777778</v>
@@ -2369,7 +2375,7 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C132">
         <v>65.75805555555556</v>
@@ -2383,7 +2389,7 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C133">
         <v>64.36138888888888</v>
@@ -2397,7 +2403,7 @@
         <v>14</v>
       </c>
       <c r="B134" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C134">
         <v>63.79805555555556</v>
@@ -2411,7 +2417,7 @@
         <v>14</v>
       </c>
       <c r="B135" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C135">
         <v>64.41055555555556</v>
@@ -2425,7 +2431,7 @@
         <v>14</v>
       </c>
       <c r="B136" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C136">
         <v>68.19583333333334</v>
@@ -2439,7 +2445,7 @@
         <v>14</v>
       </c>
       <c r="B137" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C137">
         <v>67.06861111111111</v>
@@ -2453,7 +2459,7 @@
         <v>14</v>
       </c>
       <c r="B138" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C138">
         <v>68.12666666666667</v>
@@ -2467,7 +2473,7 @@
         <v>14</v>
       </c>
       <c r="B139" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C139">
         <v>70.50722222222223</v>
@@ -2481,7 +2487,7 @@
         <v>14</v>
       </c>
       <c r="B140" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C140">
         <v>74.05527777777777</v>
@@ -2495,7 +2501,7 @@
         <v>14</v>
       </c>
       <c r="B141" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C141">
         <v>31.44361111111111</v>
@@ -2509,7 +2515,7 @@
         <v>14</v>
       </c>
       <c r="B142" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C142">
         <v>34.19</v>
@@ -2523,7 +2529,7 @@
         <v>14</v>
       </c>
       <c r="B143" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C143">
         <v>58.5775</v>
@@ -2537,7 +2543,7 @@
         <v>14</v>
       </c>
       <c r="B144" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C144">
         <v>64.37638888888888</v>
@@ -2551,7 +2557,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C145">
         <v>91.74027777777778</v>
@@ -2565,7 +2571,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C146">
         <v>97.8775</v>
@@ -2579,7 +2585,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C147">
         <v>99.83750000000001</v>
@@ -2593,7 +2599,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C148">
         <v>95.86861111111111</v>
@@ -2607,7 +2613,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C149">
         <v>95.99111111111111</v>
@@ -2621,7 +2627,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C150">
         <v>103.2552777777778</v>
@@ -2635,7 +2641,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C151">
         <v>114.1577777777778</v>
@@ -2649,7 +2655,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C152">
         <v>117.7347222222222</v>
@@ -2663,7 +2669,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C153">
         <v>116.7669444444444</v>
@@ -2677,7 +2683,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C154">
         <v>53.99805555555555</v>
@@ -2691,7 +2697,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C155">
         <v>72.11583333333333</v>
@@ -2705,7 +2711,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C156">
         <v>107.1752777777778</v>
@@ -2719,7 +2725,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C157">
         <v>111.7566666666667</v>
@@ -2733,7 +2739,7 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C158">
         <v>1.646666666666667</v>
@@ -2747,7 +2753,7 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C159">
         <v>1.690833333333333</v>
@@ -2761,7 +2767,7 @@
         <v>16</v>
       </c>
       <c r="B160" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C160">
         <v>1.596666666666667</v>
@@ -2775,7 +2781,7 @@
         <v>16</v>
       </c>
       <c r="B161" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C161">
         <v>1.391944444444444</v>
@@ -2789,7 +2795,7 @@
         <v>16</v>
       </c>
       <c r="B162" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C162">
         <v>1.223333333333333</v>
@@ -2803,7 +2809,7 @@
         <v>16</v>
       </c>
       <c r="B163" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C163">
         <v>1.598055555555556</v>
@@ -2817,7 +2823,7 @@
         <v>16</v>
       </c>
       <c r="B164" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C164">
         <v>1.749722222222222</v>
@@ -2831,7 +2837,7 @@
         <v>16</v>
       </c>
       <c r="B165" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C165">
         <v>2.136388888888889</v>
@@ -2845,7 +2851,7 @@
         <v>16</v>
       </c>
       <c r="B166" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C166">
         <v>2.599444444444444</v>
@@ -2859,7 +2865,7 @@
         <v>16</v>
       </c>
       <c r="B167" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C167">
         <v>1.476111111111111</v>
@@ -2873,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="B168" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C168">
         <v>2.341388888888889</v>
@@ -2887,7 +2893,7 @@
         <v>16</v>
       </c>
       <c r="B169" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C169">
         <v>2.345</v>
@@ -2901,7 +2907,7 @@
         <v>16</v>
       </c>
       <c r="B170" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C170">
         <v>2.386111111111111</v>
@@ -2915,7 +2921,7 @@
         <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C171">
         <v>57.80777777777778</v>
@@ -2929,7 +2935,7 @@
         <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C172">
         <v>57.80777777777778</v>
@@ -2943,7 +2949,7 @@
         <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C173">
         <v>47.19916666666666</v>
@@ -2957,7 +2963,7 @@
         <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C174">
         <v>46.52555555555556</v>
@@ -2971,7 +2977,7 @@
         <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C175">
         <v>53.69166666666667</v>
@@ -2985,7 +2991,7 @@
         <v>17</v>
       </c>
       <c r="B176" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C176">
         <v>60.01277777777778</v>
@@ -2999,7 +3005,7 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C177">
         <v>46.45194444444444</v>
@@ -3013,7 +3019,7 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C178">
         <v>50.58027777777778</v>
@@ -3027,7 +3033,7 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C179">
         <v>48.74277777777777</v>
@@ -3041,7 +3047,7 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C180">
         <v>15.64333333333333</v>
@@ -3055,7 +3061,7 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C181">
         <v>21.44972222222222</v>
@@ -3069,7 +3075,7 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C182">
         <v>37.84027777777778</v>
@@ -3083,7 +3089,7 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C183">
         <v>47.39111111111111</v>
@@ -3097,7 +3103,7 @@
         <v>18</v>
       </c>
       <c r="B184" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C184">
         <v>8.33</v>
@@ -3111,7 +3117,7 @@
         <v>18</v>
       </c>
       <c r="B185" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C185">
         <v>8.844444444444445</v>
@@ -3125,7 +3131,7 @@
         <v>18</v>
       </c>
       <c r="B186" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C186">
         <v>10.94416666666667</v>
@@ -3139,7 +3145,7 @@
         <v>18</v>
       </c>
       <c r="B187" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C187">
         <v>15.89555555555556</v>
@@ -3153,7 +3159,7 @@
         <v>18</v>
       </c>
       <c r="B188" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C188">
         <v>10.23083333333333</v>
@@ -3167,7 +3173,7 @@
         <v>18</v>
       </c>
       <c r="B189" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C189">
         <v>9.493611111111111</v>
@@ -3181,7 +3187,7 @@
         <v>18</v>
       </c>
       <c r="B190" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C190">
         <v>11.80666666666667</v>
@@ -3195,7 +3201,7 @@
         <v>18</v>
       </c>
       <c r="B191" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C191">
         <v>12.65805555555556</v>
@@ -3209,7 +3215,7 @@
         <v>18</v>
       </c>
       <c r="B192" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C192">
         <v>11.22222222222222</v>
@@ -3223,7 +3229,7 @@
         <v>18</v>
       </c>
       <c r="B193" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C193">
         <v>5.414444444444444</v>
@@ -3237,7 +3243,7 @@
         <v>18</v>
       </c>
       <c r="B194" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C194">
         <v>2.246666666666667</v>
@@ -3251,7 +3257,7 @@
         <v>18</v>
       </c>
       <c r="B195" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C195">
         <v>2.540277777777778</v>
@@ -3265,7 +3271,7 @@
         <v>18</v>
       </c>
       <c r="B196" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C196">
         <v>7.815</v>
@@ -3279,7 +3285,7 @@
         <v>19</v>
       </c>
       <c r="B197" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C197">
         <v>38.75888888888889</v>
@@ -3293,7 +3299,7 @@
         <v>19</v>
       </c>
       <c r="B198" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C198">
         <v>36.98277777777778</v>
@@ -3307,7 +3313,7 @@
         <v>19</v>
       </c>
       <c r="B199" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C199">
         <v>35.79444444444444</v>
@@ -3321,7 +3327,7 @@
         <v>19</v>
       </c>
       <c r="B200" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C200">
         <v>36.68861111111111</v>
@@ -3335,7 +3341,7 @@
         <v>19</v>
       </c>
       <c r="B201" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C201">
         <v>37.76666666666667</v>
@@ -3349,7 +3355,7 @@
         <v>19</v>
       </c>
       <c r="B202" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C202">
         <v>39.31027777777778</v>
@@ -3363,7 +3369,7 @@
         <v>19</v>
       </c>
       <c r="B203" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C203">
         <v>40.78222222222222</v>
@@ -3377,7 +3383,7 @@
         <v>19</v>
       </c>
       <c r="B204" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C204">
         <v>45.74027777777778</v>
@@ -3391,7 +3397,7 @@
         <v>19</v>
       </c>
       <c r="B205" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C205">
         <v>47.33444444444444</v>
@@ -3405,7 +3411,7 @@
         <v>19</v>
       </c>
       <c r="B206" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C206">
         <v>17.83083333333333</v>
@@ -3419,7 +3425,7 @@
         <v>19</v>
       </c>
       <c r="B207" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C207">
         <v>19.46805555555556</v>
@@ -3433,7 +3439,7 @@
         <v>19</v>
       </c>
       <c r="B208" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C208">
         <v>33.92527777777778</v>
@@ -3447,7 +3453,7 @@
         <v>19</v>
       </c>
       <c r="B209" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C209">
         <v>42.93805555555556</v>
@@ -3461,7 +3467,7 @@
         <v>20</v>
       </c>
       <c r="B210" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C210">
         <v>71.07444444444444</v>
@@ -3475,7 +3481,7 @@
         <v>20</v>
       </c>
       <c r="B211" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C211">
         <v>74.55361111111111</v>
@@ -3489,7 +3495,7 @@
         <v>20</v>
       </c>
       <c r="B212" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C212">
         <v>75.53361111111111</v>
@@ -3503,7 +3509,7 @@
         <v>20</v>
       </c>
       <c r="B213" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C213">
         <v>73.81861111111111</v>
@@ -3517,7 +3523,7 @@
         <v>20</v>
       </c>
       <c r="B214" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C214">
         <v>74.43111111111111</v>
@@ -3531,7 +3537,7 @@
         <v>20</v>
       </c>
       <c r="B215" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C215">
         <v>77.82416666666667</v>
@@ -3545,7 +3551,7 @@
         <v>20</v>
       </c>
       <c r="B216" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C216">
         <v>81.48583333333333</v>
@@ -3559,7 +3565,7 @@
         <v>20</v>
       </c>
       <c r="B217" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C217">
         <v>83.79527777777778</v>
@@ -3573,7 +3579,7 @@
         <v>20</v>
       </c>
       <c r="B218" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C218">
         <v>84.10472222222222</v>
@@ -3587,7 +3593,7 @@
         <v>20</v>
       </c>
       <c r="B219" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C219">
         <v>33.12833333333333</v>
@@ -3601,7 +3607,7 @@
         <v>20</v>
       </c>
       <c r="B220" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C220">
         <v>46.12833333333333</v>
@@ -3615,7 +3621,7 @@
         <v>20</v>
       </c>
       <c r="B221" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C221">
         <v>56.31222222222222</v>
@@ -3629,7 +3635,7 @@
         <v>20</v>
       </c>
       <c r="B222" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C222">
         <v>84.56361111111111</v>
@@ -3643,7 +3649,7 @@
         <v>21</v>
       </c>
       <c r="B223" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C223">
         <v>8.219722222222222</v>
@@ -3657,7 +3663,7 @@
         <v>21</v>
       </c>
       <c r="B224" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C224">
         <v>8.219722222222222</v>
@@ -3671,7 +3677,7 @@
         <v>21</v>
       </c>
       <c r="B225" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C225">
         <v>6.753333333333333</v>
@@ -3685,7 +3691,7 @@
         <v>21</v>
       </c>
       <c r="B226" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C226">
         <v>2.571388888888889</v>
@@ -3699,7 +3705,7 @@
         <v>21</v>
       </c>
       <c r="B227" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C227">
         <v>3.683611111111111</v>
@@ -3713,7 +3719,7 @@
         <v>21</v>
       </c>
       <c r="B228" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C228">
         <v>8.631388888888889</v>
@@ -3727,7 +3733,7 @@
         <v>21</v>
       </c>
       <c r="B229" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C229">
         <v>9.331111111111111</v>
@@ -3741,7 +3747,7 @@
         <v>21</v>
       </c>
       <c r="B230" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C230">
         <v>8.256388888888889</v>
@@ -3755,7 +3761,7 @@
         <v>21</v>
       </c>
       <c r="B231" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C231">
         <v>8.641111111111112</v>
@@ -3769,7 +3775,7 @@
         <v>21</v>
       </c>
       <c r="B232" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C232">
         <v>4.804166666666666</v>
@@ -3783,7 +3789,7 @@
         <v>21</v>
       </c>
       <c r="B233" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C233">
         <v>5.882777777777778</v>
@@ -3797,7 +3803,7 @@
         <v>21</v>
       </c>
       <c r="B234" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C234">
         <v>6.680555555555555</v>
@@ -3811,7 +3817,7 @@
         <v>21</v>
       </c>
       <c r="B235" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C235">
         <v>7.816111111111111</v>
@@ -3825,7 +3831,7 @@
         <v>22</v>
       </c>
       <c r="B236" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C236">
         <v>0.5022222222222222</v>
@@ -3839,7 +3845,7 @@
         <v>22</v>
       </c>
       <c r="B237" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C237">
         <v>2.0825</v>
@@ -3853,7 +3859,7 @@
         <v>22</v>
       </c>
       <c r="B238" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C238">
         <v>1.555833333333333</v>
@@ -3867,7 +3873,7 @@
         <v>22</v>
       </c>
       <c r="B239" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C239">
         <v>1.188333333333333</v>
@@ -3881,7 +3887,7 @@
         <v>22</v>
       </c>
       <c r="B240" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C240">
         <v>0.6247222222222222</v>
@@ -3895,7 +3901,7 @@
         <v>22</v>
       </c>
       <c r="B241" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C241">
         <v>0.6491666666666667</v>
@@ -3909,7 +3915,7 @@
         <v>22</v>
       </c>
       <c r="B242" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C242">
         <v>0.6875</v>
@@ -3923,7 +3929,7 @@
         <v>22</v>
       </c>
       <c r="B243" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C243">
         <v>0.5686111111111111</v>
@@ -3937,7 +3943,7 @@
         <v>22</v>
       </c>
       <c r="B244" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C244">
         <v>0.6036111111111111</v>
@@ -3951,7 +3957,7 @@
         <v>22</v>
       </c>
       <c r="B245" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C245">
         <v>0.2116666666666667</v>
@@ -3965,7 +3971,7 @@
         <v>22</v>
       </c>
       <c r="B246" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C246">
         <v>0.5252777777777777</v>
@@ -3979,7 +3985,7 @@
         <v>22</v>
       </c>
       <c r="B247" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C247">
         <v>0.7352777777777778</v>
@@ -3993,7 +3999,7 @@
         <v>22</v>
       </c>
       <c r="B248" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C248">
         <v>1.201944444444444</v>
@@ -4007,7 +4013,7 @@
         <v>23</v>
       </c>
       <c r="B249" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C249">
         <v>0.2058333333333333</v>
@@ -4021,7 +4027,7 @@
         <v>23</v>
       </c>
       <c r="B250" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C250">
         <v>0.2791666666666667</v>
@@ -4035,7 +4041,7 @@
         <v>23</v>
       </c>
       <c r="B251" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C251">
         <v>0.25</v>
@@ -4049,7 +4055,7 @@
         <v>23</v>
       </c>
       <c r="B252" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C252">
         <v>0.2522222222222222</v>
@@ -4063,7 +4069,7 @@
         <v>23</v>
       </c>
       <c r="B253" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C253">
         <v>0.245</v>
@@ -4077,7 +4083,7 @@
         <v>23</v>
       </c>
       <c r="B254" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C254">
         <v>0.2475</v>
@@ -4091,7 +4097,7 @@
         <v>23</v>
       </c>
       <c r="B255" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C255">
         <v>0.25</v>
@@ -4105,7 +4111,7 @@
         <v>23</v>
       </c>
       <c r="B256" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C256">
         <v>0.2744444444444444</v>
@@ -4119,7 +4125,7 @@
         <v>23</v>
       </c>
       <c r="B257" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C257">
         <v>0.2486111111111111</v>
@@ -4133,7 +4139,7 @@
         <v>23</v>
       </c>
       <c r="B258" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C258">
         <v>0.1469444444444444</v>
@@ -4147,7 +4153,7 @@
         <v>23</v>
       </c>
       <c r="B259" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C259">
         <v>0.2044444444444445</v>
@@ -4161,7 +4167,7 @@
         <v>23</v>
       </c>
       <c r="B260" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C260">
         <v>0.2191666666666667</v>
@@ -4175,7 +4181,7 @@
         <v>23</v>
       </c>
       <c r="B261" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C261">
         <v>0.1605555555555556</v>
@@ -4189,7 +4195,7 @@
         <v>24</v>
       </c>
       <c r="B262" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C262">
         <v>17.65277777777778</v>
@@ -4203,7 +4209,7 @@
         <v>24</v>
       </c>
       <c r="B263" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C263">
         <v>18.68194444444444</v>
@@ -4217,7 +4223,7 @@
         <v>24</v>
       </c>
       <c r="B264" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C264">
         <v>19.55166666666667</v>
@@ -4231,7 +4237,7 @@
         <v>24</v>
       </c>
       <c r="B265" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C265">
         <v>21.23</v>
@@ -4245,7 +4251,7 @@
         <v>24</v>
       </c>
       <c r="B266" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C266">
         <v>22.94472222222222</v>
@@ -4259,7 +4265,7 @@
         <v>24</v>
       </c>
       <c r="B267" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C267">
         <v>24.23111111111111</v>
@@ -4273,7 +4279,7 @@
         <v>24</v>
       </c>
       <c r="B268" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C268">
         <v>26.40277777777778</v>
@@ -4287,7 +4293,7 @@
         <v>24</v>
       </c>
       <c r="B269" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C269">
         <v>27.37805555555556</v>
@@ -4301,7 +4307,7 @@
         <v>24</v>
       </c>
       <c r="B270" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C270">
         <v>27.88138888888889</v>
@@ -4315,7 +4321,7 @@
         <v>24</v>
       </c>
       <c r="B271" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C271">
         <v>11.13083333333333</v>
@@ -4329,7 +4335,7 @@
         <v>24</v>
       </c>
       <c r="B272" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C272">
         <v>17.93277777777778</v>
@@ -4343,7 +4349,7 @@
         <v>24</v>
       </c>
       <c r="B273" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C273">
         <v>26.82333333333333</v>
@@ -4357,7 +4363,7 @@
         <v>24</v>
       </c>
       <c r="B274" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C274">
         <v>28.36694444444445</v>
@@ -4371,7 +4377,7 @@
         <v>25</v>
       </c>
       <c r="B275" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C275">
         <v>6.602777777777778</v>
@@ -4385,7 +4391,7 @@
         <v>25</v>
       </c>
       <c r="B276" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C276">
         <v>5.928888888888889</v>
@@ -4399,7 +4405,7 @@
         <v>25</v>
       </c>
       <c r="B277" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C277">
         <v>6.749722222222222</v>
@@ -4413,7 +4419,7 @@
         <v>25</v>
       </c>
       <c r="B278" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C278">
         <v>7.423611111111111</v>
@@ -4427,7 +4433,7 @@
         <v>25</v>
       </c>
       <c r="B279" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C279">
         <v>7.7175</v>
@@ -4441,7 +4447,7 @@
         <v>25</v>
       </c>
       <c r="B280" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C280">
         <v>7.864444444444445</v>
@@ -4455,7 +4461,7 @@
         <v>25</v>
       </c>
       <c r="B281" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C281">
         <v>8.305555555555555</v>
@@ -4469,7 +4475,7 @@
         <v>25</v>
       </c>
       <c r="B282" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C282">
         <v>8.989722222222222</v>
@@ -4483,7 +4489,7 @@
         <v>25</v>
       </c>
       <c r="B283" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C283">
         <v>9.484722222222222</v>
@@ -4497,7 +4503,7 @@
         <v>25</v>
       </c>
       <c r="B284" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C284">
         <v>3.410833333333333</v>
@@ -4511,7 +4517,7 @@
         <v>25</v>
       </c>
       <c r="B285" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C285">
         <v>4.5975</v>
@@ -4525,7 +4531,7 @@
         <v>25</v>
       </c>
       <c r="B286" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C286">
         <v>7.714444444444444</v>
@@ -4539,7 +4545,7 @@
         <v>25</v>
       </c>
       <c r="B287" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C287">
         <v>9.737222222222222</v>
@@ -4553,7 +4559,7 @@
         <v>26</v>
       </c>
       <c r="B288" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C288">
         <v>0.1225</v>
@@ -4567,7 +4573,7 @@
         <v>26</v>
       </c>
       <c r="B289" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C289">
         <v>0.5197222222222222</v>
@@ -4581,7 +4587,7 @@
         <v>26</v>
       </c>
       <c r="B290" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C290">
         <v>0.2697222222222222</v>
@@ -4595,7 +4601,7 @@
         <v>26</v>
       </c>
       <c r="B291" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C291">
         <v>0.2697222222222222</v>
@@ -4609,7 +4615,7 @@
         <v>26</v>
       </c>
       <c r="B292" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C292">
         <v>0.9066666666666666</v>
@@ -4623,7 +4629,7 @@
         <v>26</v>
       </c>
       <c r="B293" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C293">
         <v>0.7719444444444444</v>
@@ -4637,7 +4643,7 @@
         <v>26</v>
       </c>
       <c r="B294" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C294">
         <v>0.3597222222222222</v>
@@ -4651,7 +4657,7 @@
         <v>26</v>
       </c>
       <c r="B295" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C295">
         <v>0.985</v>
@@ -4665,7 +4671,7 @@
         <v>26</v>
       </c>
       <c r="B296" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C296">
         <v>1.001944444444445</v>
@@ -4679,7 +4685,7 @@
         <v>26</v>
       </c>
       <c r="B297" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C297">
         <v>1.029166666666667</v>
@@ -4693,7 +4699,7 @@
         <v>26</v>
       </c>
       <c r="B298" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C298">
         <v>1.153055555555556</v>
@@ -4707,7 +4713,7 @@
         <v>26</v>
       </c>
       <c r="B299" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C299">
         <v>1.204166666666667</v>
@@ -4721,7 +4727,7 @@
         <v>26</v>
       </c>
       <c r="B300" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C300">
         <v>1.254166666666667</v>
@@ -4735,7 +4741,7 @@
         <v>27</v>
       </c>
       <c r="B301" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C301">
         <v>4.703888888888889</v>
@@ -4749,7 +4755,7 @@
         <v>27</v>
       </c>
       <c r="B302" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C302">
         <v>4.998055555555555</v>
@@ -4763,7 +4769,7 @@
         <v>27</v>
       </c>
       <c r="B303" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C303">
         <v>4.152777777777778</v>
@@ -4777,7 +4783,7 @@
         <v>27</v>
       </c>
       <c r="B304" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C304">
         <v>3.699444444444445</v>
@@ -4791,7 +4797,7 @@
         <v>27</v>
       </c>
       <c r="B305" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C305">
         <v>4.152777777777778</v>
@@ -4805,7 +4811,7 @@
         <v>27</v>
       </c>
       <c r="B306" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C306">
         <v>5.193888888888889</v>
@@ -4819,7 +4825,7 @@
         <v>27</v>
       </c>
       <c r="B307" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C307">
         <v>6.183611111111111</v>
@@ -4833,7 +4839,7 @@
         <v>27</v>
       </c>
       <c r="B308" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C308">
         <v>7.9675</v>
@@ -4847,7 +4853,7 @@
         <v>27</v>
       </c>
       <c r="B309" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C309">
         <v>7.991944444444444</v>
@@ -4861,7 +4867,7 @@
         <v>27</v>
       </c>
       <c r="B310" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C310">
         <v>3.724722222222222</v>
@@ -4875,7 +4881,7 @@
         <v>27</v>
       </c>
       <c r="B311" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C311">
         <v>5.591666666666667</v>
@@ -4889,7 +4895,7 @@
         <v>27</v>
       </c>
       <c r="B312" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C312">
         <v>7.243055555555555</v>
@@ -4903,7 +4909,7 @@
         <v>27</v>
       </c>
       <c r="B313" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C313">
         <v>7.11</v>
@@ -4917,7 +4923,7 @@
         <v>28</v>
       </c>
       <c r="B314" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C314">
         <v>9.224166666666667</v>
@@ -4931,7 +4937,7 @@
         <v>28</v>
       </c>
       <c r="B315" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C315">
         <v>8.097222222222221</v>
@@ -4945,7 +4951,7 @@
         <v>28</v>
       </c>
       <c r="B316" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C316">
         <v>8.834722222222222</v>
@@ -4959,7 +4965,7 @@
         <v>28</v>
       </c>
       <c r="B317" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C317">
         <v>9.811111111111112</v>
@@ -4973,7 +4979,7 @@
         <v>28</v>
       </c>
       <c r="B318" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C318">
         <v>10.28638888888889</v>
@@ -4987,7 +4993,7 @@
         <v>28</v>
       </c>
       <c r="B319" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C319">
         <v>11.6375</v>
@@ -5001,7 +5007,7 @@
         <v>28</v>
       </c>
       <c r="B320" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C320">
         <v>8.300555555555556</v>
@@ -5015,7 +5021,7 @@
         <v>28</v>
       </c>
       <c r="B321" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C321">
         <v>8.294166666666667</v>
@@ -5029,7 +5035,7 @@
         <v>28</v>
       </c>
       <c r="B322" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C322">
         <v>8.652222222222223</v>
@@ -5043,7 +5049,7 @@
         <v>28</v>
       </c>
       <c r="B323" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C323">
         <v>3.089444444444445</v>
@@ -5057,7 +5063,7 @@
         <v>28</v>
       </c>
       <c r="B324" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C324">
         <v>3.726666666666667</v>
@@ -5071,7 +5077,7 @@
         <v>28</v>
       </c>
       <c r="B325" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C325">
         <v>5.495277777777778</v>
@@ -5085,7 +5091,7 @@
         <v>28</v>
       </c>
       <c r="B326" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C326">
         <v>6.546111111111111</v>
@@ -5099,7 +5105,7 @@
         <v>29</v>
       </c>
       <c r="B327" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C327">
         <v>0.6002777777777778</v>
@@ -5113,7 +5119,7 @@
         <v>29</v>
       </c>
       <c r="B328" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C328">
         <v>0.5758333333333333</v>
@@ -5127,7 +5133,7 @@
         <v>29</v>
       </c>
       <c r="B329" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C329">
         <v>0.5266666666666666</v>
@@ -5141,7 +5147,7 @@
         <v>29</v>
       </c>
       <c r="B330" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C330">
         <v>0.49</v>
@@ -5155,7 +5161,7 @@
         <v>29</v>
       </c>
       <c r="B331" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C331">
         <v>0.6125</v>
@@ -5169,7 +5175,7 @@
         <v>29</v>
       </c>
       <c r="B332" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C332">
         <v>0.5022222222222222</v>
@@ -5183,7 +5189,7 @@
         <v>29</v>
       </c>
       <c r="B333" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C333">
         <v>0.3841666666666667</v>
@@ -5197,7 +5203,7 @@
         <v>29</v>
       </c>
       <c r="B334" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C334">
         <v>0.3858333333333333</v>
@@ -5211,7 +5217,7 @@
         <v>29</v>
       </c>
       <c r="B335" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C335">
         <v>0.2163888888888889</v>
@@ -5225,7 +5231,7 @@
         <v>29</v>
       </c>
       <c r="B336" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C336">
         <v>0.2619444444444444</v>
@@ -5239,7 +5245,7 @@
         <v>29</v>
       </c>
       <c r="B337" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C337">
         <v>0.2669444444444444</v>
@@ -5253,7 +5259,7 @@
         <v>29</v>
       </c>
       <c r="B338" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C338">
         <v>0.3594444444444445</v>
@@ -5267,7 +5273,7 @@
         <v>29</v>
       </c>
       <c r="B339" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C339">
         <v>0.3875</v>
@@ -5281,13 +5287,13 @@
         <v>30</v>
       </c>
       <c r="B340" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C340">
-        <v>76.64833333333333</v>
+        <v>0.6002777777777778</v>
       </c>
       <c r="D340">
-        <v>35.11305555555555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5295,13 +5301,13 @@
         <v>30</v>
       </c>
       <c r="B341" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C341">
-        <v>80.90861111111111</v>
+        <v>0.5758333333333333</v>
       </c>
       <c r="D341">
-        <v>43.24305555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5309,13 +5315,13 @@
         <v>30</v>
       </c>
       <c r="B342" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C342">
-        <v>74.14472222222223</v>
+        <v>0.5266666666666666</v>
       </c>
       <c r="D342">
-        <v>59.66194444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5323,13 +5329,13 @@
         <v>30</v>
       </c>
       <c r="B343" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C343">
-        <v>68.93722222222222</v>
+        <v>0.49</v>
       </c>
       <c r="D343">
-        <v>179.4602777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5337,13 +5343,13 @@
         <v>30</v>
       </c>
       <c r="B344" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C344">
-        <v>61.8075</v>
+        <v>0.6125</v>
       </c>
       <c r="D344">
-        <v>201.7544444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5351,13 +5357,13 @@
         <v>30</v>
       </c>
       <c r="B345" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C345">
-        <v>59.50416666666667</v>
+        <v>0.5022222222222222</v>
       </c>
       <c r="D345">
-        <v>192.0925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5365,13 +5371,13 @@
         <v>30</v>
       </c>
       <c r="B346" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C346">
-        <v>66.14611111111111</v>
+        <v>0.3841666666666667</v>
       </c>
       <c r="D346">
-        <v>202.5288888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5379,13 +5385,13 @@
         <v>30</v>
       </c>
       <c r="B347" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C347">
-        <v>68.33222222222223</v>
+        <v>0.3858333333333333</v>
       </c>
       <c r="D347">
-        <v>138.0383333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5393,13 +5399,13 @@
         <v>30</v>
       </c>
       <c r="B348" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C348">
-        <v>39.34722222222222</v>
+        <v>0.2163888888888889</v>
       </c>
       <c r="D348">
-        <v>126.8880555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5407,13 +5413,13 @@
         <v>30</v>
       </c>
       <c r="B349" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C349">
-        <v>16.48944444444444</v>
+        <v>0.2619444444444444</v>
       </c>
       <c r="D349">
-        <v>79.93972222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5421,13 +5427,13 @@
         <v>30</v>
       </c>
       <c r="B350" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C350">
-        <v>20.13666666666667</v>
+        <v>0.2669444444444444</v>
       </c>
       <c r="D350">
-        <v>70.97750000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5435,13 +5441,13 @@
         <v>30</v>
       </c>
       <c r="B351" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C351">
-        <v>18.49861111111111</v>
+        <v>0.3594444444444445</v>
       </c>
       <c r="D351">
-        <v>77.7475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5449,13 +5455,13 @@
         <v>30</v>
       </c>
       <c r="B352" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C352">
-        <v>22.11</v>
+        <v>0.3875</v>
       </c>
       <c r="D352">
-        <v>81.71250000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5463,13 +5469,13 @@
         <v>31</v>
       </c>
       <c r="B353" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C353">
-        <v>24.61027777777778</v>
+        <v>76.64833333333333</v>
       </c>
       <c r="D353">
-        <v>35.88861111111111</v>
+        <v>35.11305555555555</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5477,13 +5483,13 @@
         <v>31</v>
       </c>
       <c r="B354" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C354">
-        <v>25.49222222222222</v>
+        <v>80.90861111111111</v>
       </c>
       <c r="D354">
-        <v>37.95361111111111</v>
+        <v>43.24305555555556</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5491,13 +5497,13 @@
         <v>31</v>
       </c>
       <c r="B355" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C355">
-        <v>22.89527777777778</v>
+        <v>74.14472222222223</v>
       </c>
       <c r="D355">
-        <v>38.425</v>
+        <v>59.66194444444444</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5505,13 +5511,13 @@
         <v>31</v>
       </c>
       <c r="B356" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C356">
-        <v>28.10138888888889</v>
+        <v>68.93722222222222</v>
       </c>
       <c r="D356">
-        <v>36.18055555555556</v>
+        <v>179.4602777777778</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5519,13 +5525,13 @@
         <v>31</v>
       </c>
       <c r="B357" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C357">
-        <v>32.31555555555556</v>
+        <v>61.8075</v>
       </c>
       <c r="D357">
-        <v>35.67555555555555</v>
+        <v>201.7544444444444</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5533,13 +5539,13 @@
         <v>31</v>
       </c>
       <c r="B358" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C358">
-        <v>34.33666666666667</v>
+        <v>59.50416666666667</v>
       </c>
       <c r="D358">
-        <v>38.75027777777778</v>
+        <v>192.0925</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5547,13 +5553,13 @@
         <v>31</v>
       </c>
       <c r="B359" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C359">
-        <v>38.72222222222222</v>
+        <v>66.14611111111111</v>
       </c>
       <c r="D359">
-        <v>37.31388888888889</v>
+        <v>202.5288888888889</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5561,13 +5567,13 @@
         <v>31</v>
       </c>
       <c r="B360" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C360">
-        <v>41.90722222222222</v>
+        <v>68.33222222222223</v>
       </c>
       <c r="D360">
-        <v>39.47972222222222</v>
+        <v>138.0383333333333</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5575,13 +5581,13 @@
         <v>31</v>
       </c>
       <c r="B361" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C361">
-        <v>41.30694444444445</v>
+        <v>39.34722222222222</v>
       </c>
       <c r="D361">
-        <v>37.68944444444445</v>
+        <v>126.8880555555556</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5589,13 +5595,13 @@
         <v>31</v>
       </c>
       <c r="B362" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C362">
-        <v>13.3525</v>
+        <v>16.48944444444444</v>
       </c>
       <c r="D362">
-        <v>30.76</v>
+        <v>79.93972222222222</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5603,13 +5609,13 @@
         <v>31</v>
       </c>
       <c r="B363" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C363">
-        <v>13.00944444444444</v>
+        <v>20.13666666666667</v>
       </c>
       <c r="D363">
-        <v>33.3525</v>
+        <v>70.97750000000001</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -5617,13 +5623,13 @@
         <v>31</v>
       </c>
       <c r="B364" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C364">
-        <v>32.64777777777778</v>
+        <v>18.49861111111111</v>
       </c>
       <c r="D364">
-        <v>39.43222222222222</v>
+        <v>77.7475</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5631,13 +5637,13 @@
         <v>31</v>
       </c>
       <c r="B365" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C365">
-        <v>43.29</v>
+        <v>22.11</v>
       </c>
       <c r="D365">
-        <v>39.13472222222222</v>
+        <v>81.71250000000001</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5645,13 +5651,13 @@
         <v>32</v>
       </c>
       <c r="B366" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C366">
-        <v>18.31416666666667</v>
+        <v>24.61027777777778</v>
       </c>
       <c r="D366">
-        <v>36.465</v>
+        <v>35.88861111111111</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5659,13 +5665,13 @@
         <v>32</v>
       </c>
       <c r="B367" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C367">
-        <v>17.65277777777778</v>
+        <v>25.49222222222222</v>
       </c>
       <c r="D367">
-        <v>37.33111111111111</v>
+        <v>37.95361111111111</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5673,13 +5679,13 @@
         <v>32</v>
       </c>
       <c r="B368" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C368">
-        <v>17.00361111111111</v>
+        <v>22.89527777777778</v>
       </c>
       <c r="D368">
-        <v>38.26694444444445</v>
+        <v>38.425</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -5687,13 +5693,13 @@
         <v>32</v>
       </c>
       <c r="B369" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C369">
-        <v>16.57472222222222</v>
+        <v>28.10138888888889</v>
       </c>
       <c r="D369">
-        <v>38.80944444444444</v>
+        <v>36.18055555555556</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -5701,13 +5707,13 @@
         <v>32</v>
       </c>
       <c r="B370" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C370">
-        <v>17.56694444444445</v>
+        <v>32.31555555555556</v>
       </c>
       <c r="D370">
-        <v>39.31777777777778</v>
+        <v>35.67555555555555</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5715,13 +5721,13 @@
         <v>32</v>
       </c>
       <c r="B371" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C371">
-        <v>19.88861111111111</v>
+        <v>34.33666666666667</v>
       </c>
       <c r="D371">
-        <v>18.66916666666667</v>
+        <v>38.75027777777778</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -5729,13 +5735,13 @@
         <v>32</v>
       </c>
       <c r="B372" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C372">
-        <v>23.93416666666667</v>
+        <v>38.72222222222222</v>
       </c>
       <c r="D372">
-        <v>8.970277777777778</v>
+        <v>37.31388888888889</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -5743,13 +5749,13 @@
         <v>32</v>
       </c>
       <c r="B373" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C373">
-        <v>19.43472222222222</v>
+        <v>41.90722222222222</v>
       </c>
       <c r="D373">
-        <v>34.5775</v>
+        <v>39.47972222222222</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -5757,13 +5763,13 @@
         <v>32</v>
       </c>
       <c r="B374" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C374">
-        <v>17.78583333333333</v>
+        <v>41.30694444444445</v>
       </c>
       <c r="D374">
-        <v>34.6675</v>
+        <v>37.68944444444445</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -5771,13 +5777,13 @@
         <v>32</v>
       </c>
       <c r="B375" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C375">
-        <v>7.890833333333333</v>
+        <v>13.3525</v>
       </c>
       <c r="D375">
-        <v>32.53166666666667</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -5785,13 +5791,13 @@
         <v>32</v>
       </c>
       <c r="B376" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C376">
-        <v>6.443611111111111</v>
+        <v>13.00944444444444</v>
       </c>
       <c r="D376">
-        <v>28.02888888888889</v>
+        <v>33.3525</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5799,13 +5805,13 @@
         <v>32</v>
       </c>
       <c r="B377" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C377">
-        <v>9.902222222222223</v>
+        <v>32.64777777777778</v>
       </c>
       <c r="D377">
-        <v>27.18833333333333</v>
+        <v>39.43222222222222</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5813,13 +5819,13 @@
         <v>32</v>
       </c>
       <c r="B378" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C378">
-        <v>12.71777777777778</v>
+        <v>43.29</v>
       </c>
       <c r="D378">
-        <v>27.185</v>
+        <v>39.13472222222222</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5827,13 +5833,13 @@
         <v>33</v>
       </c>
       <c r="B379" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C379">
-        <v>46.64805555555556</v>
+        <v>18.31416666666667</v>
       </c>
       <c r="D379">
-        <v>97.20166666666667</v>
+        <v>36.465</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5841,13 +5847,13 @@
         <v>33</v>
       </c>
       <c r="B380" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C380">
-        <v>46.6725</v>
+        <v>17.65277777777778</v>
       </c>
       <c r="D380">
-        <v>94.59722222222223</v>
+        <v>37.33111111111111</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5855,13 +5861,13 @@
         <v>33</v>
       </c>
       <c r="B381" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C381">
-        <v>49.28166666666667</v>
+        <v>17.00361111111111</v>
       </c>
       <c r="D381">
-        <v>92.50444444444445</v>
+        <v>38.26694444444445</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5869,13 +5875,13 @@
         <v>33</v>
       </c>
       <c r="B382" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C382">
-        <v>49.40416666666667</v>
+        <v>16.57472222222222</v>
       </c>
       <c r="D382">
-        <v>94.10916666666667</v>
+        <v>38.80944444444444</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5883,13 +5889,13 @@
         <v>33</v>
       </c>
       <c r="B383" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C383">
-        <v>50.78861111111111</v>
+        <v>17.56694444444445</v>
       </c>
       <c r="D383">
-        <v>104.9333333333333</v>
+        <v>39.31777777777778</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -5897,13 +5903,13 @@
         <v>33</v>
       </c>
       <c r="B384" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C384">
-        <v>56.74194444444444</v>
+        <v>19.88861111111111</v>
       </c>
       <c r="D384">
-        <v>117.3113888888889</v>
+        <v>18.66916666666667</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5911,13 +5917,13 @@
         <v>33</v>
       </c>
       <c r="B385" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C385">
-        <v>58.08944444444445</v>
+        <v>23.93416666666667</v>
       </c>
       <c r="D385">
-        <v>113.5002777777778</v>
+        <v>8.970277777777778</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5925,13 +5931,13 @@
         <v>33</v>
       </c>
       <c r="B386" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C386">
-        <v>61.20111111111111</v>
+        <v>19.43472222222222</v>
       </c>
       <c r="D386">
-        <v>106.0505555555556</v>
+        <v>34.5775</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5939,13 +5945,13 @@
         <v>33</v>
       </c>
       <c r="B387" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C387">
-        <v>64.92472222222223</v>
+        <v>17.78583333333333</v>
       </c>
       <c r="D387">
-        <v>92.80416666666666</v>
+        <v>34.6675</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5953,13 +5959,13 @@
         <v>33</v>
       </c>
       <c r="B388" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C388">
-        <v>34.68694444444444</v>
+        <v>7.890833333333333</v>
       </c>
       <c r="D388">
-        <v>111.2963888888889</v>
+        <v>32.53166666666667</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5967,13 +5973,13 @@
         <v>33</v>
       </c>
       <c r="B389" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C389">
-        <v>30.58861111111111</v>
+        <v>6.443611111111111</v>
       </c>
       <c r="D389">
-        <v>117.7855555555556</v>
+        <v>28.02888888888889</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5981,13 +5987,13 @@
         <v>33</v>
       </c>
       <c r="B390" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C390">
-        <v>38.38694444444445</v>
+        <v>9.902222222222223</v>
       </c>
       <c r="D390">
-        <v>129.37</v>
+        <v>27.18833333333333</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5995,13 +6001,13 @@
         <v>33</v>
       </c>
       <c r="B391" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C391">
-        <v>62.20138888888889</v>
+        <v>12.71777777777778</v>
       </c>
       <c r="D391">
-        <v>120.4041666666667</v>
+        <v>27.185</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6009,13 +6015,13 @@
         <v>34</v>
       </c>
       <c r="B392" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C392">
-        <v>1.176111111111111</v>
+        <v>46.64805555555556</v>
       </c>
       <c r="D392">
-        <v>0.1908333333333333</v>
+        <v>97.20166666666667</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6023,13 +6029,13 @@
         <v>34</v>
       </c>
       <c r="B393" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C393">
-        <v>1.212777777777778</v>
+        <v>46.6725</v>
       </c>
       <c r="D393">
-        <v>0.2805555555555556</v>
+        <v>94.59722222222223</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6037,13 +6043,13 @@
         <v>34</v>
       </c>
       <c r="B394" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C394">
-        <v>1.176111111111111</v>
+        <v>49.28166666666667</v>
       </c>
       <c r="D394">
-        <v>0.2133333333333333</v>
+        <v>92.50444444444445</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6051,13 +6057,13 @@
         <v>34</v>
       </c>
       <c r="B395" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C395">
-        <v>1.273888888888889</v>
+        <v>49.40416666666667</v>
       </c>
       <c r="D395">
-        <v>0.2580555555555555</v>
+        <v>94.10916666666667</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6065,13 +6071,13 @@
         <v>34</v>
       </c>
       <c r="B396" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C396">
-        <v>1.273888888888889</v>
+        <v>50.78861111111111</v>
       </c>
       <c r="D396">
-        <v>0.2244444444444444</v>
+        <v>104.9333333333333</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6079,13 +6085,13 @@
         <v>34</v>
       </c>
       <c r="B397" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C397">
-        <v>1.335277777777778</v>
+        <v>56.74194444444444</v>
       </c>
       <c r="D397">
-        <v>0.2244444444444444</v>
+        <v>117.3113888888889</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6093,13 +6099,13 @@
         <v>34</v>
       </c>
       <c r="B398" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C398">
-        <v>1.596388888888889</v>
+        <v>58.08944444444445</v>
       </c>
       <c r="D398">
-        <v>0.2244444444444444</v>
+        <v>113.5002777777778</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -6107,13 +6113,13 @@
         <v>34</v>
       </c>
       <c r="B399" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C399">
-        <v>1.721111111111111</v>
+        <v>61.20111111111111</v>
       </c>
       <c r="D399">
-        <v>0.2355555555555555</v>
+        <v>106.0505555555556</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6121,13 +6127,13 @@
         <v>34</v>
       </c>
       <c r="B400" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C400">
-        <v>1.937777777777778</v>
+        <v>64.92472222222223</v>
       </c>
       <c r="D400">
-        <v>0.2469444444444444</v>
+        <v>92.80416666666666</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6135,13 +6141,13 @@
         <v>34</v>
       </c>
       <c r="B401" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C401">
-        <v>0.9813888888888889</v>
+        <v>34.68694444444444</v>
       </c>
       <c r="D401">
-        <v>0.2469444444444444</v>
+        <v>111.2963888888889</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6149,13 +6155,13 @@
         <v>34</v>
       </c>
       <c r="B402" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C402">
-        <v>1.290277777777778</v>
+        <v>30.58861111111111</v>
       </c>
       <c r="D402">
-        <v>0.2694444444444444</v>
+        <v>117.7855555555556</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6163,13 +6169,13 @@
         <v>34</v>
       </c>
       <c r="B403" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C403">
-        <v>1.577222222222222</v>
+        <v>38.38694444444445</v>
       </c>
       <c r="D403">
-        <v>0.3255555555555555</v>
+        <v>129.37</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6177,13 +6183,13 @@
         <v>34</v>
       </c>
       <c r="B404" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C404">
-        <v>1.848333333333333</v>
+        <v>62.20138888888889</v>
       </c>
       <c r="D404">
-        <v>0.3816666666666667</v>
+        <v>120.4041666666667</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6191,13 +6197,13 @@
         <v>35</v>
       </c>
       <c r="B405" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C405">
-        <v>2.866388888888889</v>
+        <v>1.176111111111111</v>
       </c>
       <c r="D405">
-        <v>0.1455555555555555</v>
+        <v>0.1908333333333333</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6205,13 +6211,13 @@
         <v>35</v>
       </c>
       <c r="B406" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C406">
-        <v>3.454444444444444</v>
+        <v>1.212777777777778</v>
       </c>
       <c r="D406">
-        <v>0.1425</v>
+        <v>0.2805555555555556</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6219,13 +6225,13 @@
         <v>35</v>
       </c>
       <c r="B407" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C407">
-        <v>3.466666666666667</v>
+        <v>1.176111111111111</v>
       </c>
       <c r="D407">
-        <v>0.1358333333333333</v>
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6233,13 +6239,13 @@
         <v>35</v>
       </c>
       <c r="B408" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C408">
-        <v>3.233888888888889</v>
+        <v>1.273888888888889</v>
       </c>
       <c r="D408">
-        <v>0.1791666666666667</v>
+        <v>0.2580555555555555</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6247,13 +6253,13 @@
         <v>35</v>
       </c>
       <c r="B409" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C409">
-        <v>2.474444444444444</v>
+        <v>1.273888888888889</v>
       </c>
       <c r="D409">
-        <v>0.03583333333333334</v>
+        <v>0.2244444444444444</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6261,13 +6267,13 @@
         <v>35</v>
       </c>
       <c r="B410" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C410">
-        <v>2.633611111111111</v>
+        <v>1.335277777777778</v>
       </c>
       <c r="D410">
-        <v>0.02388888888888889</v>
+        <v>0.2244444444444444</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6275,13 +6281,13 @@
         <v>35</v>
       </c>
       <c r="B411" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C411">
-        <v>3.074722222222222</v>
+        <v>1.596388888888889</v>
       </c>
       <c r="D411">
-        <v>0.08361111111111111</v>
+        <v>0.2244444444444444</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6289,13 +6295,13 @@
         <v>35</v>
       </c>
       <c r="B412" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C412">
-        <v>3.478888888888889</v>
+        <v>1.721111111111111</v>
       </c>
       <c r="D412">
-        <v>0.12</v>
+        <v>0.2355555555555555</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6303,13 +6309,13 @@
         <v>35</v>
       </c>
       <c r="B413" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C413">
-        <v>3.674722222222222</v>
+        <v>1.937777777777778</v>
       </c>
       <c r="D413">
-        <v>0.1158333333333333</v>
+        <v>0.2469444444444444</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6317,13 +6323,13 @@
         <v>35</v>
       </c>
       <c r="B414" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C414">
-        <v>1.237222222222222</v>
+        <v>0.9813888888888889</v>
       </c>
       <c r="D414">
-        <v>0.07972222222222222</v>
+        <v>0.2469444444444444</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6331,13 +6337,13 @@
         <v>35</v>
       </c>
       <c r="B415" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C415">
-        <v>1.564444444444445</v>
+        <v>1.290277777777778</v>
       </c>
       <c r="D415">
-        <v>0.1266666666666667</v>
+        <v>0.2694444444444444</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6345,13 +6351,13 @@
         <v>35</v>
       </c>
       <c r="B416" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C416">
-        <v>2.598333333333333</v>
+        <v>1.577222222222222</v>
       </c>
       <c r="D416">
-        <v>0.0925</v>
+        <v>0.3255555555555555</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6359,13 +6365,13 @@
         <v>35</v>
       </c>
       <c r="B417" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C417">
-        <v>3.003055555555556</v>
+        <v>1.848333333333333</v>
       </c>
       <c r="D417">
-        <v>0.07027777777777777</v>
+        <v>0.3816666666666667</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6373,13 +6379,13 @@
         <v>36</v>
       </c>
       <c r="B418" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C418">
-        <v>133.2677777777778</v>
+        <v>2.866388888888889</v>
       </c>
       <c r="D418">
-        <v>35.82944444444445</v>
+        <v>0.1455555555555555</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6387,13 +6393,13 @@
         <v>36</v>
       </c>
       <c r="B419" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C419">
-        <v>129.2008333333333</v>
+        <v>3.454444444444444</v>
       </c>
       <c r="D419">
-        <v>30.69583333333333</v>
+        <v>0.1425</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6401,13 +6407,13 @@
         <v>36</v>
       </c>
       <c r="B420" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C420">
-        <v>128.0736111111111</v>
+        <v>3.466666666666667</v>
       </c>
       <c r="D420">
-        <v>31.49083333333333</v>
+        <v>0.1358333333333333</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6415,13 +6421,13 @@
         <v>36</v>
       </c>
       <c r="B421" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C421">
-        <v>128.0255555555555</v>
+        <v>3.233888888888889</v>
       </c>
       <c r="D421">
-        <v>31.92555555555555</v>
+        <v>0.1791666666666667</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6429,13 +6435,13 @@
         <v>36</v>
       </c>
       <c r="B422" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C422">
-        <v>129.2380555555555</v>
+        <v>2.474444444444444</v>
       </c>
       <c r="D422">
-        <v>29.35444444444444</v>
+        <v>0.03583333333333334</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6443,13 +6449,13 @@
         <v>36</v>
       </c>
       <c r="B423" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C423">
-        <v>129.3238888888889</v>
+        <v>2.633611111111111</v>
       </c>
       <c r="D423">
-        <v>31.11833333333333</v>
+        <v>0.02388888888888889</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6457,13 +6463,13 @@
         <v>36</v>
       </c>
       <c r="B424" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C424">
-        <v>138.9427777777778</v>
+        <v>3.074722222222222</v>
       </c>
       <c r="D424">
-        <v>26.30277777777778</v>
+        <v>0.08361111111111111</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6471,13 +6477,13 @@
         <v>36</v>
       </c>
       <c r="B425" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C425">
-        <v>139.9469444444445</v>
+        <v>3.478888888888889</v>
       </c>
       <c r="D425">
-        <v>28.64416666666667</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6485,13 +6491,13 @@
         <v>36</v>
       </c>
       <c r="B426" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C426">
-        <v>140.3980555555555</v>
+        <v>3.674722222222222</v>
       </c>
       <c r="D426">
-        <v>26.69833333333333</v>
+        <v>0.1158333333333333</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6499,13 +6505,13 @@
         <v>36</v>
       </c>
       <c r="B427" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C427">
-        <v>58.20027777777778</v>
+        <v>1.237222222222222</v>
       </c>
       <c r="D427">
-        <v>21.9775</v>
+        <v>0.07972222222222222</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6513,13 +6519,13 @@
         <v>36</v>
       </c>
       <c r="B428" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C428">
-        <v>55.26777777777778</v>
+        <v>1.564444444444445</v>
       </c>
       <c r="D428">
-        <v>22.60972222222222</v>
+        <v>0.1266666666666667</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6527,13 +6533,13 @@
         <v>36</v>
       </c>
       <c r="B429" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C429">
-        <v>109.3866666666667</v>
+        <v>2.598333333333333</v>
       </c>
       <c r="D429">
-        <v>22.87027777777778</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6541,13 +6547,13 @@
         <v>36</v>
       </c>
       <c r="B430" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C430">
-        <v>127.6063888888889</v>
+        <v>3.003055555555556</v>
       </c>
       <c r="D430">
-        <v>22.78194444444444</v>
+        <v>0.07027777777777777</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6555,13 +6561,13 @@
         <v>37</v>
       </c>
       <c r="B431" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C431">
-        <v>251.2230555555556</v>
+        <v>133.2677777777778</v>
       </c>
       <c r="D431">
-        <v>292.6522222222222</v>
+        <v>35.82944444444445</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6569,13 +6575,13 @@
         <v>37</v>
       </c>
       <c r="B432" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C432">
-        <v>237.2580555555556</v>
+        <v>129.2008333333333</v>
       </c>
       <c r="D432">
-        <v>208.875</v>
+        <v>30.69583333333333</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6583,13 +6589,13 @@
         <v>37</v>
       </c>
       <c r="B433" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C433">
-        <v>242.3786111111111</v>
+        <v>128.0736111111111</v>
       </c>
       <c r="D433">
-        <v>200.8572222222222</v>
+        <v>31.49083333333333</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6597,13 +6603,13 @@
         <v>37</v>
       </c>
       <c r="B434" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C434">
-        <v>248.5769444444445</v>
+        <v>128.0255555555555</v>
       </c>
       <c r="D434">
-        <v>199.7672222222222</v>
+        <v>31.92555555555555</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -6611,13 +6617,13 @@
         <v>37</v>
       </c>
       <c r="B435" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C435">
-        <v>272.5625</v>
+        <v>129.2380555555555</v>
       </c>
       <c r="D435">
-        <v>199.0302777777778</v>
+        <v>29.35444444444444</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6625,13 +6631,13 @@
         <v>37</v>
       </c>
       <c r="B436" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C436">
-        <v>283.1463888888889</v>
+        <v>129.3238888888889</v>
       </c>
       <c r="D436">
-        <v>233.0841666666667</v>
+        <v>31.11833333333333</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6639,13 +6645,13 @@
         <v>37</v>
       </c>
       <c r="B437" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C437">
-        <v>285.1633333333334</v>
+        <v>138.9427777777778</v>
       </c>
       <c r="D437">
-        <v>274.0144444444445</v>
+        <v>26.30277777777778</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6653,13 +6659,13 @@
         <v>37</v>
       </c>
       <c r="B438" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C438">
-        <v>289.5675</v>
+        <v>139.9469444444445</v>
       </c>
       <c r="D438">
-        <v>237.2283333333333</v>
+        <v>28.64416666666667</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6667,13 +6673,13 @@
         <v>37</v>
       </c>
       <c r="B439" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C439">
-        <v>294.49</v>
+        <v>140.3980555555555</v>
       </c>
       <c r="D439">
-        <v>268.1486111111111</v>
+        <v>26.69833333333333</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6681,13 +6687,13 @@
         <v>37</v>
       </c>
       <c r="B440" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C440">
-        <v>182.2222222222222</v>
+        <v>58.20027777777778</v>
       </c>
       <c r="D440">
-        <v>182.9433333333333</v>
+        <v>21.9775</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6695,13 +6701,13 @@
         <v>37</v>
       </c>
       <c r="B441" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C441">
-        <v>231.5616666666667</v>
+        <v>55.26777777777778</v>
       </c>
       <c r="D441">
-        <v>203.9113888888889</v>
+        <v>22.60972222222222</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6709,13 +6715,13 @@
         <v>37</v>
       </c>
       <c r="B442" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C442">
-        <v>263.5433333333334</v>
+        <v>109.3866666666667</v>
       </c>
       <c r="D442">
-        <v>190.6069444444445</v>
+        <v>22.87027777777778</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6723,13 +6729,13 @@
         <v>37</v>
       </c>
       <c r="B443" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C443">
-        <v>281.2844444444444</v>
+        <v>127.6063888888889</v>
       </c>
       <c r="D443">
-        <v>190.5597222222222</v>
+        <v>22.78194444444444</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -6737,13 +6743,13 @@
         <v>38</v>
       </c>
       <c r="B444" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C444">
-        <v>1.580277777777778</v>
+        <v>251.2230555555556</v>
       </c>
       <c r="D444">
-        <v>3.891944444444444</v>
+        <v>292.6522222222222</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6751,13 +6757,13 @@
         <v>38</v>
       </c>
       <c r="B445" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C445">
-        <v>0.9186111111111112</v>
+        <v>237.2580555555556</v>
       </c>
       <c r="D445">
-        <v>3.616944444444445</v>
+        <v>208.875</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6765,13 +6771,13 @@
         <v>38</v>
       </c>
       <c r="B446" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C446">
-        <v>1.482222222222222</v>
+        <v>242.3786111111111</v>
       </c>
       <c r="D446">
-        <v>3.159444444444444</v>
+        <v>200.8572222222222</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6779,13 +6785,13 @@
         <v>38</v>
       </c>
       <c r="B447" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C447">
-        <v>2.339722222222222</v>
+        <v>248.5769444444445</v>
       </c>
       <c r="D447">
-        <v>2.93</v>
+        <v>199.7672222222222</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6793,13 +6799,13 @@
         <v>38</v>
       </c>
       <c r="B448" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C448">
-        <v>5.353333333333333</v>
+        <v>272.5625</v>
       </c>
       <c r="D448">
-        <v>2.746666666666667</v>
+        <v>199.0302777777778</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -6807,13 +6813,13 @@
         <v>38</v>
       </c>
       <c r="B449" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C449">
-        <v>3.895555555555556</v>
+        <v>283.1463888888889</v>
       </c>
       <c r="D449">
-        <v>2.277222222222222</v>
+        <v>233.0841666666667</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6821,13 +6827,13 @@
         <v>38</v>
       </c>
       <c r="B450" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C450">
-        <v>3.930277777777778</v>
+        <v>285.1633333333334</v>
       </c>
       <c r="D450">
-        <v>1.920277777777778</v>
+        <v>274.0144444444445</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -6835,13 +6841,13 @@
         <v>38</v>
       </c>
       <c r="B451" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C451">
-        <v>3.729166666666667</v>
+        <v>289.5675</v>
       </c>
       <c r="D451">
-        <v>1.543055555555556</v>
+        <v>237.2283333333333</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6849,13 +6855,13 @@
         <v>38</v>
       </c>
       <c r="B452" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C452">
-        <v>2.942777777777778</v>
+        <v>294.49</v>
       </c>
       <c r="D452">
-        <v>1.116111111111111</v>
+        <v>268.1486111111111</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6863,13 +6869,13 @@
         <v>38</v>
       </c>
       <c r="B453" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C453">
-        <v>1.018611111111111</v>
+        <v>182.2222222222222</v>
       </c>
       <c r="D453">
-        <v>0.7813888888888889</v>
+        <v>182.9433333333333</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -6877,13 +6883,13 @@
         <v>38</v>
       </c>
       <c r="B454" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C454">
-        <v>1.962777777777778</v>
+        <v>231.5616666666667</v>
       </c>
       <c r="D454">
-        <v>0.7891666666666667</v>
+        <v>203.9113888888889</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -6891,13 +6897,13 @@
         <v>38</v>
       </c>
       <c r="B455" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C455">
-        <v>3.623611111111111</v>
+        <v>263.5433333333334</v>
       </c>
       <c r="D455">
-        <v>0.8522222222222222</v>
+        <v>190.6069444444445</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -6905,12 +6911,376 @@
         <v>38</v>
       </c>
       <c r="B456" t="s">
+        <v>53</v>
+      </c>
+      <c r="C456">
+        <v>281.2844444444444</v>
+      </c>
+      <c r="D456">
+        <v>190.5597222222222</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4">
+      <c r="A457" t="s">
+        <v>39</v>
+      </c>
+      <c r="B457" t="s">
+        <v>41</v>
+      </c>
+      <c r="C457">
+        <v>1.129444444444444</v>
+      </c>
+      <c r="D457">
+        <v>4.313333333333333</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4">
+      <c r="A458" t="s">
+        <v>39</v>
+      </c>
+      <c r="B458" t="s">
+        <v>42</v>
+      </c>
+      <c r="C458">
+        <v>1.120833333333333</v>
+      </c>
+      <c r="D458">
+        <v>3.272222222222222</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4">
+      <c r="A459" t="s">
+        <v>39</v>
+      </c>
+      <c r="B459" t="s">
+        <v>43</v>
+      </c>
+      <c r="C459">
+        <v>0.8611111111111112</v>
+      </c>
+      <c r="D459">
+        <v>2.668333333333333</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4">
+      <c r="A460" t="s">
+        <v>39</v>
+      </c>
+      <c r="B460" t="s">
+        <v>44</v>
+      </c>
+      <c r="C460">
+        <v>0.9627777777777777</v>
+      </c>
+      <c r="D460">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4">
+      <c r="A461" t="s">
+        <v>39</v>
+      </c>
+      <c r="B461" t="s">
+        <v>45</v>
+      </c>
+      <c r="C461">
+        <v>1.133055555555555</v>
+      </c>
+      <c r="D461">
+        <v>2.049166666666667</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4">
+      <c r="A462" t="s">
+        <v>39</v>
+      </c>
+      <c r="B462" t="s">
+        <v>46</v>
+      </c>
+      <c r="C462">
+        <v>1.171111111111111</v>
+      </c>
+      <c r="D462">
+        <v>1.555277777777778</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4">
+      <c r="A463" t="s">
+        <v>39</v>
+      </c>
+      <c r="B463" t="s">
+        <v>47</v>
+      </c>
+      <c r="C463">
+        <v>1.194444444444444</v>
+      </c>
+      <c r="D463">
+        <v>1.213888888888889</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4">
+      <c r="A464" t="s">
+        <v>39</v>
+      </c>
+      <c r="B464" t="s">
+        <v>48</v>
+      </c>
+      <c r="C464">
+        <v>1.28</v>
+      </c>
+      <c r="D464">
+        <v>1.668055555555556</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4">
+      <c r="A465" t="s">
+        <v>39</v>
+      </c>
+      <c r="B465" t="s">
+        <v>49</v>
+      </c>
+      <c r="C465">
+        <v>1.189444444444445</v>
+      </c>
+      <c r="D465">
+        <v>1.821111111111111</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4">
+      <c r="A466" t="s">
+        <v>39</v>
+      </c>
+      <c r="B466" t="s">
+        <v>50</v>
+      </c>
+      <c r="C466">
+        <v>0.5194444444444445</v>
+      </c>
+      <c r="D466">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4">
+      <c r="A467" t="s">
+        <v>39</v>
+      </c>
+      <c r="B467" t="s">
         <v>51</v>
       </c>
-      <c r="C456">
+      <c r="C467">
+        <v>0.5169444444444444</v>
+      </c>
+      <c r="D467">
+        <v>1.058888888888889</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4">
+      <c r="A468" t="s">
+        <v>39</v>
+      </c>
+      <c r="B468" t="s">
+        <v>52</v>
+      </c>
+      <c r="C468">
+        <v>0.9002777777777777</v>
+      </c>
+      <c r="D468">
+        <v>1.123055555555555</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4">
+      <c r="A469" t="s">
+        <v>39</v>
+      </c>
+      <c r="B469" t="s">
+        <v>53</v>
+      </c>
+      <c r="C469">
+        <v>1.116111111111111</v>
+      </c>
+      <c r="D469">
+        <v>1.143055555555555</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4">
+      <c r="A470" t="s">
+        <v>40</v>
+      </c>
+      <c r="B470" t="s">
+        <v>41</v>
+      </c>
+      <c r="C470">
+        <v>1.580277777777778</v>
+      </c>
+      <c r="D470">
+        <v>3.891944444444444</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4">
+      <c r="A471" t="s">
+        <v>40</v>
+      </c>
+      <c r="B471" t="s">
+        <v>42</v>
+      </c>
+      <c r="C471">
+        <v>0.9186111111111112</v>
+      </c>
+      <c r="D471">
+        <v>3.616944444444445</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4">
+      <c r="A472" t="s">
+        <v>40</v>
+      </c>
+      <c r="B472" t="s">
+        <v>43</v>
+      </c>
+      <c r="C472">
+        <v>1.482222222222222</v>
+      </c>
+      <c r="D472">
+        <v>3.159444444444444</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4">
+      <c r="A473" t="s">
+        <v>40</v>
+      </c>
+      <c r="B473" t="s">
+        <v>44</v>
+      </c>
+      <c r="C473">
+        <v>2.339722222222222</v>
+      </c>
+      <c r="D473">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4">
+      <c r="A474" t="s">
+        <v>40</v>
+      </c>
+      <c r="B474" t="s">
+        <v>45</v>
+      </c>
+      <c r="C474">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="D474">
+        <v>2.746666666666667</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4">
+      <c r="A475" t="s">
+        <v>40</v>
+      </c>
+      <c r="B475" t="s">
+        <v>46</v>
+      </c>
+      <c r="C475">
+        <v>3.895555555555556</v>
+      </c>
+      <c r="D475">
+        <v>2.277222222222222</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4">
+      <c r="A476" t="s">
+        <v>40</v>
+      </c>
+      <c r="B476" t="s">
+        <v>47</v>
+      </c>
+      <c r="C476">
+        <v>3.930277777777778</v>
+      </c>
+      <c r="D476">
+        <v>1.920277777777778</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4">
+      <c r="A477" t="s">
+        <v>40</v>
+      </c>
+      <c r="B477" t="s">
+        <v>48</v>
+      </c>
+      <c r="C477">
+        <v>3.729166666666667</v>
+      </c>
+      <c r="D477">
+        <v>1.543055555555556</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4">
+      <c r="A478" t="s">
+        <v>40</v>
+      </c>
+      <c r="B478" t="s">
+        <v>49</v>
+      </c>
+      <c r="C478">
+        <v>2.942777777777778</v>
+      </c>
+      <c r="D478">
+        <v>1.116111111111111</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4">
+      <c r="A479" t="s">
+        <v>40</v>
+      </c>
+      <c r="B479" t="s">
+        <v>50</v>
+      </c>
+      <c r="C479">
+        <v>1.018611111111111</v>
+      </c>
+      <c r="D479">
+        <v>0.7813888888888889</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4">
+      <c r="A480" t="s">
+        <v>40</v>
+      </c>
+      <c r="B480" t="s">
+        <v>51</v>
+      </c>
+      <c r="C480">
+        <v>1.962777777777778</v>
+      </c>
+      <c r="D480">
+        <v>0.7891666666666667</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4">
+      <c r="A481" t="s">
+        <v>40</v>
+      </c>
+      <c r="B481" t="s">
+        <v>52</v>
+      </c>
+      <c r="C481">
+        <v>3.623611111111111</v>
+      </c>
+      <c r="D481">
+        <v>0.8522222222222222</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4">
+      <c r="A482" t="s">
+        <v>40</v>
+      </c>
+      <c r="B482" t="s">
+        <v>53</v>
+      </c>
+      <c r="C482">
         <v>5.216666666666667</v>
       </c>
-      <c r="D456">
+      <c r="D482">
         <v>0.8863888888888889</v>
       </c>
     </row>
